--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Italy Serie B_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Italy Serie B_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1268" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1274" uniqueCount="300">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -661,6 +661,9 @@
     <t>['44', '90+1']</t>
   </si>
   <si>
+    <t>['47']</t>
+  </si>
+  <si>
     <t>['24', '45+2', '80']</t>
   </si>
   <si>
@@ -868,9 +871,6 @@
     <t>['8', '12', '66']</t>
   </si>
   <si>
-    <t>['47']</t>
-  </si>
-  <si>
     <t>['13']</t>
   </si>
   <si>
@@ -911,6 +911,9 @@
   </si>
   <si>
     <t>['72']</t>
+  </si>
+  <si>
+    <t>['6', '40']</t>
   </si>
 </sst>
 </file>
@@ -1272,7 +1275,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP201"/>
+  <dimension ref="A1:BP202"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1734,7 +1737,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q3">
         <v>2.63</v>
@@ -1940,7 +1943,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q4">
         <v>3.5</v>
@@ -2146,7 +2149,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q5">
         <v>3.2</v>
@@ -2352,7 +2355,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q6">
         <v>2.88</v>
@@ -2430,7 +2433,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ6">
         <v>1.2</v>
@@ -2558,7 +2561,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q7">
         <v>3.25</v>
@@ -2970,7 +2973,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q9">
         <v>3.4</v>
@@ -3176,7 +3179,7 @@
         <v>98</v>
       </c>
       <c r="P10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q10">
         <v>3.75</v>
@@ -3257,7 +3260,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ10">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3588,7 +3591,7 @@
         <v>100</v>
       </c>
       <c r="P12" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q12">
         <v>3.25</v>
@@ -3794,7 +3797,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q13">
         <v>3.4</v>
@@ -4000,7 +4003,7 @@
         <v>102</v>
       </c>
       <c r="P14" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q14">
         <v>2.3</v>
@@ -4618,7 +4621,7 @@
         <v>104</v>
       </c>
       <c r="P17" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q17">
         <v>2.88</v>
@@ -5236,7 +5239,7 @@
         <v>107</v>
       </c>
       <c r="P20" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q20">
         <v>2.88</v>
@@ -5648,7 +5651,7 @@
         <v>91</v>
       </c>
       <c r="P22" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q22">
         <v>3.4</v>
@@ -5729,7 +5732,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ22">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AR22">
         <v>1.6</v>
@@ -6060,7 +6063,7 @@
         <v>109</v>
       </c>
       <c r="P24" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q24">
         <v>2.98</v>
@@ -6138,7 +6141,7 @@
         <v>1</v>
       </c>
       <c r="AP24">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ24">
         <v>1</v>
@@ -6266,7 +6269,7 @@
         <v>110</v>
       </c>
       <c r="P25" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q25">
         <v>3.24</v>
@@ -6678,7 +6681,7 @@
         <v>102</v>
       </c>
       <c r="P27" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q27">
         <v>2.74</v>
@@ -7914,7 +7917,7 @@
         <v>102</v>
       </c>
       <c r="P33" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q33">
         <v>2.8</v>
@@ -8326,7 +8329,7 @@
         <v>116</v>
       </c>
       <c r="P35" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q35">
         <v>3</v>
@@ -8532,7 +8535,7 @@
         <v>117</v>
       </c>
       <c r="P36" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q36">
         <v>2.9</v>
@@ -9150,7 +9153,7 @@
         <v>119</v>
       </c>
       <c r="P39" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q39">
         <v>2.63</v>
@@ -9356,7 +9359,7 @@
         <v>120</v>
       </c>
       <c r="P40" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q40">
         <v>3.2</v>
@@ -9562,7 +9565,7 @@
         <v>121</v>
       </c>
       <c r="P41" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q41">
         <v>2.63</v>
@@ -9768,7 +9771,7 @@
         <v>122</v>
       </c>
       <c r="P42" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q42">
         <v>2.88</v>
@@ -10592,7 +10595,7 @@
         <v>125</v>
       </c>
       <c r="P46" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q46">
         <v>3.75</v>
@@ -11004,7 +11007,7 @@
         <v>116</v>
       </c>
       <c r="P48" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q48">
         <v>3.4</v>
@@ -11210,7 +11213,7 @@
         <v>102</v>
       </c>
       <c r="P49" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q49">
         <v>3.75</v>
@@ -11291,7 +11294,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ49">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AR49">
         <v>0.9399999999999999</v>
@@ -11416,7 +11419,7 @@
         <v>127</v>
       </c>
       <c r="P50" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q50">
         <v>3.4</v>
@@ -11622,7 +11625,7 @@
         <v>128</v>
       </c>
       <c r="P51" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q51">
         <v>3.1</v>
@@ -11700,7 +11703,7 @@
         <v>1</v>
       </c>
       <c r="AP51">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ51">
         <v>1.7</v>
@@ -11828,7 +11831,7 @@
         <v>129</v>
       </c>
       <c r="P52" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q52">
         <v>3.79</v>
@@ -12115,7 +12118,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ53">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AR53">
         <v>1.32</v>
@@ -12446,7 +12449,7 @@
         <v>130</v>
       </c>
       <c r="P55" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q55">
         <v>2.5</v>
@@ -13270,7 +13273,7 @@
         <v>102</v>
       </c>
       <c r="P59" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q59">
         <v>3.1</v>
@@ -13682,7 +13685,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q61">
         <v>2.38</v>
@@ -13888,7 +13891,7 @@
         <v>134</v>
       </c>
       <c r="P62" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q62">
         <v>3.25</v>
@@ -14300,7 +14303,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q64">
         <v>2.9</v>
@@ -14712,7 +14715,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q66">
         <v>2.4</v>
@@ -15124,7 +15127,7 @@
         <v>138</v>
       </c>
       <c r="P68" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q68">
         <v>3.1</v>
@@ -15408,7 +15411,7 @@
         <v>0.5</v>
       </c>
       <c r="AP69">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ69">
         <v>1.11</v>
@@ -15536,7 +15539,7 @@
         <v>139</v>
       </c>
       <c r="P70" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q70">
         <v>3.5</v>
@@ -15742,7 +15745,7 @@
         <v>140</v>
       </c>
       <c r="P71" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q71">
         <v>3.5</v>
@@ -15948,7 +15951,7 @@
         <v>141</v>
       </c>
       <c r="P72" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q72">
         <v>2.4</v>
@@ -16154,7 +16157,7 @@
         <v>102</v>
       </c>
       <c r="P73" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q73">
         <v>2.5</v>
@@ -16360,7 +16363,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q74">
         <v>2.5</v>
@@ -16772,7 +16775,7 @@
         <v>143</v>
       </c>
       <c r="P76" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q76">
         <v>2.95</v>
@@ -16978,7 +16981,7 @@
         <v>102</v>
       </c>
       <c r="P77" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q77">
         <v>3.2</v>
@@ -17184,7 +17187,7 @@
         <v>144</v>
       </c>
       <c r="P78" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q78">
         <v>3.1</v>
@@ -17390,7 +17393,7 @@
         <v>134</v>
       </c>
       <c r="P79" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q79">
         <v>2.5</v>
@@ -17596,7 +17599,7 @@
         <v>145</v>
       </c>
       <c r="P80" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q80">
         <v>3.4</v>
@@ -18214,7 +18217,7 @@
         <v>146</v>
       </c>
       <c r="P83" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q83">
         <v>3.6</v>
@@ -18420,7 +18423,7 @@
         <v>102</v>
       </c>
       <c r="P84" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q84">
         <v>3.4</v>
@@ -18498,7 +18501,7 @@
         <v>1</v>
       </c>
       <c r="AP84">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ84">
         <v>1.36</v>
@@ -18832,7 +18835,7 @@
         <v>147</v>
       </c>
       <c r="P86" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q86">
         <v>3.2</v>
@@ -19038,7 +19041,7 @@
         <v>148</v>
       </c>
       <c r="P87" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q87">
         <v>3.2</v>
@@ -19119,7 +19122,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ87">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AR87">
         <v>1.8</v>
@@ -19244,7 +19247,7 @@
         <v>149</v>
       </c>
       <c r="P88" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q88">
         <v>3.75</v>
@@ -19450,7 +19453,7 @@
         <v>150</v>
       </c>
       <c r="P89" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q89">
         <v>2.88</v>
@@ -19862,7 +19865,7 @@
         <v>152</v>
       </c>
       <c r="P91" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q91">
         <v>3.1</v>
@@ -22540,7 +22543,7 @@
         <v>160</v>
       </c>
       <c r="P104" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q104">
         <v>3.9</v>
@@ -22621,7 +22624,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ104">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AR104">
         <v>1.28</v>
@@ -22746,7 +22749,7 @@
         <v>161</v>
       </c>
       <c r="P105" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q105">
         <v>3.25</v>
@@ -23236,7 +23239,7 @@
         <v>0.25</v>
       </c>
       <c r="AP107">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ107">
         <v>0.5</v>
@@ -23364,7 +23367,7 @@
         <v>162</v>
       </c>
       <c r="P108" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q108">
         <v>3.1</v>
@@ -24394,7 +24397,7 @@
         <v>163</v>
       </c>
       <c r="P113" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q113">
         <v>2.75</v>
@@ -25218,7 +25221,7 @@
         <v>164</v>
       </c>
       <c r="P117" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q117">
         <v>3</v>
@@ -25424,7 +25427,7 @@
         <v>164</v>
       </c>
       <c r="P118" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q118">
         <v>2.88</v>
@@ -25836,7 +25839,7 @@
         <v>102</v>
       </c>
       <c r="P120" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q120">
         <v>2.4</v>
@@ -26248,7 +26251,7 @@
         <v>166</v>
       </c>
       <c r="P122" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q122">
         <v>3.45</v>
@@ -26535,7 +26538,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ123">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AR123">
         <v>1.52</v>
@@ -27072,7 +27075,7 @@
         <v>169</v>
       </c>
       <c r="P126" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q126">
         <v>3.1</v>
@@ -27484,7 +27487,7 @@
         <v>102</v>
       </c>
       <c r="P128" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q128">
         <v>3.65</v>
@@ -27690,7 +27693,7 @@
         <v>102</v>
       </c>
       <c r="P129" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q129">
         <v>3.35</v>
@@ -27896,7 +27899,7 @@
         <v>170</v>
       </c>
       <c r="P130" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q130">
         <v>3</v>
@@ -28102,7 +28105,7 @@
         <v>102</v>
       </c>
       <c r="P131" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q131">
         <v>3.1</v>
@@ -28180,7 +28183,7 @@
         <v>1.2</v>
       </c>
       <c r="AP131">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ131">
         <v>1.11</v>
@@ -28308,7 +28311,7 @@
         <v>119</v>
       </c>
       <c r="P132" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q132">
         <v>3.4</v>
@@ -29132,7 +29135,7 @@
         <v>173</v>
       </c>
       <c r="P136" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q136">
         <v>2.5</v>
@@ -29338,7 +29341,7 @@
         <v>174</v>
       </c>
       <c r="P137" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q137">
         <v>2.6</v>
@@ -29544,7 +29547,7 @@
         <v>175</v>
       </c>
       <c r="P138" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q138">
         <v>2.6</v>
@@ -30162,7 +30165,7 @@
         <v>178</v>
       </c>
       <c r="P141" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -30368,7 +30371,7 @@
         <v>102</v>
       </c>
       <c r="P142" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q142">
         <v>4.2</v>
@@ -30449,7 +30452,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ142">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AR142">
         <v>1.2</v>
@@ -30574,7 +30577,7 @@
         <v>179</v>
       </c>
       <c r="P143" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q143">
         <v>2.55</v>
@@ -30780,7 +30783,7 @@
         <v>102</v>
       </c>
       <c r="P144" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q144">
         <v>3.95</v>
@@ -31192,7 +31195,7 @@
         <v>181</v>
       </c>
       <c r="P146" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q146">
         <v>3.1</v>
@@ -31810,7 +31813,7 @@
         <v>183</v>
       </c>
       <c r="P149" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q149">
         <v>2.63</v>
@@ -32016,7 +32019,7 @@
         <v>184</v>
       </c>
       <c r="P150" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q150">
         <v>3.6</v>
@@ -32300,7 +32303,7 @@
         <v>0.57</v>
       </c>
       <c r="AP151">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ151">
         <v>0.6</v>
@@ -32428,7 +32431,7 @@
         <v>186</v>
       </c>
       <c r="P152" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q152">
         <v>2.95</v>
@@ -33046,7 +33049,7 @@
         <v>188</v>
       </c>
       <c r="P155" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q155">
         <v>3.7</v>
@@ -33252,7 +33255,7 @@
         <v>174</v>
       </c>
       <c r="P156" t="s">
-        <v>284</v>
+        <v>215</v>
       </c>
       <c r="Q156">
         <v>2.62</v>
@@ -35187,7 +35190,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ165">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AR165">
         <v>1.36</v>
@@ -36420,7 +36423,7 @@
         <v>1.38</v>
       </c>
       <c r="AP171">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ171">
         <v>1.4</v>
@@ -36626,7 +36629,7 @@
         <v>1</v>
       </c>
       <c r="AP172">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ172">
         <v>1</v>
@@ -37784,7 +37787,7 @@
         <v>201</v>
       </c>
       <c r="P178" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q178">
         <v>3.1</v>
@@ -38689,7 +38692,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ182">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AR182">
         <v>1.39</v>
@@ -42679,6 +42682,212 @@
       </c>
       <c r="BP201">
         <v>1.14</v>
+      </c>
+    </row>
+    <row r="202" spans="1:68">
+      <c r="A202" s="1">
+        <v>201</v>
+      </c>
+      <c r="B202">
+        <v>7509784</v>
+      </c>
+      <c r="C202" t="s">
+        <v>68</v>
+      </c>
+      <c r="D202" t="s">
+        <v>69</v>
+      </c>
+      <c r="E202" s="2">
+        <v>45669.35416666666</v>
+      </c>
+      <c r="F202">
+        <v>21</v>
+      </c>
+      <c r="G202" t="s">
+        <v>74</v>
+      </c>
+      <c r="H202" t="s">
+        <v>84</v>
+      </c>
+      <c r="I202">
+        <v>0</v>
+      </c>
+      <c r="J202">
+        <v>2</v>
+      </c>
+      <c r="K202">
+        <v>2</v>
+      </c>
+      <c r="L202">
+        <v>1</v>
+      </c>
+      <c r="M202">
+        <v>2</v>
+      </c>
+      <c r="N202">
+        <v>3</v>
+      </c>
+      <c r="O202" t="s">
+        <v>215</v>
+      </c>
+      <c r="P202" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q202">
+        <v>4.33</v>
+      </c>
+      <c r="R202">
+        <v>2.2</v>
+      </c>
+      <c r="S202">
+        <v>2.5</v>
+      </c>
+      <c r="T202">
+        <v>1.36</v>
+      </c>
+      <c r="U202">
+        <v>3</v>
+      </c>
+      <c r="V202">
+        <v>2.75</v>
+      </c>
+      <c r="W202">
+        <v>1.4</v>
+      </c>
+      <c r="X202">
+        <v>7</v>
+      </c>
+      <c r="Y202">
+        <v>1.1</v>
+      </c>
+      <c r="Z202">
+        <v>3.65</v>
+      </c>
+      <c r="AA202">
+        <v>3.4</v>
+      </c>
+      <c r="AB202">
+        <v>1.8</v>
+      </c>
+      <c r="AC202">
+        <v>1.05</v>
+      </c>
+      <c r="AD202">
+        <v>9.5</v>
+      </c>
+      <c r="AE202">
+        <v>1.25</v>
+      </c>
+      <c r="AF202">
+        <v>3.6</v>
+      </c>
+      <c r="AG202">
+        <v>1.8</v>
+      </c>
+      <c r="AH202">
+        <v>1.9</v>
+      </c>
+      <c r="AI202">
+        <v>1.75</v>
+      </c>
+      <c r="AJ202">
+        <v>2</v>
+      </c>
+      <c r="AK202">
+        <v>1.87</v>
+      </c>
+      <c r="AL202">
+        <v>1.28</v>
+      </c>
+      <c r="AM202">
+        <v>1.24</v>
+      </c>
+      <c r="AN202">
+        <v>1.2</v>
+      </c>
+      <c r="AO202">
+        <v>2.1</v>
+      </c>
+      <c r="AP202">
+        <v>1.09</v>
+      </c>
+      <c r="AQ202">
+        <v>2.18</v>
+      </c>
+      <c r="AR202">
+        <v>1.7</v>
+      </c>
+      <c r="AS202">
+        <v>1.43</v>
+      </c>
+      <c r="AT202">
+        <v>3.13</v>
+      </c>
+      <c r="AU202">
+        <v>7</v>
+      </c>
+      <c r="AV202">
+        <v>7</v>
+      </c>
+      <c r="AW202">
+        <v>9</v>
+      </c>
+      <c r="AX202">
+        <v>6</v>
+      </c>
+      <c r="AY202">
+        <v>16</v>
+      </c>
+      <c r="AZ202">
+        <v>15</v>
+      </c>
+      <c r="BA202">
+        <v>6</v>
+      </c>
+      <c r="BB202">
+        <v>2</v>
+      </c>
+      <c r="BC202">
+        <v>8</v>
+      </c>
+      <c r="BD202">
+        <v>2.65</v>
+      </c>
+      <c r="BE202">
+        <v>6.4</v>
+      </c>
+      <c r="BF202">
+        <v>1.58</v>
+      </c>
+      <c r="BG202">
+        <v>1.42</v>
+      </c>
+      <c r="BH202">
+        <v>2.65</v>
+      </c>
+      <c r="BI202">
+        <v>1.68</v>
+      </c>
+      <c r="BJ202">
+        <v>2.02</v>
+      </c>
+      <c r="BK202">
+        <v>2.08</v>
+      </c>
+      <c r="BL202">
+        <v>1.65</v>
+      </c>
+      <c r="BM202">
+        <v>2.65</v>
+      </c>
+      <c r="BN202">
+        <v>1.4</v>
+      </c>
+      <c r="BO202">
+        <v>3.55</v>
+      </c>
+      <c r="BP202">
+        <v>1.24</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Italy Serie B_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Italy Serie B_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1274" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1322" uniqueCount="305">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -664,6 +664,15 @@
     <t>['47']</t>
   </si>
   <si>
+    <t>['36', '56']</t>
+  </si>
+  <si>
+    <t>['8']</t>
+  </si>
+  <si>
+    <t>['10', '23']</t>
+  </si>
+  <si>
     <t>['24', '45+2', '80']</t>
   </si>
   <si>
@@ -671,9 +680,6 @@
   </si>
   <si>
     <t>['21', '45+2']</t>
-  </si>
-  <si>
-    <t>['8']</t>
   </si>
   <si>
     <t>['54', '67']</t>
@@ -914,6 +920,15 @@
   </si>
   <si>
     <t>['6', '40']</t>
+  </si>
+  <si>
+    <t>['3']</t>
+  </si>
+  <si>
+    <t>['36', '63']</t>
+  </si>
+  <si>
+    <t>['24', '45+4', '59']</t>
   </si>
 </sst>
 </file>
@@ -1275,7 +1290,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP202"/>
+  <dimension ref="A1:BP210"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1609,7 +1624,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ2">
         <v>1.09</v>
@@ -1737,7 +1752,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="Q3">
         <v>2.63</v>
@@ -1818,7 +1833,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ3">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1943,7 +1958,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="Q4">
         <v>3.5</v>
@@ -2021,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AQ4">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2149,7 +2164,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="Q5">
         <v>3.2</v>
@@ -2355,7 +2370,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="Q6">
         <v>2.88</v>
@@ -2436,7 +2451,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ6">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2561,7 +2576,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q7">
         <v>3.25</v>
@@ -2639,7 +2654,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ7">
         <v>1</v>
@@ -2845,7 +2860,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AQ8">
         <v>0.6</v>
@@ -2973,7 +2988,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q9">
         <v>3.4</v>
@@ -3051,10 +3066,10 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ9">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3179,7 +3194,7 @@
         <v>98</v>
       </c>
       <c r="P10" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q10">
         <v>3.75</v>
@@ -3463,10 +3478,10 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ11">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3591,7 +3606,7 @@
         <v>100</v>
       </c>
       <c r="P12" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q12">
         <v>3.25</v>
@@ -3672,7 +3687,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ12">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3797,7 +3812,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q13">
         <v>3.4</v>
@@ -3875,7 +3890,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AQ13">
         <v>0.6</v>
@@ -4003,7 +4018,7 @@
         <v>102</v>
       </c>
       <c r="P14" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q14">
         <v>2.3</v>
@@ -4287,10 +4302,10 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ15">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR15">
         <v>1.84</v>
@@ -4621,7 +4636,7 @@
         <v>104</v>
       </c>
       <c r="P17" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q17">
         <v>2.88</v>
@@ -4699,7 +4714,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="AQ17">
         <v>0.9</v>
@@ -5239,7 +5254,7 @@
         <v>107</v>
       </c>
       <c r="P20" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q20">
         <v>2.88</v>
@@ -5526,7 +5541,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ21">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR21">
         <v>1.33</v>
@@ -5651,7 +5666,7 @@
         <v>91</v>
       </c>
       <c r="P22" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q22">
         <v>3.4</v>
@@ -6063,7 +6078,7 @@
         <v>109</v>
       </c>
       <c r="P24" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q24">
         <v>2.98</v>
@@ -6269,7 +6284,7 @@
         <v>110</v>
       </c>
       <c r="P25" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="Q25">
         <v>3.24</v>
@@ -6553,7 +6568,7 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ26">
         <v>1</v>
@@ -6681,7 +6696,7 @@
         <v>102</v>
       </c>
       <c r="P27" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q27">
         <v>2.74</v>
@@ -6965,10 +6980,10 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ28">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR28">
         <v>2.15</v>
@@ -7171,10 +7186,10 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AQ29">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AR29">
         <v>1.89</v>
@@ -7377,7 +7392,7 @@
         <v>1</v>
       </c>
       <c r="AP30">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ30">
         <v>1.36</v>
@@ -7586,7 +7601,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ31">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AR31">
         <v>0</v>
@@ -7792,7 +7807,7 @@
         <v>1</v>
       </c>
       <c r="AQ32">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AR32">
         <v>0.67</v>
@@ -7917,7 +7932,7 @@
         <v>102</v>
       </c>
       <c r="P33" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q33">
         <v>2.8</v>
@@ -7998,7 +8013,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ33">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR33">
         <v>1.54</v>
@@ -8329,7 +8344,7 @@
         <v>116</v>
       </c>
       <c r="P35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q35">
         <v>3</v>
@@ -8410,7 +8425,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ35">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR35">
         <v>1.36</v>
@@ -8535,7 +8550,7 @@
         <v>117</v>
       </c>
       <c r="P36" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q36">
         <v>2.9</v>
@@ -8613,7 +8628,7 @@
         <v>0</v>
       </c>
       <c r="AP36">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AQ36">
         <v>1</v>
@@ -8819,10 +8834,10 @@
         <v>2</v>
       </c>
       <c r="AP37">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ37">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR37">
         <v>1.58</v>
@@ -9153,7 +9168,7 @@
         <v>119</v>
       </c>
       <c r="P39" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="Q39">
         <v>2.63</v>
@@ -9231,7 +9246,7 @@
         <v>0</v>
       </c>
       <c r="AP39">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AQ39">
         <v>1</v>
@@ -9359,7 +9374,7 @@
         <v>120</v>
       </c>
       <c r="P40" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q40">
         <v>3.2</v>
@@ -9437,7 +9452,7 @@
         <v>0</v>
       </c>
       <c r="AP40">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="AQ40">
         <v>0.5</v>
@@ -9565,7 +9580,7 @@
         <v>121</v>
       </c>
       <c r="P41" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q41">
         <v>2.63</v>
@@ -9771,7 +9786,7 @@
         <v>122</v>
       </c>
       <c r="P42" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q42">
         <v>2.88</v>
@@ -9849,10 +9864,10 @@
         <v>0.5</v>
       </c>
       <c r="AP42">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AQ42">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR42">
         <v>1.75</v>
@@ -10058,7 +10073,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ43">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AR43">
         <v>1.15</v>
@@ -10264,7 +10279,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ44">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AR44">
         <v>1.6</v>
@@ -10467,7 +10482,7 @@
         <v>0</v>
       </c>
       <c r="AP45">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ45">
         <v>0.9</v>
@@ -10595,7 +10610,7 @@
         <v>125</v>
       </c>
       <c r="P46" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q46">
         <v>3.75</v>
@@ -11007,7 +11022,7 @@
         <v>116</v>
       </c>
       <c r="P48" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q48">
         <v>3.4</v>
@@ -11085,7 +11100,7 @@
         <v>0</v>
       </c>
       <c r="AP48">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ48">
         <v>1</v>
@@ -11213,7 +11228,7 @@
         <v>102</v>
       </c>
       <c r="P49" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q49">
         <v>3.75</v>
@@ -11419,7 +11434,7 @@
         <v>127</v>
       </c>
       <c r="P50" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q50">
         <v>3.4</v>
@@ -11497,7 +11512,7 @@
         <v>0.5</v>
       </c>
       <c r="AP50">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ50">
         <v>1</v>
@@ -11625,7 +11640,7 @@
         <v>128</v>
       </c>
       <c r="P51" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q51">
         <v>3.1</v>
@@ -11831,7 +11846,7 @@
         <v>129</v>
       </c>
       <c r="P52" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q52">
         <v>3.79</v>
@@ -11912,7 +11927,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ52">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR52">
         <v>1.42</v>
@@ -12115,7 +12130,7 @@
         <v>1.67</v>
       </c>
       <c r="AP53">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ53">
         <v>2.18</v>
@@ -12321,7 +12336,7 @@
         <v>0</v>
       </c>
       <c r="AP54">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AQ54">
         <v>0.5</v>
@@ -12449,7 +12464,7 @@
         <v>130</v>
       </c>
       <c r="P55" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q55">
         <v>2.5</v>
@@ -12733,7 +12748,7 @@
         <v>0</v>
       </c>
       <c r="AP56">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ56">
         <v>0.6</v>
@@ -13148,7 +13163,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ58">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR58">
         <v>1.74</v>
@@ -13273,7 +13288,7 @@
         <v>102</v>
       </c>
       <c r="P59" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q59">
         <v>3.1</v>
@@ -13351,10 +13366,10 @@
         <v>0.5</v>
       </c>
       <c r="AP59">
+        <v>1</v>
+      </c>
+      <c r="AQ59">
         <v>1.1</v>
-      </c>
-      <c r="AQ59">
-        <v>1.11</v>
       </c>
       <c r="AR59">
         <v>1.43</v>
@@ -13560,7 +13575,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ60">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR60">
         <v>0.97</v>
@@ -13685,7 +13700,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q61">
         <v>2.38</v>
@@ -13763,7 +13778,7 @@
         <v>0</v>
       </c>
       <c r="AP61">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="AQ61">
         <v>0.6</v>
@@ -13891,7 +13906,7 @@
         <v>134</v>
       </c>
       <c r="P62" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q62">
         <v>3.25</v>
@@ -14303,7 +14318,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q64">
         <v>2.9</v>
@@ -14715,7 +14730,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q66">
         <v>2.4</v>
@@ -14793,10 +14808,10 @@
         <v>0.33</v>
       </c>
       <c r="AP66">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AQ66">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AR66">
         <v>1.61</v>
@@ -15127,7 +15142,7 @@
         <v>138</v>
       </c>
       <c r="P68" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q68">
         <v>3.1</v>
@@ -15414,7 +15429,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ69">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AR69">
         <v>1.8</v>
@@ -15539,7 +15554,7 @@
         <v>139</v>
       </c>
       <c r="P70" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q70">
         <v>3.5</v>
@@ -15617,7 +15632,7 @@
         <v>1.5</v>
       </c>
       <c r="AP70">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AQ70">
         <v>1.09</v>
@@ -15745,7 +15760,7 @@
         <v>140</v>
       </c>
       <c r="P71" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q71">
         <v>3.5</v>
@@ -15823,10 +15838,10 @@
         <v>2</v>
       </c>
       <c r="AP71">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ71">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR71">
         <v>1.89</v>
@@ -15951,7 +15966,7 @@
         <v>141</v>
       </c>
       <c r="P72" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q72">
         <v>2.4</v>
@@ -16032,7 +16047,7 @@
         <v>1</v>
       </c>
       <c r="AQ72">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR72">
         <v>0.97</v>
@@ -16157,7 +16172,7 @@
         <v>102</v>
       </c>
       <c r="P73" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q73">
         <v>2.5</v>
@@ -16235,7 +16250,7 @@
         <v>0</v>
       </c>
       <c r="AP73">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ73">
         <v>0.6</v>
@@ -16363,7 +16378,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q74">
         <v>2.5</v>
@@ -16444,7 +16459,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ74">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR74">
         <v>1.29</v>
@@ -16647,7 +16662,7 @@
         <v>1.33</v>
       </c>
       <c r="AP75">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="AQ75">
         <v>1.2</v>
@@ -16775,7 +16790,7 @@
         <v>143</v>
       </c>
       <c r="P76" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q76">
         <v>2.95</v>
@@ -16981,7 +16996,7 @@
         <v>102</v>
       </c>
       <c r="P77" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q77">
         <v>3.2</v>
@@ -17059,7 +17074,7 @@
         <v>1</v>
       </c>
       <c r="AP77">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ77">
         <v>1</v>
@@ -17187,7 +17202,7 @@
         <v>144</v>
       </c>
       <c r="P78" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q78">
         <v>3.1</v>
@@ -17393,7 +17408,7 @@
         <v>134</v>
       </c>
       <c r="P79" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q79">
         <v>2.5</v>
@@ -17474,7 +17489,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ79">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AR79">
         <v>1.53</v>
@@ -17599,7 +17614,7 @@
         <v>145</v>
       </c>
       <c r="P80" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q80">
         <v>3.4</v>
@@ -17680,7 +17695,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ80">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR80">
         <v>1.3</v>
@@ -17883,7 +17898,7 @@
         <v>0.33</v>
       </c>
       <c r="AP81">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AQ81">
         <v>0.6</v>
@@ -18092,7 +18107,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ82">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AR82">
         <v>1.28</v>
@@ -18217,7 +18232,7 @@
         <v>146</v>
       </c>
       <c r="P83" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q83">
         <v>3.6</v>
@@ -18295,7 +18310,7 @@
         <v>1.33</v>
       </c>
       <c r="AP83">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AQ83">
         <v>1.7</v>
@@ -18423,7 +18438,7 @@
         <v>102</v>
       </c>
       <c r="P84" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q84">
         <v>3.4</v>
@@ -18835,7 +18850,7 @@
         <v>147</v>
       </c>
       <c r="P86" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q86">
         <v>3.2</v>
@@ -19041,7 +19056,7 @@
         <v>148</v>
       </c>
       <c r="P87" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q87">
         <v>3.2</v>
@@ -19119,7 +19134,7 @@
         <v>2</v>
       </c>
       <c r="AP87">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ87">
         <v>2.18</v>
@@ -19247,7 +19262,7 @@
         <v>149</v>
       </c>
       <c r="P88" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q88">
         <v>3.75</v>
@@ -19328,7 +19343,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ88">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR88">
         <v>1.29</v>
@@ -19453,7 +19468,7 @@
         <v>150</v>
       </c>
       <c r="P89" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q89">
         <v>2.88</v>
@@ -19534,7 +19549,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ89">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AR89">
         <v>1.21</v>
@@ -19737,7 +19752,7 @@
         <v>1</v>
       </c>
       <c r="AP90">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ90">
         <v>0.9</v>
@@ -19865,7 +19880,7 @@
         <v>152</v>
       </c>
       <c r="P91" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q91">
         <v>3.1</v>
@@ -19943,7 +19958,7 @@
         <v>1</v>
       </c>
       <c r="AP91">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AQ91">
         <v>1</v>
@@ -20149,10 +20164,10 @@
         <v>1.25</v>
       </c>
       <c r="AP92">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="AQ92">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AR92">
         <v>1.53</v>
@@ -20355,7 +20370,7 @@
         <v>1</v>
       </c>
       <c r="AP93">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AQ93">
         <v>1</v>
@@ -20561,10 +20576,10 @@
         <v>1.6</v>
       </c>
       <c r="AP94">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ94">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR94">
         <v>1.63</v>
@@ -20973,7 +20988,7 @@
         <v>1</v>
       </c>
       <c r="AP96">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AQ96">
         <v>1.2</v>
@@ -21182,7 +21197,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ97">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR97">
         <v>1.32</v>
@@ -21388,7 +21403,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ98">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR98">
         <v>1.24</v>
@@ -21797,7 +21812,7 @@
         <v>1.75</v>
       </c>
       <c r="AP100">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ100">
         <v>1.7</v>
@@ -22006,7 +22021,7 @@
         <v>1</v>
       </c>
       <c r="AQ101">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AR101">
         <v>1.13</v>
@@ -22415,7 +22430,7 @@
         <v>1.4</v>
       </c>
       <c r="AP103">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ103">
         <v>1.36</v>
@@ -22543,7 +22558,7 @@
         <v>160</v>
       </c>
       <c r="P104" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q104">
         <v>3.9</v>
@@ -22749,7 +22764,7 @@
         <v>161</v>
       </c>
       <c r="P105" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q105">
         <v>3.25</v>
@@ -22830,7 +22845,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ105">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR105">
         <v>1.48</v>
@@ -23033,7 +23048,7 @@
         <v>0.75</v>
       </c>
       <c r="AP106">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ106">
         <v>1</v>
@@ -23367,7 +23382,7 @@
         <v>162</v>
       </c>
       <c r="P108" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q108">
         <v>3.1</v>
@@ -23445,7 +23460,7 @@
         <v>0.75</v>
       </c>
       <c r="AP108">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AQ108">
         <v>0.9</v>
@@ -24066,7 +24081,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ111">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AR111">
         <v>1.35</v>
@@ -24269,10 +24284,10 @@
         <v>0.6</v>
       </c>
       <c r="AP112">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="AQ112">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR112">
         <v>1.57</v>
@@ -24397,7 +24412,7 @@
         <v>163</v>
       </c>
       <c r="P113" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q113">
         <v>2.75</v>
@@ -24684,7 +24699,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ114">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR114">
         <v>1.23</v>
@@ -25093,7 +25108,7 @@
         <v>1.2</v>
       </c>
       <c r="AP116">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AQ116">
         <v>1</v>
@@ -25221,7 +25236,7 @@
         <v>164</v>
       </c>
       <c r="P117" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q117">
         <v>3</v>
@@ -25299,7 +25314,7 @@
         <v>0.8</v>
       </c>
       <c r="AP117">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ117">
         <v>0.6</v>
@@ -25427,7 +25442,7 @@
         <v>164</v>
       </c>
       <c r="P118" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q118">
         <v>2.88</v>
@@ -25711,10 +25726,10 @@
         <v>1</v>
       </c>
       <c r="AP119">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AQ119">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR119">
         <v>1.61</v>
@@ -25839,7 +25854,7 @@
         <v>102</v>
       </c>
       <c r="P120" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q120">
         <v>2.4</v>
@@ -26126,7 +26141,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ121">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AR121">
         <v>1.35</v>
@@ -26251,7 +26266,7 @@
         <v>166</v>
       </c>
       <c r="P122" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q122">
         <v>3.45</v>
@@ -26329,7 +26344,7 @@
         <v>1.57</v>
       </c>
       <c r="AP122">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ122">
         <v>1.09</v>
@@ -26535,7 +26550,7 @@
         <v>2</v>
       </c>
       <c r="AP123">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AQ123">
         <v>2.18</v>
@@ -27075,7 +27090,7 @@
         <v>169</v>
       </c>
       <c r="P126" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q126">
         <v>3.1</v>
@@ -27153,7 +27168,7 @@
         <v>1.2</v>
       </c>
       <c r="AP126">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ126">
         <v>1</v>
@@ -27362,7 +27377,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ127">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR127">
         <v>1.2</v>
@@ -27487,7 +27502,7 @@
         <v>102</v>
       </c>
       <c r="P128" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q128">
         <v>3.65</v>
@@ -27693,7 +27708,7 @@
         <v>102</v>
       </c>
       <c r="P129" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q129">
         <v>3.35</v>
@@ -27899,7 +27914,7 @@
         <v>170</v>
       </c>
       <c r="P130" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q130">
         <v>3</v>
@@ -27977,10 +27992,10 @@
         <v>0.8</v>
       </c>
       <c r="AP130">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ130">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AR130">
         <v>1.24</v>
@@ -28105,7 +28120,7 @@
         <v>102</v>
       </c>
       <c r="P131" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q131">
         <v>3.1</v>
@@ -28186,7 +28201,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ131">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AR131">
         <v>1.62</v>
@@ -28311,7 +28326,7 @@
         <v>119</v>
       </c>
       <c r="P132" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q132">
         <v>3.4</v>
@@ -28389,10 +28404,10 @@
         <v>0.5</v>
       </c>
       <c r="AP132">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ132">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR132">
         <v>1.56</v>
@@ -29135,7 +29150,7 @@
         <v>173</v>
       </c>
       <c r="P136" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q136">
         <v>2.5</v>
@@ -29216,7 +29231,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ136">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AR136">
         <v>1.26</v>
@@ -29341,7 +29356,7 @@
         <v>174</v>
       </c>
       <c r="P137" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q137">
         <v>2.6</v>
@@ -29419,7 +29434,7 @@
         <v>0.83</v>
       </c>
       <c r="AP137">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AQ137">
         <v>1.2</v>
@@ -29547,7 +29562,7 @@
         <v>175</v>
       </c>
       <c r="P138" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q138">
         <v>2.6</v>
@@ -29628,7 +29643,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ138">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR138">
         <v>1.4</v>
@@ -29831,7 +29846,7 @@
         <v>1</v>
       </c>
       <c r="AP139">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="AQ139">
         <v>1</v>
@@ -30165,7 +30180,7 @@
         <v>178</v>
       </c>
       <c r="P141" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -30243,7 +30258,7 @@
         <v>1.14</v>
       </c>
       <c r="AP141">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AQ141">
         <v>1</v>
@@ -30371,7 +30386,7 @@
         <v>102</v>
       </c>
       <c r="P142" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q142">
         <v>4.2</v>
@@ -30449,7 +30464,7 @@
         <v>2.14</v>
       </c>
       <c r="AP142">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ142">
         <v>2.18</v>
@@ -30577,7 +30592,7 @@
         <v>179</v>
       </c>
       <c r="P143" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q143">
         <v>2.55</v>
@@ -30658,7 +30673,7 @@
         <v>1</v>
       </c>
       <c r="AQ143">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AR143">
         <v>1.37</v>
@@ -30783,7 +30798,7 @@
         <v>102</v>
       </c>
       <c r="P144" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q144">
         <v>3.95</v>
@@ -30861,10 +30876,10 @@
         <v>1.43</v>
       </c>
       <c r="AP144">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AQ144">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR144">
         <v>1.46</v>
@@ -31067,10 +31082,10 @@
         <v>1.5</v>
       </c>
       <c r="AP145">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ145">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AR145">
         <v>1.73</v>
@@ -31195,7 +31210,7 @@
         <v>181</v>
       </c>
       <c r="P146" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q146">
         <v>3.1</v>
@@ -31276,7 +31291,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ146">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR146">
         <v>1.34</v>
@@ -31482,7 +31497,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ147">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR147">
         <v>1.21</v>
@@ -31685,7 +31700,7 @@
         <v>1.57</v>
       </c>
       <c r="AP148">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AQ148">
         <v>1.36</v>
@@ -31813,7 +31828,7 @@
         <v>183</v>
       </c>
       <c r="P149" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q149">
         <v>2.63</v>
@@ -32019,7 +32034,7 @@
         <v>184</v>
       </c>
       <c r="P150" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q150">
         <v>3.6</v>
@@ -32097,7 +32112,7 @@
         <v>0.83</v>
       </c>
       <c r="AP150">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ150">
         <v>0.5</v>
@@ -32431,7 +32446,7 @@
         <v>186</v>
       </c>
       <c r="P152" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q152">
         <v>2.95</v>
@@ -33049,7 +33064,7 @@
         <v>188</v>
       </c>
       <c r="P155" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q155">
         <v>3.7</v>
@@ -33461,7 +33476,7 @@
         <v>102</v>
       </c>
       <c r="P157" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q157">
         <v>2.9</v>
@@ -33539,7 +33554,7 @@
         <v>0.71</v>
       </c>
       <c r="AP157">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ157">
         <v>0.9</v>
@@ -33873,7 +33888,7 @@
         <v>102</v>
       </c>
       <c r="P159" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q159">
         <v>2.2</v>
@@ -34157,10 +34172,10 @@
         <v>1.13</v>
       </c>
       <c r="AP160">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="AQ160">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR160">
         <v>1.62</v>
@@ -34285,7 +34300,7 @@
         <v>191</v>
       </c>
       <c r="P161" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q161">
         <v>2.2</v>
@@ -34572,7 +34587,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ162">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AR162">
         <v>1.37</v>
@@ -34697,7 +34712,7 @@
         <v>193</v>
       </c>
       <c r="P163" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q163">
         <v>3</v>
@@ -34775,10 +34790,10 @@
         <v>0.38</v>
       </c>
       <c r="AP163">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AQ163">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AR163">
         <v>1.43</v>
@@ -34981,10 +34996,10 @@
         <v>0.63</v>
       </c>
       <c r="AP164">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ164">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR164">
         <v>1.25</v>
@@ -35109,7 +35124,7 @@
         <v>194</v>
       </c>
       <c r="P165" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q165">
         <v>4.33</v>
@@ -35187,7 +35202,7 @@
         <v>2.25</v>
       </c>
       <c r="AP165">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ165">
         <v>2.18</v>
@@ -35393,7 +35408,7 @@
         <v>1.43</v>
       </c>
       <c r="AP166">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AQ166">
         <v>1</v>
@@ -35727,7 +35742,7 @@
         <v>196</v>
       </c>
       <c r="P168" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q168">
         <v>2.4</v>
@@ -35805,10 +35820,10 @@
         <v>0.86</v>
       </c>
       <c r="AP168">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AQ168">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AR168">
         <v>1.83</v>
@@ -36011,7 +36026,7 @@
         <v>0.5</v>
       </c>
       <c r="AP169">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ169">
         <v>0.6</v>
@@ -36220,7 +36235,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ170">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR170">
         <v>1.38</v>
@@ -36345,7 +36360,7 @@
         <v>197</v>
       </c>
       <c r="P171" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q171">
         <v>3</v>
@@ -36426,7 +36441,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ171">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR171">
         <v>1.73</v>
@@ -37787,7 +37802,7 @@
         <v>201</v>
       </c>
       <c r="P178" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q178">
         <v>3.1</v>
@@ -37993,7 +38008,7 @@
         <v>102</v>
       </c>
       <c r="P179" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q179">
         <v>3.55</v>
@@ -38895,10 +38910,10 @@
         <v>1.56</v>
       </c>
       <c r="AP183">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ183">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR183">
         <v>1.3</v>
@@ -39023,7 +39038,7 @@
         <v>91</v>
       </c>
       <c r="P184" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q184">
         <v>2.3</v>
@@ -39101,10 +39116,10 @@
         <v>0.44</v>
       </c>
       <c r="AP184">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="AQ184">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AR184">
         <v>1.68</v>
@@ -39229,7 +39244,7 @@
         <v>204</v>
       </c>
       <c r="P185" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q185">
         <v>3.1</v>
@@ -39307,10 +39322,10 @@
         <v>1</v>
       </c>
       <c r="AP185">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AQ185">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR185">
         <v>1.43</v>
@@ -39513,10 +39528,10 @@
         <v>1.13</v>
       </c>
       <c r="AP186">
+        <v>1.09</v>
+      </c>
+      <c r="AQ186">
         <v>1.1</v>
-      </c>
-      <c r="AQ186">
-        <v>1.11</v>
       </c>
       <c r="AR186">
         <v>1.56</v>
@@ -39719,10 +39734,10 @@
         <v>1.56</v>
       </c>
       <c r="AP187">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AQ187">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR187">
         <v>1.56</v>
@@ -39847,7 +39862,7 @@
         <v>206</v>
       </c>
       <c r="P188" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q188">
         <v>3.25</v>
@@ -39925,10 +39940,10 @@
         <v>0.89</v>
       </c>
       <c r="AP188">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ188">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR188">
         <v>1.56</v>
@@ -40131,7 +40146,7 @@
         <v>0.75</v>
       </c>
       <c r="AP189">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ189">
         <v>0.6</v>
@@ -40337,10 +40352,10 @@
         <v>1.25</v>
       </c>
       <c r="AP190">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AQ190">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AR190">
         <v>1.89</v>
@@ -40465,7 +40480,7 @@
         <v>209</v>
       </c>
       <c r="P191" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q191">
         <v>2.75</v>
@@ -40671,7 +40686,7 @@
         <v>210</v>
       </c>
       <c r="P192" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q192">
         <v>2.4</v>
@@ -41701,7 +41716,7 @@
         <v>102</v>
       </c>
       <c r="P197" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q197">
         <v>2.5</v>
@@ -42319,7 +42334,7 @@
         <v>149</v>
       </c>
       <c r="P200" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q200">
         <v>2.63</v>
@@ -42731,7 +42746,7 @@
         <v>215</v>
       </c>
       <c r="P202" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q202">
         <v>4.33</v>
@@ -42830,16 +42845,16 @@
         <v>7</v>
       </c>
       <c r="AW202">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AX202">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AY202">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ202">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BA202">
         <v>6</v>
@@ -42888,6 +42903,1654 @@
       </c>
       <c r="BP202">
         <v>1.24</v>
+      </c>
+    </row>
+    <row r="203" spans="1:68">
+      <c r="A203" s="1">
+        <v>202</v>
+      </c>
+      <c r="B203">
+        <v>7509783</v>
+      </c>
+      <c r="C203" t="s">
+        <v>68</v>
+      </c>
+      <c r="D203" t="s">
+        <v>69</v>
+      </c>
+      <c r="E203" s="2">
+        <v>45669.45833333334</v>
+      </c>
+      <c r="F203">
+        <v>21</v>
+      </c>
+      <c r="G203" t="s">
+        <v>77</v>
+      </c>
+      <c r="H203" t="s">
+        <v>71</v>
+      </c>
+      <c r="I203">
+        <v>0</v>
+      </c>
+      <c r="J203">
+        <v>0</v>
+      </c>
+      <c r="K203">
+        <v>0</v>
+      </c>
+      <c r="L203">
+        <v>0</v>
+      </c>
+      <c r="M203">
+        <v>0</v>
+      </c>
+      <c r="N203">
+        <v>0</v>
+      </c>
+      <c r="O203" t="s">
+        <v>102</v>
+      </c>
+      <c r="P203" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q203">
+        <v>3.2</v>
+      </c>
+      <c r="R203">
+        <v>2</v>
+      </c>
+      <c r="S203">
+        <v>3.75</v>
+      </c>
+      <c r="T203">
+        <v>1.5</v>
+      </c>
+      <c r="U203">
+        <v>2.5</v>
+      </c>
+      <c r="V203">
+        <v>3.4</v>
+      </c>
+      <c r="W203">
+        <v>1.3</v>
+      </c>
+      <c r="X203">
+        <v>10</v>
+      </c>
+      <c r="Y203">
+        <v>1.06</v>
+      </c>
+      <c r="Z203">
+        <v>2.4</v>
+      </c>
+      <c r="AA203">
+        <v>2.65</v>
+      </c>
+      <c r="AB203">
+        <v>3.1</v>
+      </c>
+      <c r="AC203">
+        <v>1.09</v>
+      </c>
+      <c r="AD203">
+        <v>7</v>
+      </c>
+      <c r="AE203">
+        <v>1.4</v>
+      </c>
+      <c r="AF203">
+        <v>2.8</v>
+      </c>
+      <c r="AG203">
+        <v>2.35</v>
+      </c>
+      <c r="AH203">
+        <v>1.53</v>
+      </c>
+      <c r="AI203">
+        <v>1.91</v>
+      </c>
+      <c r="AJ203">
+        <v>1.91</v>
+      </c>
+      <c r="AK203">
+        <v>1.36</v>
+      </c>
+      <c r="AL203">
+        <v>1.35</v>
+      </c>
+      <c r="AM203">
+        <v>1.55</v>
+      </c>
+      <c r="AN203">
+        <v>1.2</v>
+      </c>
+      <c r="AO203">
+        <v>1.11</v>
+      </c>
+      <c r="AP203">
+        <v>1.18</v>
+      </c>
+      <c r="AQ203">
+        <v>1.1</v>
+      </c>
+      <c r="AR203">
+        <v>1.37</v>
+      </c>
+      <c r="AS203">
+        <v>1.27</v>
+      </c>
+      <c r="AT203">
+        <v>2.64</v>
+      </c>
+      <c r="AU203">
+        <v>4</v>
+      </c>
+      <c r="AV203">
+        <v>2</v>
+      </c>
+      <c r="AW203">
+        <v>4</v>
+      </c>
+      <c r="AX203">
+        <v>7</v>
+      </c>
+      <c r="AY203">
+        <v>11</v>
+      </c>
+      <c r="AZ203">
+        <v>12</v>
+      </c>
+      <c r="BA203">
+        <v>3</v>
+      </c>
+      <c r="BB203">
+        <v>5</v>
+      </c>
+      <c r="BC203">
+        <v>8</v>
+      </c>
+      <c r="BD203">
+        <v>1.84</v>
+      </c>
+      <c r="BE203">
+        <v>6.1</v>
+      </c>
+      <c r="BF203">
+        <v>2.2</v>
+      </c>
+      <c r="BG203">
+        <v>1.5</v>
+      </c>
+      <c r="BH203">
+        <v>2.35</v>
+      </c>
+      <c r="BI203">
+        <v>1.85</v>
+      </c>
+      <c r="BJ203">
+        <v>1.83</v>
+      </c>
+      <c r="BK203">
+        <v>2.35</v>
+      </c>
+      <c r="BL203">
+        <v>1.5</v>
+      </c>
+      <c r="BM203">
+        <v>3.05</v>
+      </c>
+      <c r="BN203">
+        <v>1.3</v>
+      </c>
+      <c r="BO203">
+        <v>4.1</v>
+      </c>
+      <c r="BP203">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="204" spans="1:68">
+      <c r="A204" s="1">
+        <v>203</v>
+      </c>
+      <c r="B204">
+        <v>7509785</v>
+      </c>
+      <c r="C204" t="s">
+        <v>68</v>
+      </c>
+      <c r="D204" t="s">
+        <v>69</v>
+      </c>
+      <c r="E204" s="2">
+        <v>45669.45833333334</v>
+      </c>
+      <c r="F204">
+        <v>21</v>
+      </c>
+      <c r="G204" t="s">
+        <v>83</v>
+      </c>
+      <c r="H204" t="s">
+        <v>88</v>
+      </c>
+      <c r="I204">
+        <v>1</v>
+      </c>
+      <c r="J204">
+        <v>0</v>
+      </c>
+      <c r="K204">
+        <v>1</v>
+      </c>
+      <c r="L204">
+        <v>1</v>
+      </c>
+      <c r="M204">
+        <v>1</v>
+      </c>
+      <c r="N204">
+        <v>2</v>
+      </c>
+      <c r="O204" t="s">
+        <v>197</v>
+      </c>
+      <c r="P204" t="s">
+        <v>241</v>
+      </c>
+      <c r="Q204">
+        <v>2.5</v>
+      </c>
+      <c r="R204">
+        <v>2</v>
+      </c>
+      <c r="S204">
+        <v>5.5</v>
+      </c>
+      <c r="T204">
+        <v>1.5</v>
+      </c>
+      <c r="U204">
+        <v>2.5</v>
+      </c>
+      <c r="V204">
+        <v>3.5</v>
+      </c>
+      <c r="W204">
+        <v>1.29</v>
+      </c>
+      <c r="X204">
+        <v>11</v>
+      </c>
+      <c r="Y204">
+        <v>1.05</v>
+      </c>
+      <c r="Z204">
+        <v>1.73</v>
+      </c>
+      <c r="AA204">
+        <v>3.15</v>
+      </c>
+      <c r="AB204">
+        <v>4.5</v>
+      </c>
+      <c r="AC204">
+        <v>1.09</v>
+      </c>
+      <c r="AD204">
+        <v>7</v>
+      </c>
+      <c r="AE204">
+        <v>1.44</v>
+      </c>
+      <c r="AF204">
+        <v>2.7</v>
+      </c>
+      <c r="AG204">
+        <v>2.3</v>
+      </c>
+      <c r="AH204">
+        <v>1.55</v>
+      </c>
+      <c r="AI204">
+        <v>2.1</v>
+      </c>
+      <c r="AJ204">
+        <v>1.67</v>
+      </c>
+      <c r="AK204">
+        <v>1.19</v>
+      </c>
+      <c r="AL204">
+        <v>1.31</v>
+      </c>
+      <c r="AM204">
+        <v>1.93</v>
+      </c>
+      <c r="AN204">
+        <v>2.56</v>
+      </c>
+      <c r="AO204">
+        <v>1.4</v>
+      </c>
+      <c r="AP204">
+        <v>2.4</v>
+      </c>
+      <c r="AQ204">
+        <v>1.36</v>
+      </c>
+      <c r="AR204">
+        <v>1.74</v>
+      </c>
+      <c r="AS204">
+        <v>1.09</v>
+      </c>
+      <c r="AT204">
+        <v>2.83</v>
+      </c>
+      <c r="AU204">
+        <v>6</v>
+      </c>
+      <c r="AV204">
+        <v>3</v>
+      </c>
+      <c r="AW204">
+        <v>6</v>
+      </c>
+      <c r="AX204">
+        <v>1</v>
+      </c>
+      <c r="AY204">
+        <v>16</v>
+      </c>
+      <c r="AZ204">
+        <v>5</v>
+      </c>
+      <c r="BA204">
+        <v>7</v>
+      </c>
+      <c r="BB204">
+        <v>2</v>
+      </c>
+      <c r="BC204">
+        <v>9</v>
+      </c>
+      <c r="BD204">
+        <v>1.49</v>
+      </c>
+      <c r="BE204">
+        <v>6.75</v>
+      </c>
+      <c r="BF204">
+        <v>2.9</v>
+      </c>
+      <c r="BG204">
+        <v>1.43</v>
+      </c>
+      <c r="BH204">
+        <v>2.6</v>
+      </c>
+      <c r="BI204">
+        <v>1.72</v>
+      </c>
+      <c r="BJ204">
+        <v>1.98</v>
+      </c>
+      <c r="BK204">
+        <v>2.12</v>
+      </c>
+      <c r="BL204">
+        <v>1.63</v>
+      </c>
+      <c r="BM204">
+        <v>2.7</v>
+      </c>
+      <c r="BN204">
+        <v>1.38</v>
+      </c>
+      <c r="BO204">
+        <v>3.65</v>
+      </c>
+      <c r="BP204">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="205" spans="1:68">
+      <c r="A205" s="1">
+        <v>204</v>
+      </c>
+      <c r="B205">
+        <v>7509781</v>
+      </c>
+      <c r="C205" t="s">
+        <v>68</v>
+      </c>
+      <c r="D205" t="s">
+        <v>69</v>
+      </c>
+      <c r="E205" s="2">
+        <v>45669.45833333334</v>
+      </c>
+      <c r="F205">
+        <v>21</v>
+      </c>
+      <c r="G205" t="s">
+        <v>89</v>
+      </c>
+      <c r="H205" t="s">
+        <v>80</v>
+      </c>
+      <c r="I205">
+        <v>1</v>
+      </c>
+      <c r="J205">
+        <v>0</v>
+      </c>
+      <c r="K205">
+        <v>1</v>
+      </c>
+      <c r="L205">
+        <v>2</v>
+      </c>
+      <c r="M205">
+        <v>0</v>
+      </c>
+      <c r="N205">
+        <v>2</v>
+      </c>
+      <c r="O205" t="s">
+        <v>216</v>
+      </c>
+      <c r="P205" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q205">
+        <v>2.75</v>
+      </c>
+      <c r="R205">
+        <v>2.05</v>
+      </c>
+      <c r="S205">
+        <v>4.5</v>
+      </c>
+      <c r="T205">
+        <v>1.5</v>
+      </c>
+      <c r="U205">
+        <v>2.5</v>
+      </c>
+      <c r="V205">
+        <v>3.4</v>
+      </c>
+      <c r="W205">
+        <v>1.3</v>
+      </c>
+      <c r="X205">
+        <v>10</v>
+      </c>
+      <c r="Y205">
+        <v>1.06</v>
+      </c>
+      <c r="Z205">
+        <v>1.95</v>
+      </c>
+      <c r="AA205">
+        <v>2.95</v>
+      </c>
+      <c r="AB205">
+        <v>3.75</v>
+      </c>
+      <c r="AC205">
+        <v>1.09</v>
+      </c>
+      <c r="AD205">
+        <v>7</v>
+      </c>
+      <c r="AE205">
+        <v>1.42</v>
+      </c>
+      <c r="AF205">
+        <v>2.75</v>
+      </c>
+      <c r="AG205">
+        <v>2.25</v>
+      </c>
+      <c r="AH205">
+        <v>1.57</v>
+      </c>
+      <c r="AI205">
+        <v>1.95</v>
+      </c>
+      <c r="AJ205">
+        <v>1.8</v>
+      </c>
+      <c r="AK205">
+        <v>1.26</v>
+      </c>
+      <c r="AL205">
+        <v>1.33</v>
+      </c>
+      <c r="AM205">
+        <v>1.72</v>
+      </c>
+      <c r="AN205">
+        <v>1.33</v>
+      </c>
+      <c r="AO205">
+        <v>0.9</v>
+      </c>
+      <c r="AP205">
+        <v>1.5</v>
+      </c>
+      <c r="AQ205">
+        <v>0.82</v>
+      </c>
+      <c r="AR205">
+        <v>1.88</v>
+      </c>
+      <c r="AS205">
+        <v>1.17</v>
+      </c>
+      <c r="AT205">
+        <v>3.05</v>
+      </c>
+      <c r="AU205">
+        <v>7</v>
+      </c>
+      <c r="AV205">
+        <v>2</v>
+      </c>
+      <c r="AW205">
+        <v>5</v>
+      </c>
+      <c r="AX205">
+        <v>9</v>
+      </c>
+      <c r="AY205">
+        <v>16</v>
+      </c>
+      <c r="AZ205">
+        <v>18</v>
+      </c>
+      <c r="BA205">
+        <v>9</v>
+      </c>
+      <c r="BB205">
+        <v>8</v>
+      </c>
+      <c r="BC205">
+        <v>17</v>
+      </c>
+      <c r="BD205">
+        <v>1.67</v>
+      </c>
+      <c r="BE205">
+        <v>6.5</v>
+      </c>
+      <c r="BF205">
+        <v>2.5</v>
+      </c>
+      <c r="BG205">
+        <v>1.32</v>
+      </c>
+      <c r="BH205">
+        <v>3.05</v>
+      </c>
+      <c r="BI205">
+        <v>1.56</v>
+      </c>
+      <c r="BJ205">
+        <v>2.23</v>
+      </c>
+      <c r="BK205">
+        <v>1.92</v>
+      </c>
+      <c r="BL205">
+        <v>1.77</v>
+      </c>
+      <c r="BM205">
+        <v>2.4</v>
+      </c>
+      <c r="BN205">
+        <v>1.49</v>
+      </c>
+      <c r="BO205">
+        <v>3.15</v>
+      </c>
+      <c r="BP205">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="206" spans="1:68">
+      <c r="A206" s="1">
+        <v>205</v>
+      </c>
+      <c r="B206">
+        <v>7509786</v>
+      </c>
+      <c r="C206" t="s">
+        <v>68</v>
+      </c>
+      <c r="D206" t="s">
+        <v>69</v>
+      </c>
+      <c r="E206" s="2">
+        <v>45669.45833333334</v>
+      </c>
+      <c r="F206">
+        <v>21</v>
+      </c>
+      <c r="G206" t="s">
+        <v>72</v>
+      </c>
+      <c r="H206" t="s">
+        <v>78</v>
+      </c>
+      <c r="I206">
+        <v>1</v>
+      </c>
+      <c r="J206">
+        <v>1</v>
+      </c>
+      <c r="K206">
+        <v>2</v>
+      </c>
+      <c r="L206">
+        <v>1</v>
+      </c>
+      <c r="M206">
+        <v>1</v>
+      </c>
+      <c r="N206">
+        <v>2</v>
+      </c>
+      <c r="O206" t="s">
+        <v>217</v>
+      </c>
+      <c r="P206" t="s">
+        <v>302</v>
+      </c>
+      <c r="Q206">
+        <v>3.4</v>
+      </c>
+      <c r="R206">
+        <v>1.95</v>
+      </c>
+      <c r="S206">
+        <v>3.75</v>
+      </c>
+      <c r="T206">
+        <v>1.53</v>
+      </c>
+      <c r="U206">
+        <v>2.38</v>
+      </c>
+      <c r="V206">
+        <v>3.75</v>
+      </c>
+      <c r="W206">
+        <v>1.25</v>
+      </c>
+      <c r="X206">
+        <v>11</v>
+      </c>
+      <c r="Y206">
+        <v>1.05</v>
+      </c>
+      <c r="Z206">
+        <v>2.4</v>
+      </c>
+      <c r="AA206">
+        <v>2.85</v>
+      </c>
+      <c r="AB206">
+        <v>2.85</v>
+      </c>
+      <c r="AC206">
+        <v>1.1</v>
+      </c>
+      <c r="AD206">
+        <v>6.5</v>
+      </c>
+      <c r="AE206">
+        <v>1.45</v>
+      </c>
+      <c r="AF206">
+        <v>2.6</v>
+      </c>
+      <c r="AG206">
+        <v>2.35</v>
+      </c>
+      <c r="AH206">
+        <v>1.53</v>
+      </c>
+      <c r="AI206">
+        <v>2.05</v>
+      </c>
+      <c r="AJ206">
+        <v>1.7</v>
+      </c>
+      <c r="AK206">
+        <v>1.38</v>
+      </c>
+      <c r="AL206">
+        <v>1.36</v>
+      </c>
+      <c r="AM206">
+        <v>1.5</v>
+      </c>
+      <c r="AN206">
+        <v>0.8</v>
+      </c>
+      <c r="AO206">
+        <v>1.11</v>
+      </c>
+      <c r="AP206">
+        <v>0.82</v>
+      </c>
+      <c r="AQ206">
+        <v>1.1</v>
+      </c>
+      <c r="AR206">
+        <v>1.39</v>
+      </c>
+      <c r="AS206">
+        <v>1.2</v>
+      </c>
+      <c r="AT206">
+        <v>2.59</v>
+      </c>
+      <c r="AU206">
+        <v>8</v>
+      </c>
+      <c r="AV206">
+        <v>4</v>
+      </c>
+      <c r="AW206">
+        <v>5</v>
+      </c>
+      <c r="AX206">
+        <v>7</v>
+      </c>
+      <c r="AY206">
+        <v>21</v>
+      </c>
+      <c r="AZ206">
+        <v>12</v>
+      </c>
+      <c r="BA206">
+        <v>7</v>
+      </c>
+      <c r="BB206">
+        <v>2</v>
+      </c>
+      <c r="BC206">
+        <v>9</v>
+      </c>
+      <c r="BD206">
+        <v>1.86</v>
+      </c>
+      <c r="BE206">
+        <v>6.1</v>
+      </c>
+      <c r="BF206">
+        <v>2.17</v>
+      </c>
+      <c r="BG206">
+        <v>1.55</v>
+      </c>
+      <c r="BH206">
+        <v>2.28</v>
+      </c>
+      <c r="BI206">
+        <v>1.93</v>
+      </c>
+      <c r="BJ206">
+        <v>1.77</v>
+      </c>
+      <c r="BK206">
+        <v>2.48</v>
+      </c>
+      <c r="BL206">
+        <v>1.47</v>
+      </c>
+      <c r="BM206">
+        <v>3.25</v>
+      </c>
+      <c r="BN206">
+        <v>1.28</v>
+      </c>
+      <c r="BO206">
+        <v>4.35</v>
+      </c>
+      <c r="BP206">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="207" spans="1:68">
+      <c r="A207" s="1">
+        <v>206</v>
+      </c>
+      <c r="B207">
+        <v>7509779</v>
+      </c>
+      <c r="C207" t="s">
+        <v>68</v>
+      </c>
+      <c r="D207" t="s">
+        <v>69</v>
+      </c>
+      <c r="E207" s="2">
+        <v>45669.45833333334</v>
+      </c>
+      <c r="F207">
+        <v>21</v>
+      </c>
+      <c r="G207" t="s">
+        <v>79</v>
+      </c>
+      <c r="H207" t="s">
+        <v>85</v>
+      </c>
+      <c r="I207">
+        <v>2</v>
+      </c>
+      <c r="J207">
+        <v>1</v>
+      </c>
+      <c r="K207">
+        <v>3</v>
+      </c>
+      <c r="L207">
+        <v>2</v>
+      </c>
+      <c r="M207">
+        <v>2</v>
+      </c>
+      <c r="N207">
+        <v>4</v>
+      </c>
+      <c r="O207" t="s">
+        <v>218</v>
+      </c>
+      <c r="P207" t="s">
+        <v>303</v>
+      </c>
+      <c r="Q207">
+        <v>2.75</v>
+      </c>
+      <c r="R207">
+        <v>2.05</v>
+      </c>
+      <c r="S207">
+        <v>4.33</v>
+      </c>
+      <c r="T207">
+        <v>1.44</v>
+      </c>
+      <c r="U207">
+        <v>2.63</v>
+      </c>
+      <c r="V207">
+        <v>3.25</v>
+      </c>
+      <c r="W207">
+        <v>1.33</v>
+      </c>
+      <c r="X207">
+        <v>10</v>
+      </c>
+      <c r="Y207">
+        <v>1.06</v>
+      </c>
+      <c r="Z207">
+        <v>1.95</v>
+      </c>
+      <c r="AA207">
+        <v>3.1</v>
+      </c>
+      <c r="AB207">
+        <v>3.6</v>
+      </c>
+      <c r="AC207">
+        <v>1.07</v>
+      </c>
+      <c r="AD207">
+        <v>8</v>
+      </c>
+      <c r="AE207">
+        <v>1.33</v>
+      </c>
+      <c r="AF207">
+        <v>3.1</v>
+      </c>
+      <c r="AG207">
+        <v>2</v>
+      </c>
+      <c r="AH207">
+        <v>1.7</v>
+      </c>
+      <c r="AI207">
+        <v>1.91</v>
+      </c>
+      <c r="AJ207">
+        <v>1.91</v>
+      </c>
+      <c r="AK207">
+        <v>1.26</v>
+      </c>
+      <c r="AL207">
+        <v>1.32</v>
+      </c>
+      <c r="AM207">
+        <v>1.73</v>
+      </c>
+      <c r="AN207">
+        <v>1.1</v>
+      </c>
+      <c r="AO207">
+        <v>0.5</v>
+      </c>
+      <c r="AP207">
+        <v>1.09</v>
+      </c>
+      <c r="AQ207">
+        <v>0.55</v>
+      </c>
+      <c r="AR207">
+        <v>1.56</v>
+      </c>
+      <c r="AS207">
+        <v>1.07</v>
+      </c>
+      <c r="AT207">
+        <v>2.63</v>
+      </c>
+      <c r="AU207">
+        <v>5</v>
+      </c>
+      <c r="AV207">
+        <v>6</v>
+      </c>
+      <c r="AW207">
+        <v>3</v>
+      </c>
+      <c r="AX207">
+        <v>3</v>
+      </c>
+      <c r="AY207">
+        <v>11</v>
+      </c>
+      <c r="AZ207">
+        <v>14</v>
+      </c>
+      <c r="BA207">
+        <v>3</v>
+      </c>
+      <c r="BB207">
+        <v>4</v>
+      </c>
+      <c r="BC207">
+        <v>7</v>
+      </c>
+      <c r="BD207">
+        <v>1.66</v>
+      </c>
+      <c r="BE207">
+        <v>6.4</v>
+      </c>
+      <c r="BF207">
+        <v>2.5</v>
+      </c>
+      <c r="BG207">
+        <v>1.48</v>
+      </c>
+      <c r="BH207">
+        <v>2.45</v>
+      </c>
+      <c r="BI207">
+        <v>1.79</v>
+      </c>
+      <c r="BJ207">
+        <v>1.9</v>
+      </c>
+      <c r="BK207">
+        <v>2.28</v>
+      </c>
+      <c r="BL207">
+        <v>1.55</v>
+      </c>
+      <c r="BM207">
+        <v>2.9</v>
+      </c>
+      <c r="BN207">
+        <v>1.34</v>
+      </c>
+      <c r="BO207">
+        <v>3.95</v>
+      </c>
+      <c r="BP207">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="208" spans="1:68">
+      <c r="A208" s="1">
+        <v>207</v>
+      </c>
+      <c r="B208">
+        <v>7509780</v>
+      </c>
+      <c r="C208" t="s">
+        <v>68</v>
+      </c>
+      <c r="D208" t="s">
+        <v>69</v>
+      </c>
+      <c r="E208" s="2">
+        <v>45669.45833333334</v>
+      </c>
+      <c r="F208">
+        <v>21</v>
+      </c>
+      <c r="G208" t="s">
+        <v>75</v>
+      </c>
+      <c r="H208" t="s">
+        <v>82</v>
+      </c>
+      <c r="I208">
+        <v>0</v>
+      </c>
+      <c r="J208">
+        <v>2</v>
+      </c>
+      <c r="K208">
+        <v>2</v>
+      </c>
+      <c r="L208">
+        <v>0</v>
+      </c>
+      <c r="M208">
+        <v>3</v>
+      </c>
+      <c r="N208">
+        <v>3</v>
+      </c>
+      <c r="O208" t="s">
+        <v>102</v>
+      </c>
+      <c r="P208" t="s">
+        <v>304</v>
+      </c>
+      <c r="Q208">
+        <v>4</v>
+      </c>
+      <c r="R208">
+        <v>2</v>
+      </c>
+      <c r="S208">
+        <v>3</v>
+      </c>
+      <c r="T208">
+        <v>1.5</v>
+      </c>
+      <c r="U208">
+        <v>2.5</v>
+      </c>
+      <c r="V208">
+        <v>3.4</v>
+      </c>
+      <c r="W208">
+        <v>1.3</v>
+      </c>
+      <c r="X208">
+        <v>10</v>
+      </c>
+      <c r="Y208">
+        <v>1.06</v>
+      </c>
+      <c r="Z208">
+        <v>3.2</v>
+      </c>
+      <c r="AA208">
+        <v>2.95</v>
+      </c>
+      <c r="AB208">
+        <v>2.15</v>
+      </c>
+      <c r="AC208">
+        <v>1.08</v>
+      </c>
+      <c r="AD208">
+        <v>7.5</v>
+      </c>
+      <c r="AE208">
+        <v>1.4</v>
+      </c>
+      <c r="AF208">
+        <v>2.8</v>
+      </c>
+      <c r="AG208">
+        <v>2.2</v>
+      </c>
+      <c r="AH208">
+        <v>1.6</v>
+      </c>
+      <c r="AI208">
+        <v>1.95</v>
+      </c>
+      <c r="AJ208">
+        <v>1.8</v>
+      </c>
+      <c r="AK208">
+        <v>1.61</v>
+      </c>
+      <c r="AL208">
+        <v>1.34</v>
+      </c>
+      <c r="AM208">
+        <v>1.32</v>
+      </c>
+      <c r="AN208">
+        <v>1.1</v>
+      </c>
+      <c r="AO208">
+        <v>1.7</v>
+      </c>
+      <c r="AP208">
+        <v>1</v>
+      </c>
+      <c r="AQ208">
+        <v>1.82</v>
+      </c>
+      <c r="AR208">
+        <v>1.42</v>
+      </c>
+      <c r="AS208">
+        <v>1.36</v>
+      </c>
+      <c r="AT208">
+        <v>2.78</v>
+      </c>
+      <c r="AU208">
+        <v>4</v>
+      </c>
+      <c r="AV208">
+        <v>6</v>
+      </c>
+      <c r="AW208">
+        <v>4</v>
+      </c>
+      <c r="AX208">
+        <v>7</v>
+      </c>
+      <c r="AY208">
+        <v>10</v>
+      </c>
+      <c r="AZ208">
+        <v>14</v>
+      </c>
+      <c r="BA208">
+        <v>2</v>
+      </c>
+      <c r="BB208">
+        <v>4</v>
+      </c>
+      <c r="BC208">
+        <v>6</v>
+      </c>
+      <c r="BD208">
+        <v>2.32</v>
+      </c>
+      <c r="BE208">
+        <v>6.4</v>
+      </c>
+      <c r="BF208">
+        <v>1.75</v>
+      </c>
+      <c r="BG208">
+        <v>1.33</v>
+      </c>
+      <c r="BH208">
+        <v>2.95</v>
+      </c>
+      <c r="BI208">
+        <v>1.56</v>
+      </c>
+      <c r="BJ208">
+        <v>2.23</v>
+      </c>
+      <c r="BK208">
+        <v>1.92</v>
+      </c>
+      <c r="BL208">
+        <v>1.77</v>
+      </c>
+      <c r="BM208">
+        <v>2.4</v>
+      </c>
+      <c r="BN208">
+        <v>1.49</v>
+      </c>
+      <c r="BO208">
+        <v>3.15</v>
+      </c>
+      <c r="BP208">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="209" spans="1:68">
+      <c r="A209" s="1">
+        <v>208</v>
+      </c>
+      <c r="B209">
+        <v>7509778</v>
+      </c>
+      <c r="C209" t="s">
+        <v>68</v>
+      </c>
+      <c r="D209" t="s">
+        <v>69</v>
+      </c>
+      <c r="E209" s="2">
+        <v>45669.55208333334</v>
+      </c>
+      <c r="F209">
+        <v>21</v>
+      </c>
+      <c r="G209" t="s">
+        <v>76</v>
+      </c>
+      <c r="H209" t="s">
+        <v>87</v>
+      </c>
+      <c r="I209">
+        <v>0</v>
+      </c>
+      <c r="J209">
+        <v>0</v>
+      </c>
+      <c r="K209">
+        <v>0</v>
+      </c>
+      <c r="L209">
+        <v>0</v>
+      </c>
+      <c r="M209">
+        <v>0</v>
+      </c>
+      <c r="N209">
+        <v>0</v>
+      </c>
+      <c r="O209" t="s">
+        <v>102</v>
+      </c>
+      <c r="P209" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q209">
+        <v>2.75</v>
+      </c>
+      <c r="R209">
+        <v>2.05</v>
+      </c>
+      <c r="S209">
+        <v>4.5</v>
+      </c>
+      <c r="T209">
+        <v>1.5</v>
+      </c>
+      <c r="U209">
+        <v>2.5</v>
+      </c>
+      <c r="V209">
+        <v>3.4</v>
+      </c>
+      <c r="W209">
+        <v>1.3</v>
+      </c>
+      <c r="X209">
+        <v>10</v>
+      </c>
+      <c r="Y209">
+        <v>1.06</v>
+      </c>
+      <c r="Z209">
+        <v>1.87</v>
+      </c>
+      <c r="AA209">
+        <v>3</v>
+      </c>
+      <c r="AB209">
+        <v>4.4</v>
+      </c>
+      <c r="AC209">
+        <v>1.08</v>
+      </c>
+      <c r="AD209">
+        <v>7.5</v>
+      </c>
+      <c r="AE209">
+        <v>1.38</v>
+      </c>
+      <c r="AF209">
+        <v>2.9</v>
+      </c>
+      <c r="AG209">
+        <v>2.05</v>
+      </c>
+      <c r="AH209">
+        <v>1.61</v>
+      </c>
+      <c r="AI209">
+        <v>1.95</v>
+      </c>
+      <c r="AJ209">
+        <v>1.8</v>
+      </c>
+      <c r="AK209">
+        <v>1.23</v>
+      </c>
+      <c r="AL209">
+        <v>1.34</v>
+      </c>
+      <c r="AM209">
+        <v>1.77</v>
+      </c>
+      <c r="AN209">
+        <v>2</v>
+      </c>
+      <c r="AO209">
+        <v>1.2</v>
+      </c>
+      <c r="AP209">
+        <v>1.91</v>
+      </c>
+      <c r="AQ209">
+        <v>1.18</v>
+      </c>
+      <c r="AR209">
+        <v>1.52</v>
+      </c>
+      <c r="AS209">
+        <v>1.23</v>
+      </c>
+      <c r="AT209">
+        <v>2.75</v>
+      </c>
+      <c r="AU209">
+        <v>3</v>
+      </c>
+      <c r="AV209">
+        <v>4</v>
+      </c>
+      <c r="AW209">
+        <v>8</v>
+      </c>
+      <c r="AX209">
+        <v>5</v>
+      </c>
+      <c r="AY209">
+        <v>11</v>
+      </c>
+      <c r="AZ209">
+        <v>10</v>
+      </c>
+      <c r="BA209">
+        <v>5</v>
+      </c>
+      <c r="BB209">
+        <v>2</v>
+      </c>
+      <c r="BC209">
+        <v>7</v>
+      </c>
+      <c r="BD209">
+        <v>1.61</v>
+      </c>
+      <c r="BE209">
+        <v>6.4</v>
+      </c>
+      <c r="BF209">
+        <v>2.55</v>
+      </c>
+      <c r="BG209">
+        <v>1.49</v>
+      </c>
+      <c r="BH209">
+        <v>2.4</v>
+      </c>
+      <c r="BI209">
+        <v>1.81</v>
+      </c>
+      <c r="BJ209">
+        <v>1.88</v>
+      </c>
+      <c r="BK209">
+        <v>2.3</v>
+      </c>
+      <c r="BL209">
+        <v>1.53</v>
+      </c>
+      <c r="BM209">
+        <v>3.05</v>
+      </c>
+      <c r="BN209">
+        <v>1.32</v>
+      </c>
+      <c r="BO209">
+        <v>4.1</v>
+      </c>
+      <c r="BP209">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="210" spans="1:68">
+      <c r="A210" s="1">
+        <v>209</v>
+      </c>
+      <c r="B210">
+        <v>7509777</v>
+      </c>
+      <c r="C210" t="s">
+        <v>68</v>
+      </c>
+      <c r="D210" t="s">
+        <v>69</v>
+      </c>
+      <c r="E210" s="2">
+        <v>45669.64583333334</v>
+      </c>
+      <c r="F210">
+        <v>21</v>
+      </c>
+      <c r="G210" t="s">
+        <v>70</v>
+      </c>
+      <c r="H210" t="s">
+        <v>81</v>
+      </c>
+      <c r="I210">
+        <v>0</v>
+      </c>
+      <c r="J210">
+        <v>1</v>
+      </c>
+      <c r="K210">
+        <v>1</v>
+      </c>
+      <c r="L210">
+        <v>1</v>
+      </c>
+      <c r="M210">
+        <v>1</v>
+      </c>
+      <c r="N210">
+        <v>2</v>
+      </c>
+      <c r="O210" t="s">
+        <v>139</v>
+      </c>
+      <c r="P210" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q210">
+        <v>3.4</v>
+      </c>
+      <c r="R210">
+        <v>2.05</v>
+      </c>
+      <c r="S210">
+        <v>3.4</v>
+      </c>
+      <c r="T210">
+        <v>1.44</v>
+      </c>
+      <c r="U210">
+        <v>2.63</v>
+      </c>
+      <c r="V210">
+        <v>3.25</v>
+      </c>
+      <c r="W210">
+        <v>1.33</v>
+      </c>
+      <c r="X210">
+        <v>10</v>
+      </c>
+      <c r="Y210">
+        <v>1.06</v>
+      </c>
+      <c r="Z210">
+        <v>2.5</v>
+      </c>
+      <c r="AA210">
+        <v>3.1</v>
+      </c>
+      <c r="AB210">
+        <v>2.62</v>
+      </c>
+      <c r="AC210">
+        <v>1.07</v>
+      </c>
+      <c r="AD210">
+        <v>8</v>
+      </c>
+      <c r="AE210">
+        <v>1.36</v>
+      </c>
+      <c r="AF210">
+        <v>3</v>
+      </c>
+      <c r="AG210">
+        <v>2.05</v>
+      </c>
+      <c r="AH210">
+        <v>1.65</v>
+      </c>
+      <c r="AI210">
+        <v>1.91</v>
+      </c>
+      <c r="AJ210">
+        <v>1.91</v>
+      </c>
+      <c r="AK210">
+        <v>1.43</v>
+      </c>
+      <c r="AL210">
+        <v>1.33</v>
+      </c>
+      <c r="AM210">
+        <v>1.47</v>
+      </c>
+      <c r="AN210">
+        <v>1.3</v>
+      </c>
+      <c r="AO210">
+        <v>1</v>
+      </c>
+      <c r="AP210">
+        <v>1.27</v>
+      </c>
+      <c r="AQ210">
+        <v>1</v>
+      </c>
+      <c r="AR210">
+        <v>1.56</v>
+      </c>
+      <c r="AS210">
+        <v>1.15</v>
+      </c>
+      <c r="AT210">
+        <v>2.71</v>
+      </c>
+      <c r="AU210">
+        <v>7</v>
+      </c>
+      <c r="AV210">
+        <v>6</v>
+      </c>
+      <c r="AW210">
+        <v>15</v>
+      </c>
+      <c r="AX210">
+        <v>9</v>
+      </c>
+      <c r="AY210">
+        <v>25</v>
+      </c>
+      <c r="AZ210">
+        <v>20</v>
+      </c>
+      <c r="BA210">
+        <v>5</v>
+      </c>
+      <c r="BB210">
+        <v>5</v>
+      </c>
+      <c r="BC210">
+        <v>10</v>
+      </c>
+      <c r="BD210">
+        <v>2.02</v>
+      </c>
+      <c r="BE210">
+        <v>6.25</v>
+      </c>
+      <c r="BF210">
+        <v>1.98</v>
+      </c>
+      <c r="BG210">
+        <v>1.46</v>
+      </c>
+      <c r="BH210">
+        <v>2.5</v>
+      </c>
+      <c r="BI210">
+        <v>1.76</v>
+      </c>
+      <c r="BJ210">
+        <v>1.94</v>
+      </c>
+      <c r="BK210">
+        <v>2.18</v>
+      </c>
+      <c r="BL210">
+        <v>1.58</v>
+      </c>
+      <c r="BM210">
+        <v>2.9</v>
+      </c>
+      <c r="BN210">
+        <v>1.35</v>
+      </c>
+      <c r="BO210">
+        <v>3.9</v>
+      </c>
+      <c r="BP210">
+        <v>1.21</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Italy Serie B_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Italy Serie B_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1322" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1328" uniqueCount="306">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -673,6 +673,9 @@
     <t>['10', '23']</t>
   </si>
   <si>
+    <t>['22', '87']</t>
+  </si>
+  <si>
     <t>['24', '45+2', '80']</t>
   </si>
   <si>
@@ -1290,7 +1293,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP210"/>
+  <dimension ref="A1:BP211"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1752,7 +1755,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q3">
         <v>2.63</v>
@@ -1958,7 +1961,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q4">
         <v>3.5</v>
@@ -2164,7 +2167,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q5">
         <v>3.2</v>
@@ -2242,7 +2245,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ5">
         <v>1.36</v>
@@ -2576,7 +2579,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q7">
         <v>3.25</v>
@@ -2863,7 +2866,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ8">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2988,7 +2991,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q9">
         <v>3.4</v>
@@ -3194,7 +3197,7 @@
         <v>98</v>
       </c>
       <c r="P10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q10">
         <v>3.75</v>
@@ -3606,7 +3609,7 @@
         <v>100</v>
       </c>
       <c r="P12" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q12">
         <v>3.25</v>
@@ -3812,7 +3815,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q13">
         <v>3.4</v>
@@ -4018,7 +4021,7 @@
         <v>102</v>
       </c>
       <c r="P14" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q14">
         <v>2.3</v>
@@ -4511,7 +4514,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ16">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4636,7 +4639,7 @@
         <v>104</v>
       </c>
       <c r="P17" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q17">
         <v>2.88</v>
@@ -4920,7 +4923,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ18">
         <v>1.09</v>
@@ -5254,7 +5257,7 @@
         <v>107</v>
       </c>
       <c r="P20" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q20">
         <v>2.88</v>
@@ -5666,7 +5669,7 @@
         <v>91</v>
       </c>
       <c r="P22" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q22">
         <v>3.4</v>
@@ -6078,7 +6081,7 @@
         <v>109</v>
       </c>
       <c r="P24" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q24">
         <v>2.98</v>
@@ -6696,7 +6699,7 @@
         <v>102</v>
       </c>
       <c r="P27" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q27">
         <v>2.74</v>
@@ -7932,7 +7935,7 @@
         <v>102</v>
       </c>
       <c r="P33" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q33">
         <v>2.8</v>
@@ -8216,7 +8219,7 @@
         <v>3</v>
       </c>
       <c r="AP34">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ34">
         <v>1.2</v>
@@ -8344,7 +8347,7 @@
         <v>116</v>
       </c>
       <c r="P35" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q35">
         <v>3</v>
@@ -8550,7 +8553,7 @@
         <v>117</v>
       </c>
       <c r="P36" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q36">
         <v>2.9</v>
@@ -9168,7 +9171,7 @@
         <v>119</v>
       </c>
       <c r="P39" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q39">
         <v>2.63</v>
@@ -9374,7 +9377,7 @@
         <v>120</v>
       </c>
       <c r="P40" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q40">
         <v>3.2</v>
@@ -9580,7 +9583,7 @@
         <v>121</v>
       </c>
       <c r="P41" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q41">
         <v>2.63</v>
@@ -9661,7 +9664,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ41">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR41">
         <v>1.16</v>
@@ -9786,7 +9789,7 @@
         <v>122</v>
       </c>
       <c r="P42" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q42">
         <v>2.88</v>
@@ -10610,7 +10613,7 @@
         <v>125</v>
       </c>
       <c r="P46" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q46">
         <v>3.75</v>
@@ -11022,7 +11025,7 @@
         <v>116</v>
       </c>
       <c r="P48" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q48">
         <v>3.4</v>
@@ -11228,7 +11231,7 @@
         <v>102</v>
       </c>
       <c r="P49" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q49">
         <v>3.75</v>
@@ -11434,7 +11437,7 @@
         <v>127</v>
       </c>
       <c r="P50" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q50">
         <v>3.4</v>
@@ -11640,7 +11643,7 @@
         <v>128</v>
       </c>
       <c r="P51" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q51">
         <v>3.1</v>
@@ -11846,7 +11849,7 @@
         <v>129</v>
       </c>
       <c r="P52" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q52">
         <v>3.79</v>
@@ -12464,7 +12467,7 @@
         <v>130</v>
       </c>
       <c r="P55" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q55">
         <v>2.5</v>
@@ -12542,7 +12545,7 @@
         <v>1.5</v>
       </c>
       <c r="AP55">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ55">
         <v>1</v>
@@ -13288,7 +13291,7 @@
         <v>102</v>
       </c>
       <c r="P59" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q59">
         <v>3.1</v>
@@ -13700,7 +13703,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q61">
         <v>2.38</v>
@@ -13781,7 +13784,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ61">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR61">
         <v>1.42</v>
@@ -13906,7 +13909,7 @@
         <v>134</v>
       </c>
       <c r="P62" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q62">
         <v>3.25</v>
@@ -14318,7 +14321,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q64">
         <v>2.9</v>
@@ -14730,7 +14733,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q66">
         <v>2.4</v>
@@ -15142,7 +15145,7 @@
         <v>138</v>
       </c>
       <c r="P68" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q68">
         <v>3.1</v>
@@ -15554,7 +15557,7 @@
         <v>139</v>
       </c>
       <c r="P70" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q70">
         <v>3.5</v>
@@ -15760,7 +15763,7 @@
         <v>140</v>
       </c>
       <c r="P71" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q71">
         <v>3.5</v>
@@ -15966,7 +15969,7 @@
         <v>141</v>
       </c>
       <c r="P72" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q72">
         <v>2.4</v>
@@ -16172,7 +16175,7 @@
         <v>102</v>
       </c>
       <c r="P73" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q73">
         <v>2.5</v>
@@ -16253,7 +16256,7 @@
         <v>1</v>
       </c>
       <c r="AQ73">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR73">
         <v>1.51</v>
@@ -16378,7 +16381,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q74">
         <v>2.5</v>
@@ -16790,7 +16793,7 @@
         <v>143</v>
       </c>
       <c r="P76" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q76">
         <v>2.95</v>
@@ -16868,7 +16871,7 @@
         <v>0.33</v>
       </c>
       <c r="AP76">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ76">
         <v>0.5</v>
@@ -16996,7 +16999,7 @@
         <v>102</v>
       </c>
       <c r="P77" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q77">
         <v>3.2</v>
@@ -17202,7 +17205,7 @@
         <v>144</v>
       </c>
       <c r="P78" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q78">
         <v>3.1</v>
@@ -17408,7 +17411,7 @@
         <v>134</v>
       </c>
       <c r="P79" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q79">
         <v>2.5</v>
@@ -17614,7 +17617,7 @@
         <v>145</v>
       </c>
       <c r="P80" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q80">
         <v>3.4</v>
@@ -18232,7 +18235,7 @@
         <v>146</v>
       </c>
       <c r="P83" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q83">
         <v>3.6</v>
@@ -18438,7 +18441,7 @@
         <v>102</v>
       </c>
       <c r="P84" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q84">
         <v>3.4</v>
@@ -18850,7 +18853,7 @@
         <v>147</v>
       </c>
       <c r="P86" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q86">
         <v>3.2</v>
@@ -19056,7 +19059,7 @@
         <v>148</v>
       </c>
       <c r="P87" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q87">
         <v>3.2</v>
@@ -19262,7 +19265,7 @@
         <v>149</v>
       </c>
       <c r="P88" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q88">
         <v>3.75</v>
@@ -19468,7 +19471,7 @@
         <v>150</v>
       </c>
       <c r="P89" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q89">
         <v>2.88</v>
@@ -19880,7 +19883,7 @@
         <v>152</v>
       </c>
       <c r="P91" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q91">
         <v>3.1</v>
@@ -22227,7 +22230,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ102">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR102">
         <v>1.3</v>
@@ -22558,7 +22561,7 @@
         <v>160</v>
       </c>
       <c r="P104" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q104">
         <v>3.9</v>
@@ -22764,7 +22767,7 @@
         <v>161</v>
       </c>
       <c r="P105" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q105">
         <v>3.25</v>
@@ -23382,7 +23385,7 @@
         <v>162</v>
       </c>
       <c r="P108" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q108">
         <v>3.1</v>
@@ -24078,7 +24081,7 @@
         <v>0.75</v>
       </c>
       <c r="AP111">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ111">
         <v>1.1</v>
@@ -24412,7 +24415,7 @@
         <v>163</v>
       </c>
       <c r="P113" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q113">
         <v>2.75</v>
@@ -25236,7 +25239,7 @@
         <v>164</v>
       </c>
       <c r="P117" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q117">
         <v>3</v>
@@ -25442,7 +25445,7 @@
         <v>164</v>
       </c>
       <c r="P118" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q118">
         <v>2.88</v>
@@ -25854,7 +25857,7 @@
         <v>102</v>
       </c>
       <c r="P120" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q120">
         <v>2.4</v>
@@ -26266,7 +26269,7 @@
         <v>166</v>
       </c>
       <c r="P122" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q122">
         <v>3.45</v>
@@ -26756,7 +26759,7 @@
         <v>1.33</v>
       </c>
       <c r="AP124">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ124">
         <v>1</v>
@@ -26965,7 +26968,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ125">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR125">
         <v>1.55</v>
@@ -27090,7 +27093,7 @@
         <v>169</v>
       </c>
       <c r="P126" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q126">
         <v>3.1</v>
@@ -27502,7 +27505,7 @@
         <v>102</v>
       </c>
       <c r="P128" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q128">
         <v>3.65</v>
@@ -27708,7 +27711,7 @@
         <v>102</v>
       </c>
       <c r="P129" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q129">
         <v>3.35</v>
@@ -27914,7 +27917,7 @@
         <v>170</v>
       </c>
       <c r="P130" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q130">
         <v>3</v>
@@ -28120,7 +28123,7 @@
         <v>102</v>
       </c>
       <c r="P131" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q131">
         <v>3.1</v>
@@ -28326,7 +28329,7 @@
         <v>119</v>
       </c>
       <c r="P132" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q132">
         <v>3.4</v>
@@ -29150,7 +29153,7 @@
         <v>173</v>
       </c>
       <c r="P136" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q136">
         <v>2.5</v>
@@ -29356,7 +29359,7 @@
         <v>174</v>
       </c>
       <c r="P137" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q137">
         <v>2.6</v>
@@ -29562,7 +29565,7 @@
         <v>175</v>
       </c>
       <c r="P138" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q138">
         <v>2.6</v>
@@ -30180,7 +30183,7 @@
         <v>178</v>
       </c>
       <c r="P141" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -30386,7 +30389,7 @@
         <v>102</v>
       </c>
       <c r="P142" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q142">
         <v>4.2</v>
@@ -30592,7 +30595,7 @@
         <v>179</v>
       </c>
       <c r="P143" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q143">
         <v>2.55</v>
@@ -30798,7 +30801,7 @@
         <v>102</v>
       </c>
       <c r="P144" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q144">
         <v>3.95</v>
@@ -31210,7 +31213,7 @@
         <v>181</v>
       </c>
       <c r="P146" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q146">
         <v>3.1</v>
@@ -31828,7 +31831,7 @@
         <v>183</v>
       </c>
       <c r="P149" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q149">
         <v>2.63</v>
@@ -31906,7 +31909,7 @@
         <v>1.5</v>
       </c>
       <c r="AP149">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ149">
         <v>1</v>
@@ -32034,7 +32037,7 @@
         <v>184</v>
       </c>
       <c r="P150" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q150">
         <v>3.6</v>
@@ -32321,7 +32324,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ151">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR151">
         <v>1.67</v>
@@ -32446,7 +32449,7 @@
         <v>186</v>
       </c>
       <c r="P152" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q152">
         <v>2.95</v>
@@ -33064,7 +33067,7 @@
         <v>188</v>
       </c>
       <c r="P155" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q155">
         <v>3.7</v>
@@ -33476,7 +33479,7 @@
         <v>102</v>
       </c>
       <c r="P157" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q157">
         <v>2.9</v>
@@ -33888,7 +33891,7 @@
         <v>102</v>
       </c>
       <c r="P159" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q159">
         <v>2.2</v>
@@ -34300,7 +34303,7 @@
         <v>191</v>
       </c>
       <c r="P161" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q161">
         <v>2.2</v>
@@ -34584,7 +34587,7 @@
         <v>1.43</v>
       </c>
       <c r="AP162">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ162">
         <v>1.1</v>
@@ -34712,7 +34715,7 @@
         <v>193</v>
       </c>
       <c r="P163" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q163">
         <v>3</v>
@@ -35124,7 +35127,7 @@
         <v>194</v>
       </c>
       <c r="P165" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q165">
         <v>4.33</v>
@@ -35742,7 +35745,7 @@
         <v>196</v>
       </c>
       <c r="P168" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q168">
         <v>2.4</v>
@@ -36029,7 +36032,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ169">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR169">
         <v>1.68</v>
@@ -36360,7 +36363,7 @@
         <v>197</v>
       </c>
       <c r="P171" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q171">
         <v>3</v>
@@ -37802,7 +37805,7 @@
         <v>201</v>
       </c>
       <c r="P178" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q178">
         <v>3.1</v>
@@ -38008,7 +38011,7 @@
         <v>102</v>
       </c>
       <c r="P179" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q179">
         <v>3.55</v>
@@ -38704,7 +38707,7 @@
         <v>2.33</v>
       </c>
       <c r="AP182">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ182">
         <v>2.18</v>
@@ -39038,7 +39041,7 @@
         <v>91</v>
       </c>
       <c r="P184" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q184">
         <v>2.3</v>
@@ -39244,7 +39247,7 @@
         <v>204</v>
       </c>
       <c r="P185" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q185">
         <v>3.1</v>
@@ -39862,7 +39865,7 @@
         <v>206</v>
       </c>
       <c r="P188" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q188">
         <v>3.25</v>
@@ -40480,7 +40483,7 @@
         <v>209</v>
       </c>
       <c r="P191" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q191">
         <v>2.75</v>
@@ -40561,7 +40564,7 @@
         <v>1</v>
       </c>
       <c r="AQ191">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR191">
         <v>1.37</v>
@@ -40686,7 +40689,7 @@
         <v>210</v>
       </c>
       <c r="P192" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q192">
         <v>2.4</v>
@@ -41716,7 +41719,7 @@
         <v>102</v>
       </c>
       <c r="P197" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q197">
         <v>2.5</v>
@@ -42334,7 +42337,7 @@
         <v>149</v>
       </c>
       <c r="P200" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q200">
         <v>2.63</v>
@@ -42746,7 +42749,7 @@
         <v>215</v>
       </c>
       <c r="P202" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q202">
         <v>4.33</v>
@@ -43158,7 +43161,7 @@
         <v>197</v>
       </c>
       <c r="P204" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q204">
         <v>2.5</v>
@@ -43570,7 +43573,7 @@
         <v>217</v>
       </c>
       <c r="P206" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q206">
         <v>3.4</v>
@@ -43776,7 +43779,7 @@
         <v>218</v>
       </c>
       <c r="P207" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q207">
         <v>2.75</v>
@@ -43982,7 +43985,7 @@
         <v>102</v>
       </c>
       <c r="P208" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q208">
         <v>4</v>
@@ -44551,6 +44554,212 @@
       </c>
       <c r="BP210">
         <v>1.21</v>
+      </c>
+    </row>
+    <row r="211" spans="1:68">
+      <c r="A211" s="1">
+        <v>210</v>
+      </c>
+      <c r="B211">
+        <v>7509782</v>
+      </c>
+      <c r="C211" t="s">
+        <v>68</v>
+      </c>
+      <c r="D211" t="s">
+        <v>69</v>
+      </c>
+      <c r="E211" s="2">
+        <v>45670.6875</v>
+      </c>
+      <c r="F211">
+        <v>21</v>
+      </c>
+      <c r="G211" t="s">
+        <v>73</v>
+      </c>
+      <c r="H211" t="s">
+        <v>86</v>
+      </c>
+      <c r="I211">
+        <v>1</v>
+      </c>
+      <c r="J211">
+        <v>0</v>
+      </c>
+      <c r="K211">
+        <v>1</v>
+      </c>
+      <c r="L211">
+        <v>2</v>
+      </c>
+      <c r="M211">
+        <v>1</v>
+      </c>
+      <c r="N211">
+        <v>3</v>
+      </c>
+      <c r="O211" t="s">
+        <v>219</v>
+      </c>
+      <c r="P211" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q211">
+        <v>2.5</v>
+      </c>
+      <c r="R211">
+        <v>2.05</v>
+      </c>
+      <c r="S211">
+        <v>5</v>
+      </c>
+      <c r="T211">
+        <v>1.5</v>
+      </c>
+      <c r="U211">
+        <v>2.5</v>
+      </c>
+      <c r="V211">
+        <v>3.4</v>
+      </c>
+      <c r="W211">
+        <v>1.3</v>
+      </c>
+      <c r="X211">
+        <v>10</v>
+      </c>
+      <c r="Y211">
+        <v>1.06</v>
+      </c>
+      <c r="Z211">
+        <v>1.93</v>
+      </c>
+      <c r="AA211">
+        <v>3.32</v>
+      </c>
+      <c r="AB211">
+        <v>4.29</v>
+      </c>
+      <c r="AC211">
+        <v>1.04</v>
+      </c>
+      <c r="AD211">
+        <v>6.8</v>
+      </c>
+      <c r="AE211">
+        <v>1.4</v>
+      </c>
+      <c r="AF211">
+        <v>2.8</v>
+      </c>
+      <c r="AG211">
+        <v>2.2</v>
+      </c>
+      <c r="AH211">
+        <v>1.65</v>
+      </c>
+      <c r="AI211">
+        <v>2.05</v>
+      </c>
+      <c r="AJ211">
+        <v>1.7</v>
+      </c>
+      <c r="AK211">
+        <v>1.2</v>
+      </c>
+      <c r="AL211">
+        <v>1.31</v>
+      </c>
+      <c r="AM211">
+        <v>1.9</v>
+      </c>
+      <c r="AN211">
+        <v>2.4</v>
+      </c>
+      <c r="AO211">
+        <v>0.6</v>
+      </c>
+      <c r="AP211">
+        <v>2.45</v>
+      </c>
+      <c r="AQ211">
+        <v>0.55</v>
+      </c>
+      <c r="AR211">
+        <v>1.37</v>
+      </c>
+      <c r="AS211">
+        <v>1.11</v>
+      </c>
+      <c r="AT211">
+        <v>2.48</v>
+      </c>
+      <c r="AU211">
+        <v>6</v>
+      </c>
+      <c r="AV211">
+        <v>8</v>
+      </c>
+      <c r="AW211">
+        <v>15</v>
+      </c>
+      <c r="AX211">
+        <v>4</v>
+      </c>
+      <c r="AY211">
+        <v>23</v>
+      </c>
+      <c r="AZ211">
+        <v>13</v>
+      </c>
+      <c r="BA211">
+        <v>8</v>
+      </c>
+      <c r="BB211">
+        <v>6</v>
+      </c>
+      <c r="BC211">
+        <v>14</v>
+      </c>
+      <c r="BD211">
+        <v>1.55</v>
+      </c>
+      <c r="BE211">
+        <v>6.4</v>
+      </c>
+      <c r="BF211">
+        <v>2.7</v>
+      </c>
+      <c r="BG211">
+        <v>1.4</v>
+      </c>
+      <c r="BH211">
+        <v>2.65</v>
+      </c>
+      <c r="BI211">
+        <v>1.68</v>
+      </c>
+      <c r="BJ211">
+        <v>2.05</v>
+      </c>
+      <c r="BK211">
+        <v>2.08</v>
+      </c>
+      <c r="BL211">
+        <v>1.66</v>
+      </c>
+      <c r="BM211">
+        <v>2.65</v>
+      </c>
+      <c r="BN211">
+        <v>1.41</v>
+      </c>
+      <c r="BO211">
+        <v>3.55</v>
+      </c>
+      <c r="BP211">
+        <v>1.24</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Italy Serie B_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Italy Serie B_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1328" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1364" uniqueCount="314">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -676,6 +676,18 @@
     <t>['22', '87']</t>
   </si>
   <si>
+    <t>['76', '90+10']</t>
+  </si>
+  <si>
+    <t>['23', '85', '90+3']</t>
+  </si>
+  <si>
+    <t>['42']</t>
+  </si>
+  <si>
+    <t>['1', '41']</t>
+  </si>
+  <si>
     <t>['24', '45+2', '80']</t>
   </si>
   <si>
@@ -932,6 +944,18 @@
   </si>
   <si>
     <t>['24', '45+4', '59']</t>
+  </si>
+  <si>
+    <t>['31', '62']</t>
+  </si>
+  <si>
+    <t>['62']</t>
+  </si>
+  <si>
+    <t>['34', '52']</t>
+  </si>
+  <si>
+    <t>['30', '65']</t>
   </si>
 </sst>
 </file>
@@ -1293,7 +1317,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP211"/>
+  <dimension ref="A1:BP217"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1755,7 +1779,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="Q3">
         <v>2.63</v>
@@ -1833,7 +1857,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ3">
         <v>1.36</v>
@@ -1961,7 +1985,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="Q4">
         <v>3.5</v>
@@ -2167,7 +2191,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="Q5">
         <v>3.2</v>
@@ -2451,7 +2475,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ6">
         <v>1.18</v>
@@ -2579,7 +2603,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="Q7">
         <v>3.25</v>
@@ -2991,7 +3015,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="Q9">
         <v>3.4</v>
@@ -3072,7 +3096,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ9">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3197,7 +3221,7 @@
         <v>98</v>
       </c>
       <c r="P10" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="Q10">
         <v>3.75</v>
@@ -3609,7 +3633,7 @@
         <v>100</v>
       </c>
       <c r="P12" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="Q12">
         <v>3.25</v>
@@ -3687,7 +3711,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ12">
         <v>1.1</v>
@@ -3815,7 +3839,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="Q13">
         <v>3.4</v>
@@ -4021,7 +4045,7 @@
         <v>102</v>
       </c>
       <c r="P14" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="Q14">
         <v>2.3</v>
@@ -4099,10 +4123,10 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ14">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4511,7 +4535,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ16">
         <v>0.55</v>
@@ -4639,7 +4663,7 @@
         <v>104</v>
       </c>
       <c r="P17" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="Q17">
         <v>2.88</v>
@@ -4720,7 +4744,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ17">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -5132,7 +5156,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ19">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5257,7 +5281,7 @@
         <v>107</v>
       </c>
       <c r="P20" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="Q20">
         <v>2.88</v>
@@ -5338,7 +5362,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ20">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR20">
         <v>0</v>
@@ -5669,7 +5693,7 @@
         <v>91</v>
       </c>
       <c r="P22" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="Q22">
         <v>3.4</v>
@@ -5747,7 +5771,7 @@
         <v>1</v>
       </c>
       <c r="AP22">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ22">
         <v>2.18</v>
@@ -6081,7 +6105,7 @@
         <v>109</v>
       </c>
       <c r="P24" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="Q24">
         <v>2.98</v>
@@ -6159,7 +6183,7 @@
         <v>1</v>
       </c>
       <c r="AP24">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ24">
         <v>1</v>
@@ -6365,7 +6389,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ25">
         <v>1.7</v>
@@ -6699,7 +6723,7 @@
         <v>102</v>
       </c>
       <c r="P27" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="Q27">
         <v>2.74</v>
@@ -6777,7 +6801,7 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ27">
         <v>1.09</v>
@@ -7604,7 +7628,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ31">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AR31">
         <v>0</v>
@@ -7807,7 +7831,7 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ32">
         <v>1.1</v>
@@ -7935,7 +7959,7 @@
         <v>102</v>
       </c>
       <c r="P33" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="Q33">
         <v>2.8</v>
@@ -8013,7 +8037,7 @@
         <v>1.5</v>
       </c>
       <c r="AP33">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ33">
         <v>1.18</v>
@@ -8222,7 +8246,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ34">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR34">
         <v>1.4</v>
@@ -8347,7 +8371,7 @@
         <v>116</v>
       </c>
       <c r="P35" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="Q35">
         <v>3</v>
@@ -8553,7 +8577,7 @@
         <v>117</v>
       </c>
       <c r="P36" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="Q36">
         <v>2.9</v>
@@ -9171,7 +9195,7 @@
         <v>119</v>
       </c>
       <c r="P39" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="Q39">
         <v>2.63</v>
@@ -9252,7 +9276,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ39">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR39">
         <v>0</v>
@@ -9377,7 +9401,7 @@
         <v>120</v>
       </c>
       <c r="P40" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="Q40">
         <v>3.2</v>
@@ -9458,7 +9482,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ40">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR40">
         <v>1.5</v>
@@ -9583,7 +9607,7 @@
         <v>121</v>
       </c>
       <c r="P41" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="Q41">
         <v>2.63</v>
@@ -9789,7 +9813,7 @@
         <v>122</v>
       </c>
       <c r="P42" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="Q42">
         <v>2.88</v>
@@ -10073,7 +10097,7 @@
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ43">
         <v>1.1</v>
@@ -10279,10 +10303,10 @@
         <v>0.5</v>
       </c>
       <c r="AP44">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ44">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AR44">
         <v>1.6</v>
@@ -10488,7 +10512,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ45">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR45">
         <v>1.98</v>
@@ -10613,7 +10637,7 @@
         <v>125</v>
       </c>
       <c r="P46" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="Q46">
         <v>3.75</v>
@@ -10897,7 +10921,7 @@
         <v>1</v>
       </c>
       <c r="AP47">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ47">
         <v>1.36</v>
@@ -11025,7 +11049,7 @@
         <v>116</v>
       </c>
       <c r="P48" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="Q48">
         <v>3.4</v>
@@ -11231,7 +11255,7 @@
         <v>102</v>
       </c>
       <c r="P49" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="Q49">
         <v>3.75</v>
@@ -11437,7 +11461,7 @@
         <v>127</v>
       </c>
       <c r="P50" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="Q50">
         <v>3.4</v>
@@ -11643,7 +11667,7 @@
         <v>128</v>
       </c>
       <c r="P51" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="Q51">
         <v>3.1</v>
@@ -11721,7 +11745,7 @@
         <v>1</v>
       </c>
       <c r="AP51">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ51">
         <v>1.7</v>
@@ -11849,7 +11873,7 @@
         <v>129</v>
       </c>
       <c r="P52" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="Q52">
         <v>3.79</v>
@@ -12342,7 +12366,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ54">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR54">
         <v>2.1</v>
@@ -12467,7 +12491,7 @@
         <v>130</v>
       </c>
       <c r="P55" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="Q55">
         <v>2.5</v>
@@ -12957,7 +12981,7 @@
         <v>1.5</v>
       </c>
       <c r="AP57">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ57">
         <v>1</v>
@@ -13163,7 +13187,7 @@
         <v>1.67</v>
       </c>
       <c r="AP58">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ58">
         <v>1.36</v>
@@ -13291,7 +13315,7 @@
         <v>102</v>
       </c>
       <c r="P59" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="Q59">
         <v>3.1</v>
@@ -13703,7 +13727,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="Q61">
         <v>2.38</v>
@@ -13909,7 +13933,7 @@
         <v>134</v>
       </c>
       <c r="P62" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="Q62">
         <v>3.25</v>
@@ -13987,10 +14011,10 @@
         <v>0</v>
       </c>
       <c r="AP62">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ62">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR62">
         <v>1.33</v>
@@ -14321,7 +14345,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="Q64">
         <v>2.9</v>
@@ -14399,10 +14423,10 @@
         <v>0.5</v>
       </c>
       <c r="AP64">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ64">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR64">
         <v>1.44</v>
@@ -14608,7 +14632,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ65">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR65">
         <v>1.09</v>
@@ -14733,7 +14757,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="Q66">
         <v>2.4</v>
@@ -14814,7 +14838,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ66">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AR66">
         <v>1.61</v>
@@ -15145,7 +15169,7 @@
         <v>138</v>
       </c>
       <c r="P68" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="Q68">
         <v>3.1</v>
@@ -15223,7 +15247,7 @@
         <v>0.33</v>
       </c>
       <c r="AP68">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ68">
         <v>1</v>
@@ -15429,7 +15453,7 @@
         <v>0.5</v>
       </c>
       <c r="AP69">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ69">
         <v>1.1</v>
@@ -15557,7 +15581,7 @@
         <v>139</v>
       </c>
       <c r="P70" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="Q70">
         <v>3.5</v>
@@ -15763,7 +15787,7 @@
         <v>140</v>
       </c>
       <c r="P71" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="Q71">
         <v>3.5</v>
@@ -15969,7 +15993,7 @@
         <v>141</v>
       </c>
       <c r="P72" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="Q72">
         <v>2.4</v>
@@ -16047,7 +16071,7 @@
         <v>1.25</v>
       </c>
       <c r="AP72">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ72">
         <v>1.36</v>
@@ -16175,7 +16199,7 @@
         <v>102</v>
       </c>
       <c r="P73" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="Q73">
         <v>2.5</v>
@@ -16381,7 +16405,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="Q74">
         <v>2.5</v>
@@ -16668,7 +16692,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ75">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR75">
         <v>1.77</v>
@@ -16793,7 +16817,7 @@
         <v>143</v>
       </c>
       <c r="P76" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="Q76">
         <v>2.95</v>
@@ -16874,7 +16898,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ76">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR76">
         <v>1.44</v>
@@ -16999,7 +17023,7 @@
         <v>102</v>
       </c>
       <c r="P77" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="Q77">
         <v>3.2</v>
@@ -17205,7 +17229,7 @@
         <v>144</v>
       </c>
       <c r="P78" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="Q78">
         <v>3.1</v>
@@ -17411,7 +17435,7 @@
         <v>134</v>
       </c>
       <c r="P79" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="Q79">
         <v>2.5</v>
@@ -17489,7 +17513,7 @@
         <v>1.33</v>
       </c>
       <c r="AP79">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ79">
         <v>1.1</v>
@@ -17617,7 +17641,7 @@
         <v>145</v>
       </c>
       <c r="P80" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="Q80">
         <v>3.4</v>
@@ -18107,7 +18131,7 @@
         <v>0.67</v>
       </c>
       <c r="AP82">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ82">
         <v>1.1</v>
@@ -18235,7 +18259,7 @@
         <v>146</v>
       </c>
       <c r="P83" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="Q83">
         <v>3.6</v>
@@ -18441,7 +18465,7 @@
         <v>102</v>
       </c>
       <c r="P84" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="Q84">
         <v>3.4</v>
@@ -18519,7 +18543,7 @@
         <v>1</v>
       </c>
       <c r="AP84">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ84">
         <v>1.36</v>
@@ -18725,10 +18749,10 @@
         <v>0.67</v>
       </c>
       <c r="AP85">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ85">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR85">
         <v>1.41</v>
@@ -18853,7 +18877,7 @@
         <v>147</v>
       </c>
       <c r="P86" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="Q86">
         <v>3.2</v>
@@ -18931,7 +18955,7 @@
         <v>1.8</v>
       </c>
       <c r="AP86">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ86">
         <v>1.09</v>
@@ -19059,7 +19083,7 @@
         <v>148</v>
       </c>
       <c r="P87" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="Q87">
         <v>3.2</v>
@@ -19265,7 +19289,7 @@
         <v>149</v>
       </c>
       <c r="P88" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="Q88">
         <v>3.75</v>
@@ -19471,7 +19495,7 @@
         <v>150</v>
       </c>
       <c r="P89" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="Q89">
         <v>2.88</v>
@@ -19552,7 +19576,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ89">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AR89">
         <v>1.21</v>
@@ -19758,7 +19782,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ90">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR90">
         <v>1.38</v>
@@ -19883,7 +19907,7 @@
         <v>152</v>
       </c>
       <c r="P91" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="Q91">
         <v>3.1</v>
@@ -20785,7 +20809,7 @@
         <v>1</v>
       </c>
       <c r="AP95">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ95">
         <v>0.6</v>
@@ -20994,7 +21018,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ96">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR96">
         <v>1.62</v>
@@ -22021,10 +22045,10 @@
         <v>0.4</v>
       </c>
       <c r="AP101">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ101">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AR101">
         <v>1.13</v>
@@ -22227,7 +22251,7 @@
         <v>0.6</v>
       </c>
       <c r="AP102">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ102">
         <v>0.55</v>
@@ -22561,7 +22585,7 @@
         <v>160</v>
       </c>
       <c r="P104" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="Q104">
         <v>3.9</v>
@@ -22767,7 +22791,7 @@
         <v>161</v>
       </c>
       <c r="P105" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="Q105">
         <v>3.25</v>
@@ -22845,7 +22869,7 @@
         <v>1.8</v>
       </c>
       <c r="AP105">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ105">
         <v>1.82</v>
@@ -23054,7 +23078,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ106">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR106">
         <v>1.29</v>
@@ -23257,10 +23281,10 @@
         <v>0.25</v>
       </c>
       <c r="AP107">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ107">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR107">
         <v>1.73</v>
@@ -23385,7 +23409,7 @@
         <v>162</v>
       </c>
       <c r="P108" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q108">
         <v>3.1</v>
@@ -23466,7 +23490,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ108">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR108">
         <v>1.52</v>
@@ -23669,7 +23693,7 @@
         <v>1.4</v>
       </c>
       <c r="AP109">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ109">
         <v>1</v>
@@ -24415,7 +24439,7 @@
         <v>163</v>
       </c>
       <c r="P113" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="Q113">
         <v>2.75</v>
@@ -24493,10 +24517,10 @@
         <v>0.8</v>
       </c>
       <c r="AP113">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ113">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR113">
         <v>1.36</v>
@@ -24908,7 +24932,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ115">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR115">
         <v>1.26</v>
@@ -25239,7 +25263,7 @@
         <v>164</v>
       </c>
       <c r="P117" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="Q117">
         <v>3</v>
@@ -25445,7 +25469,7 @@
         <v>164</v>
       </c>
       <c r="P118" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="Q118">
         <v>2.88</v>
@@ -25523,7 +25547,7 @@
         <v>1.6</v>
       </c>
       <c r="AP118">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ118">
         <v>1.7</v>
@@ -25857,7 +25881,7 @@
         <v>102</v>
       </c>
       <c r="P120" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="Q120">
         <v>2.4</v>
@@ -25935,7 +25959,7 @@
         <v>0.8</v>
       </c>
       <c r="AP120">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ120">
         <v>1</v>
@@ -26144,7 +26168,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ121">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AR121">
         <v>1.35</v>
@@ -26269,7 +26293,7 @@
         <v>166</v>
       </c>
       <c r="P122" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="Q122">
         <v>3.45</v>
@@ -26965,7 +26989,7 @@
         <v>0.67</v>
       </c>
       <c r="AP125">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ125">
         <v>0.55</v>
@@ -27093,7 +27117,7 @@
         <v>169</v>
       </c>
       <c r="P126" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="Q126">
         <v>3.1</v>
@@ -27174,7 +27198,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ126">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR126">
         <v>1.73</v>
@@ -27505,7 +27529,7 @@
         <v>102</v>
       </c>
       <c r="P128" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="Q128">
         <v>3.65</v>
@@ -27711,7 +27735,7 @@
         <v>102</v>
       </c>
       <c r="P129" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="Q129">
         <v>3.35</v>
@@ -27789,10 +27813,10 @@
         <v>0.4</v>
       </c>
       <c r="AP129">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ129">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR129">
         <v>1.41</v>
@@ -27917,7 +27941,7 @@
         <v>170</v>
       </c>
       <c r="P130" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="Q130">
         <v>3</v>
@@ -28123,7 +28147,7 @@
         <v>102</v>
       </c>
       <c r="P131" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="Q131">
         <v>3.1</v>
@@ -28201,7 +28225,7 @@
         <v>1.2</v>
       </c>
       <c r="AP131">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ131">
         <v>1.1</v>
@@ -28329,7 +28353,7 @@
         <v>119</v>
       </c>
       <c r="P132" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="Q132">
         <v>3.4</v>
@@ -29153,7 +29177,7 @@
         <v>173</v>
       </c>
       <c r="P136" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="Q136">
         <v>2.5</v>
@@ -29234,7 +29258,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ136">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AR136">
         <v>1.26</v>
@@ -29359,7 +29383,7 @@
         <v>174</v>
       </c>
       <c r="P137" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q137">
         <v>2.6</v>
@@ -29440,7 +29464,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ137">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR137">
         <v>1.49</v>
@@ -29565,7 +29589,7 @@
         <v>175</v>
       </c>
       <c r="P138" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="Q138">
         <v>2.6</v>
@@ -29643,7 +29667,7 @@
         <v>1.29</v>
       </c>
       <c r="AP138">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ138">
         <v>1.18</v>
@@ -30055,10 +30079,10 @@
         <v>0.83</v>
       </c>
       <c r="AP140">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ140">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR140">
         <v>1.37</v>
@@ -30183,7 +30207,7 @@
         <v>178</v>
       </c>
       <c r="P141" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -30389,7 +30413,7 @@
         <v>102</v>
       </c>
       <c r="P142" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="Q142">
         <v>4.2</v>
@@ -30595,7 +30619,7 @@
         <v>179</v>
       </c>
       <c r="P143" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="Q143">
         <v>2.55</v>
@@ -30673,7 +30697,7 @@
         <v>0.83</v>
       </c>
       <c r="AP143">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ143">
         <v>1.1</v>
@@ -30801,7 +30825,7 @@
         <v>102</v>
       </c>
       <c r="P144" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="Q144">
         <v>3.95</v>
@@ -31213,7 +31237,7 @@
         <v>181</v>
       </c>
       <c r="P146" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="Q146">
         <v>3.1</v>
@@ -31291,7 +31315,7 @@
         <v>1.43</v>
       </c>
       <c r="AP146">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ146">
         <v>1.36</v>
@@ -31831,7 +31855,7 @@
         <v>183</v>
       </c>
       <c r="P149" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="Q149">
         <v>2.63</v>
@@ -31912,7 +31936,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ149">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR149">
         <v>1.34</v>
@@ -32037,7 +32061,7 @@
         <v>184</v>
       </c>
       <c r="P150" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="Q150">
         <v>3.6</v>
@@ -32118,7 +32142,7 @@
         <v>1</v>
       </c>
       <c r="AQ150">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR150">
         <v>1.37</v>
@@ -32321,7 +32345,7 @@
         <v>0.57</v>
       </c>
       <c r="AP151">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ151">
         <v>0.55</v>
@@ -32449,7 +32473,7 @@
         <v>186</v>
       </c>
       <c r="P152" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="Q152">
         <v>2.95</v>
@@ -32733,10 +32757,10 @@
         <v>0.71</v>
       </c>
       <c r="AP153">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ153">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR153">
         <v>1.41</v>
@@ -33067,7 +33091,7 @@
         <v>188</v>
       </c>
       <c r="P155" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="Q155">
         <v>3.7</v>
@@ -33351,7 +33375,7 @@
         <v>0.71</v>
       </c>
       <c r="AP156">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ156">
         <v>0.6</v>
@@ -33479,7 +33503,7 @@
         <v>102</v>
       </c>
       <c r="P157" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="Q157">
         <v>2.9</v>
@@ -33560,7 +33584,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ157">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR157">
         <v>1.58</v>
@@ -33891,7 +33915,7 @@
         <v>102</v>
       </c>
       <c r="P159" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="Q159">
         <v>2.2</v>
@@ -33969,10 +33993,10 @@
         <v>0.86</v>
       </c>
       <c r="AP159">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ159">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR159">
         <v>1.43</v>
@@ -34303,7 +34327,7 @@
         <v>191</v>
       </c>
       <c r="P161" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="Q161">
         <v>2.2</v>
@@ -34715,7 +34739,7 @@
         <v>193</v>
       </c>
       <c r="P163" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="Q163">
         <v>3</v>
@@ -34796,7 +34820,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ163">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AR163">
         <v>1.43</v>
@@ -35127,7 +35151,7 @@
         <v>194</v>
       </c>
       <c r="P165" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="Q165">
         <v>4.33</v>
@@ -35414,7 +35438,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ166">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR166">
         <v>1.6</v>
@@ -35617,7 +35641,7 @@
         <v>1.38</v>
       </c>
       <c r="AP167">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ167">
         <v>1.36</v>
@@ -35745,7 +35769,7 @@
         <v>196</v>
       </c>
       <c r="P168" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="Q168">
         <v>2.4</v>
@@ -36235,7 +36259,7 @@
         <v>1.63</v>
       </c>
       <c r="AP170">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ170">
         <v>1.82</v>
@@ -36363,7 +36387,7 @@
         <v>197</v>
       </c>
       <c r="P171" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="Q171">
         <v>3</v>
@@ -36441,7 +36465,7 @@
         <v>1.38</v>
       </c>
       <c r="AP171">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ171">
         <v>1.36</v>
@@ -36647,7 +36671,7 @@
         <v>1</v>
       </c>
       <c r="AP172">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ172">
         <v>1</v>
@@ -37059,7 +37083,7 @@
         <v>0.75</v>
       </c>
       <c r="AP174">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ174">
         <v>1</v>
@@ -37268,7 +37292,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ175">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR175">
         <v>1.25</v>
@@ -37474,7 +37498,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ176">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR176">
         <v>1.34</v>
@@ -37677,7 +37701,7 @@
         <v>1.75</v>
       </c>
       <c r="AP177">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ177">
         <v>1.7</v>
@@ -37805,7 +37829,7 @@
         <v>201</v>
       </c>
       <c r="P178" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="Q178">
         <v>3.1</v>
@@ -37883,10 +37907,10 @@
         <v>1.13</v>
       </c>
       <c r="AP178">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ178">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR178">
         <v>1.29</v>
@@ -38011,7 +38035,7 @@
         <v>102</v>
       </c>
       <c r="P179" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="Q179">
         <v>3.55</v>
@@ -38298,7 +38322,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ180">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR180">
         <v>1.28</v>
@@ -38501,7 +38525,7 @@
         <v>1</v>
       </c>
       <c r="AP181">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ181">
         <v>1</v>
@@ -39041,7 +39065,7 @@
         <v>91</v>
       </c>
       <c r="P184" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="Q184">
         <v>2.3</v>
@@ -39122,7 +39146,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ184">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AR184">
         <v>1.68</v>
@@ -39247,7 +39271,7 @@
         <v>204</v>
       </c>
       <c r="P185" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="Q185">
         <v>3.1</v>
@@ -39865,7 +39889,7 @@
         <v>206</v>
       </c>
       <c r="P188" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="Q188">
         <v>3.25</v>
@@ -40483,7 +40507,7 @@
         <v>209</v>
       </c>
       <c r="P191" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="Q191">
         <v>2.75</v>
@@ -40561,7 +40585,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP191">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ191">
         <v>0.55</v>
@@ -40689,7 +40713,7 @@
         <v>210</v>
       </c>
       <c r="P192" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="Q192">
         <v>2.4</v>
@@ -40767,7 +40791,7 @@
         <v>1</v>
       </c>
       <c r="AP192">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ192">
         <v>1</v>
@@ -40973,7 +40997,7 @@
         <v>1.5</v>
       </c>
       <c r="AP193">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ193">
         <v>1.36</v>
@@ -41182,7 +41206,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ194">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR194">
         <v>1.3</v>
@@ -41388,7 +41412,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ195">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR195">
         <v>1.65</v>
@@ -41591,7 +41615,7 @@
         <v>1</v>
       </c>
       <c r="AP196">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ196">
         <v>1</v>
@@ -41719,7 +41743,7 @@
         <v>102</v>
       </c>
       <c r="P197" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="Q197">
         <v>2.5</v>
@@ -41800,7 +41824,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ197">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR197">
         <v>1.37</v>
@@ -42003,7 +42027,7 @@
         <v>1.2</v>
       </c>
       <c r="AP198">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ198">
         <v>1.09</v>
@@ -42337,7 +42361,7 @@
         <v>149</v>
       </c>
       <c r="P200" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="Q200">
         <v>2.63</v>
@@ -42418,7 +42442,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ200">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR200">
         <v>1.24</v>
@@ -42621,7 +42645,7 @@
         <v>1.56</v>
       </c>
       <c r="AP201">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ201">
         <v>1.7</v>
@@ -42749,7 +42773,7 @@
         <v>215</v>
       </c>
       <c r="P202" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="Q202">
         <v>4.33</v>
@@ -42827,7 +42851,7 @@
         <v>2.1</v>
       </c>
       <c r="AP202">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ202">
         <v>2.18</v>
@@ -43161,7 +43185,7 @@
         <v>197</v>
       </c>
       <c r="P204" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="Q204">
         <v>2.5</v>
@@ -43573,7 +43597,7 @@
         <v>217</v>
       </c>
       <c r="P206" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="Q206">
         <v>3.4</v>
@@ -43779,7 +43803,7 @@
         <v>218</v>
       </c>
       <c r="P207" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="Q207">
         <v>2.75</v>
@@ -43860,7 +43884,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ207">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AR207">
         <v>1.56</v>
@@ -43985,7 +44009,7 @@
         <v>102</v>
       </c>
       <c r="P208" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="Q208">
         <v>4</v>
@@ -44760,6 +44784,1242 @@
       </c>
       <c r="BP211">
         <v>1.24</v>
+      </c>
+    </row>
+    <row r="212" spans="1:68">
+      <c r="A212" s="1">
+        <v>211</v>
+      </c>
+      <c r="B212">
+        <v>7509795</v>
+      </c>
+      <c r="C212" t="s">
+        <v>68</v>
+      </c>
+      <c r="D212" t="s">
+        <v>69</v>
+      </c>
+      <c r="E212" s="2">
+        <v>45674.6875</v>
+      </c>
+      <c r="F212">
+        <v>22</v>
+      </c>
+      <c r="G212" t="s">
+        <v>81</v>
+      </c>
+      <c r="H212" t="s">
+        <v>76</v>
+      </c>
+      <c r="I212">
+        <v>1</v>
+      </c>
+      <c r="J212">
+        <v>1</v>
+      </c>
+      <c r="K212">
+        <v>2</v>
+      </c>
+      <c r="L212">
+        <v>1</v>
+      </c>
+      <c r="M212">
+        <v>2</v>
+      </c>
+      <c r="N212">
+        <v>3</v>
+      </c>
+      <c r="O212" t="s">
+        <v>217</v>
+      </c>
+      <c r="P212" t="s">
+        <v>310</v>
+      </c>
+      <c r="Q212">
+        <v>3</v>
+      </c>
+      <c r="R212">
+        <v>1.98</v>
+      </c>
+      <c r="S212">
+        <v>3.5</v>
+      </c>
+      <c r="T212">
+        <v>1.46</v>
+      </c>
+      <c r="U212">
+        <v>2.5</v>
+      </c>
+      <c r="V212">
+        <v>3.1</v>
+      </c>
+      <c r="W212">
+        <v>1.32</v>
+      </c>
+      <c r="X212">
+        <v>8.5</v>
+      </c>
+      <c r="Y212">
+        <v>1.06</v>
+      </c>
+      <c r="Z212">
+        <v>2.35</v>
+      </c>
+      <c r="AA212">
+        <v>3.25</v>
+      </c>
+      <c r="AB212">
+        <v>3</v>
+      </c>
+      <c r="AC212">
+        <v>1.08</v>
+      </c>
+      <c r="AD212">
+        <v>7.5</v>
+      </c>
+      <c r="AE212">
+        <v>1.4</v>
+      </c>
+      <c r="AF212">
+        <v>2.9</v>
+      </c>
+      <c r="AG212">
+        <v>2.1</v>
+      </c>
+      <c r="AH212">
+        <v>1.65</v>
+      </c>
+      <c r="AI212">
+        <v>1.87</v>
+      </c>
+      <c r="AJ212">
+        <v>1.8</v>
+      </c>
+      <c r="AK212">
+        <v>1.37</v>
+      </c>
+      <c r="AL212">
+        <v>1.33</v>
+      </c>
+      <c r="AM212">
+        <v>1.55</v>
+      </c>
+      <c r="AN212">
+        <v>1</v>
+      </c>
+      <c r="AO212">
+        <v>0.5</v>
+      </c>
+      <c r="AP212">
+        <v>0.91</v>
+      </c>
+      <c r="AQ212">
+        <v>0.73</v>
+      </c>
+      <c r="AR212">
+        <v>1.48</v>
+      </c>
+      <c r="AS212">
+        <v>1.25</v>
+      </c>
+      <c r="AT212">
+        <v>2.73</v>
+      </c>
+      <c r="AU212">
+        <v>2</v>
+      </c>
+      <c r="AV212">
+        <v>8</v>
+      </c>
+      <c r="AW212">
+        <v>6</v>
+      </c>
+      <c r="AX212">
+        <v>8</v>
+      </c>
+      <c r="AY212">
+        <v>11</v>
+      </c>
+      <c r="AZ212">
+        <v>19</v>
+      </c>
+      <c r="BA212">
+        <v>1</v>
+      </c>
+      <c r="BB212">
+        <v>4</v>
+      </c>
+      <c r="BC212">
+        <v>5</v>
+      </c>
+      <c r="BD212">
+        <v>1.86</v>
+      </c>
+      <c r="BE212">
+        <v>6.25</v>
+      </c>
+      <c r="BF212">
+        <v>2.15</v>
+      </c>
+      <c r="BG212">
+        <v>1.47</v>
+      </c>
+      <c r="BH212">
+        <v>2.48</v>
+      </c>
+      <c r="BI212">
+        <v>1.76</v>
+      </c>
+      <c r="BJ212">
+        <v>1.93</v>
+      </c>
+      <c r="BK212">
+        <v>2.23</v>
+      </c>
+      <c r="BL212">
+        <v>1.57</v>
+      </c>
+      <c r="BM212">
+        <v>2.9</v>
+      </c>
+      <c r="BN212">
+        <v>1.35</v>
+      </c>
+      <c r="BO212">
+        <v>3.9</v>
+      </c>
+      <c r="BP212">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="213" spans="1:68">
+      <c r="A213" s="1">
+        <v>212</v>
+      </c>
+      <c r="B213">
+        <v>7509794</v>
+      </c>
+      <c r="C213" t="s">
+        <v>68</v>
+      </c>
+      <c r="D213" t="s">
+        <v>69</v>
+      </c>
+      <c r="E213" s="2">
+        <v>45675.45833333334</v>
+      </c>
+      <c r="F213">
+        <v>22</v>
+      </c>
+      <c r="G213" t="s">
+        <v>74</v>
+      </c>
+      <c r="H213" t="s">
+        <v>77</v>
+      </c>
+      <c r="I213">
+        <v>0</v>
+      </c>
+      <c r="J213">
+        <v>0</v>
+      </c>
+      <c r="K213">
+        <v>0</v>
+      </c>
+      <c r="L213">
+        <v>2</v>
+      </c>
+      <c r="M213">
+        <v>1</v>
+      </c>
+      <c r="N213">
+        <v>3</v>
+      </c>
+      <c r="O213" t="s">
+        <v>220</v>
+      </c>
+      <c r="P213" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q213">
+        <v>2.87</v>
+      </c>
+      <c r="R213">
+        <v>1.98</v>
+      </c>
+      <c r="S213">
+        <v>3.75</v>
+      </c>
+      <c r="T213">
+        <v>1.47</v>
+      </c>
+      <c r="U213">
+        <v>2.45</v>
+      </c>
+      <c r="V213">
+        <v>3.2</v>
+      </c>
+      <c r="W213">
+        <v>1.3</v>
+      </c>
+      <c r="X213">
+        <v>8.75</v>
+      </c>
+      <c r="Y213">
+        <v>1.06</v>
+      </c>
+      <c r="Z213">
+        <v>2.2</v>
+      </c>
+      <c r="AA213">
+        <v>2.97</v>
+      </c>
+      <c r="AB213">
+        <v>2.94</v>
+      </c>
+      <c r="AC213">
+        <v>1.08</v>
+      </c>
+      <c r="AD213">
+        <v>7.5</v>
+      </c>
+      <c r="AE213">
+        <v>1.42</v>
+      </c>
+      <c r="AF213">
+        <v>2.8</v>
+      </c>
+      <c r="AG213">
+        <v>2.19</v>
+      </c>
+      <c r="AH213">
+        <v>1.6</v>
+      </c>
+      <c r="AI213">
+        <v>1.95</v>
+      </c>
+      <c r="AJ213">
+        <v>1.75</v>
+      </c>
+      <c r="AK213">
+        <v>1.33</v>
+      </c>
+      <c r="AL213">
+        <v>1.33</v>
+      </c>
+      <c r="AM213">
+        <v>1.62</v>
+      </c>
+      <c r="AN213">
+        <v>1.09</v>
+      </c>
+      <c r="AO213">
+        <v>1.2</v>
+      </c>
+      <c r="AP213">
+        <v>1.25</v>
+      </c>
+      <c r="AQ213">
+        <v>1.09</v>
+      </c>
+      <c r="AR213">
+        <v>1.68</v>
+      </c>
+      <c r="AS213">
+        <v>1.27</v>
+      </c>
+      <c r="AT213">
+        <v>2.95</v>
+      </c>
+      <c r="AU213">
+        <v>5</v>
+      </c>
+      <c r="AV213">
+        <v>4</v>
+      </c>
+      <c r="AW213">
+        <v>18</v>
+      </c>
+      <c r="AX213">
+        <v>8</v>
+      </c>
+      <c r="AY213">
+        <v>26</v>
+      </c>
+      <c r="AZ213">
+        <v>13</v>
+      </c>
+      <c r="BA213">
+        <v>3</v>
+      </c>
+      <c r="BB213">
+        <v>1</v>
+      </c>
+      <c r="BC213">
+        <v>4</v>
+      </c>
+      <c r="BD213">
+        <v>1.77</v>
+      </c>
+      <c r="BE213">
+        <v>6.25</v>
+      </c>
+      <c r="BF213">
+        <v>2.3</v>
+      </c>
+      <c r="BG213">
+        <v>1.49</v>
+      </c>
+      <c r="BH213">
+        <v>2.4</v>
+      </c>
+      <c r="BI213">
+        <v>1.82</v>
+      </c>
+      <c r="BJ213">
+        <v>1.86</v>
+      </c>
+      <c r="BK213">
+        <v>2.33</v>
+      </c>
+      <c r="BL213">
+        <v>1.52</v>
+      </c>
+      <c r="BM213">
+        <v>3.05</v>
+      </c>
+      <c r="BN213">
+        <v>1.3</v>
+      </c>
+      <c r="BO213">
+        <v>4.1</v>
+      </c>
+      <c r="BP213">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="214" spans="1:68">
+      <c r="A214" s="1">
+        <v>213</v>
+      </c>
+      <c r="B214">
+        <v>7509790</v>
+      </c>
+      <c r="C214" t="s">
+        <v>68</v>
+      </c>
+      <c r="D214" t="s">
+        <v>69</v>
+      </c>
+      <c r="E214" s="2">
+        <v>45675.45833333334</v>
+      </c>
+      <c r="F214">
+        <v>22</v>
+      </c>
+      <c r="G214" t="s">
+        <v>87</v>
+      </c>
+      <c r="H214" t="s">
+        <v>85</v>
+      </c>
+      <c r="I214">
+        <v>0</v>
+      </c>
+      <c r="J214">
+        <v>1</v>
+      </c>
+      <c r="K214">
+        <v>1</v>
+      </c>
+      <c r="L214">
+        <v>1</v>
+      </c>
+      <c r="M214">
+        <v>2</v>
+      </c>
+      <c r="N214">
+        <v>3</v>
+      </c>
+      <c r="O214" t="s">
+        <v>112</v>
+      </c>
+      <c r="P214" t="s">
+        <v>312</v>
+      </c>
+      <c r="Q214">
+        <v>2.7</v>
+      </c>
+      <c r="R214">
+        <v>2</v>
+      </c>
+      <c r="S214">
+        <v>4</v>
+      </c>
+      <c r="T214">
+        <v>1.46</v>
+      </c>
+      <c r="U214">
+        <v>2.5</v>
+      </c>
+      <c r="V214">
+        <v>3.1</v>
+      </c>
+      <c r="W214">
+        <v>1.32</v>
+      </c>
+      <c r="X214">
+        <v>8.5</v>
+      </c>
+      <c r="Y214">
+        <v>1.06</v>
+      </c>
+      <c r="Z214">
+        <v>2.08</v>
+      </c>
+      <c r="AA214">
+        <v>3.04</v>
+      </c>
+      <c r="AB214">
+        <v>3.11</v>
+      </c>
+      <c r="AC214">
+        <v>1.08</v>
+      </c>
+      <c r="AD214">
+        <v>7.5</v>
+      </c>
+      <c r="AE214">
+        <v>1.4</v>
+      </c>
+      <c r="AF214">
+        <v>2.9</v>
+      </c>
+      <c r="AG214">
+        <v>2.11</v>
+      </c>
+      <c r="AH214">
+        <v>1.65</v>
+      </c>
+      <c r="AI214">
+        <v>1.9</v>
+      </c>
+      <c r="AJ214">
+        <v>1.77</v>
+      </c>
+      <c r="AK214">
+        <v>1.29</v>
+      </c>
+      <c r="AL214">
+        <v>1.32</v>
+      </c>
+      <c r="AM214">
+        <v>1.7</v>
+      </c>
+      <c r="AN214">
+        <v>1.2</v>
+      </c>
+      <c r="AO214">
+        <v>0.55</v>
+      </c>
+      <c r="AP214">
+        <v>1.09</v>
+      </c>
+      <c r="AQ214">
+        <v>0.75</v>
+      </c>
+      <c r="AR214">
+        <v>1.3</v>
+      </c>
+      <c r="AS214">
+        <v>1.1</v>
+      </c>
+      <c r="AT214">
+        <v>2.4</v>
+      </c>
+      <c r="AU214">
+        <v>7</v>
+      </c>
+      <c r="AV214">
+        <v>6</v>
+      </c>
+      <c r="AW214">
+        <v>14</v>
+      </c>
+      <c r="AX214">
+        <v>6</v>
+      </c>
+      <c r="AY214">
+        <v>24</v>
+      </c>
+      <c r="AZ214">
+        <v>13</v>
+      </c>
+      <c r="BA214">
+        <v>6</v>
+      </c>
+      <c r="BB214">
+        <v>2</v>
+      </c>
+      <c r="BC214">
+        <v>8</v>
+      </c>
+      <c r="BD214">
+        <v>1.78</v>
+      </c>
+      <c r="BE214">
+        <v>6.25</v>
+      </c>
+      <c r="BF214">
+        <v>2.28</v>
+      </c>
+      <c r="BG214">
+        <v>1.46</v>
+      </c>
+      <c r="BH214">
+        <v>2.48</v>
+      </c>
+      <c r="BI214">
+        <v>1.77</v>
+      </c>
+      <c r="BJ214">
+        <v>1.92</v>
+      </c>
+      <c r="BK214">
+        <v>2.23</v>
+      </c>
+      <c r="BL214">
+        <v>1.56</v>
+      </c>
+      <c r="BM214">
+        <v>2.9</v>
+      </c>
+      <c r="BN214">
+        <v>1.35</v>
+      </c>
+      <c r="BO214">
+        <v>3.9</v>
+      </c>
+      <c r="BP214">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="215" spans="1:68">
+      <c r="A215" s="1">
+        <v>214</v>
+      </c>
+      <c r="B215">
+        <v>7509791</v>
+      </c>
+      <c r="C215" t="s">
+        <v>68</v>
+      </c>
+      <c r="D215" t="s">
+        <v>69</v>
+      </c>
+      <c r="E215" s="2">
+        <v>45675.45833333334</v>
+      </c>
+      <c r="F215">
+        <v>22</v>
+      </c>
+      <c r="G215" t="s">
+        <v>82</v>
+      </c>
+      <c r="H215" t="s">
+        <v>79</v>
+      </c>
+      <c r="I215">
+        <v>1</v>
+      </c>
+      <c r="J215">
+        <v>1</v>
+      </c>
+      <c r="K215">
+        <v>2</v>
+      </c>
+      <c r="L215">
+        <v>3</v>
+      </c>
+      <c r="M215">
+        <v>1</v>
+      </c>
+      <c r="N215">
+        <v>4</v>
+      </c>
+      <c r="O215" t="s">
+        <v>221</v>
+      </c>
+      <c r="P215" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q215">
+        <v>2.3</v>
+      </c>
+      <c r="R215">
+        <v>2.05</v>
+      </c>
+      <c r="S215">
+        <v>5</v>
+      </c>
+      <c r="T215">
+        <v>1.43</v>
+      </c>
+      <c r="U215">
+        <v>2.6</v>
+      </c>
+      <c r="V215">
+        <v>2.95</v>
+      </c>
+      <c r="W215">
+        <v>1.34</v>
+      </c>
+      <c r="X215">
+        <v>7.75</v>
+      </c>
+      <c r="Y215">
+        <v>1.07</v>
+      </c>
+      <c r="Z215">
+        <v>1.68</v>
+      </c>
+      <c r="AA215">
+        <v>3.28</v>
+      </c>
+      <c r="AB215">
+        <v>4.41</v>
+      </c>
+      <c r="AC215">
+        <v>1.07</v>
+      </c>
+      <c r="AD215">
+        <v>8</v>
+      </c>
+      <c r="AE215">
+        <v>1.36</v>
+      </c>
+      <c r="AF215">
+        <v>3.1</v>
+      </c>
+      <c r="AG215">
+        <v>1.96</v>
+      </c>
+      <c r="AH215">
+        <v>1.75</v>
+      </c>
+      <c r="AI215">
+        <v>1.98</v>
+      </c>
+      <c r="AJ215">
+        <v>1.72</v>
+      </c>
+      <c r="AK215">
+        <v>1.18</v>
+      </c>
+      <c r="AL215">
+        <v>1.27</v>
+      </c>
+      <c r="AM215">
+        <v>2.05</v>
+      </c>
+      <c r="AN215">
+        <v>1.3</v>
+      </c>
+      <c r="AO215">
+        <v>1</v>
+      </c>
+      <c r="AP215">
+        <v>1.45</v>
+      </c>
+      <c r="AQ215">
+        <v>0.91</v>
+      </c>
+      <c r="AR215">
+        <v>1.56</v>
+      </c>
+      <c r="AS215">
+        <v>1.29</v>
+      </c>
+      <c r="AT215">
+        <v>2.85</v>
+      </c>
+      <c r="AU215">
+        <v>11</v>
+      </c>
+      <c r="AV215">
+        <v>4</v>
+      </c>
+      <c r="AW215">
+        <v>18</v>
+      </c>
+      <c r="AX215">
+        <v>5</v>
+      </c>
+      <c r="AY215">
+        <v>37</v>
+      </c>
+      <c r="AZ215">
+        <v>11</v>
+      </c>
+      <c r="BA215">
+        <v>13</v>
+      </c>
+      <c r="BB215">
+        <v>1</v>
+      </c>
+      <c r="BC215">
+        <v>14</v>
+      </c>
+      <c r="BD215">
+        <v>1.53</v>
+      </c>
+      <c r="BE215">
+        <v>6.4</v>
+      </c>
+      <c r="BF215">
+        <v>2.8</v>
+      </c>
+      <c r="BG215">
+        <v>1.46</v>
+      </c>
+      <c r="BH215">
+        <v>2.5</v>
+      </c>
+      <c r="BI215">
+        <v>1.77</v>
+      </c>
+      <c r="BJ215">
+        <v>1.93</v>
+      </c>
+      <c r="BK215">
+        <v>2.23</v>
+      </c>
+      <c r="BL215">
+        <v>1.56</v>
+      </c>
+      <c r="BM215">
+        <v>2.9</v>
+      </c>
+      <c r="BN215">
+        <v>1.34</v>
+      </c>
+      <c r="BO215">
+        <v>3.9</v>
+      </c>
+      <c r="BP215">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="216" spans="1:68">
+      <c r="A216" s="1">
+        <v>215</v>
+      </c>
+      <c r="B216">
+        <v>7509792</v>
+      </c>
+      <c r="C216" t="s">
+        <v>68</v>
+      </c>
+      <c r="D216" t="s">
+        <v>69</v>
+      </c>
+      <c r="E216" s="2">
+        <v>45675.45833333334</v>
+      </c>
+      <c r="F216">
+        <v>22</v>
+      </c>
+      <c r="G216" t="s">
+        <v>80</v>
+      </c>
+      <c r="H216" t="s">
+        <v>75</v>
+      </c>
+      <c r="I216">
+        <v>1</v>
+      </c>
+      <c r="J216">
+        <v>0</v>
+      </c>
+      <c r="K216">
+        <v>1</v>
+      </c>
+      <c r="L216">
+        <v>1</v>
+      </c>
+      <c r="M216">
+        <v>1</v>
+      </c>
+      <c r="N216">
+        <v>2</v>
+      </c>
+      <c r="O216" t="s">
+        <v>222</v>
+      </c>
+      <c r="P216" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q216">
+        <v>2.75</v>
+      </c>
+      <c r="R216">
+        <v>1.95</v>
+      </c>
+      <c r="S216">
+        <v>4.1</v>
+      </c>
+      <c r="T216">
+        <v>1.51</v>
+      </c>
+      <c r="U216">
+        <v>2.37</v>
+      </c>
+      <c r="V216">
+        <v>3.4</v>
+      </c>
+      <c r="W216">
+        <v>1.27</v>
+      </c>
+      <c r="X216">
+        <v>9.75</v>
+      </c>
+      <c r="Y216">
+        <v>1.04</v>
+      </c>
+      <c r="Z216">
+        <v>2</v>
+      </c>
+      <c r="AA216">
+        <v>2.96</v>
+      </c>
+      <c r="AB216">
+        <v>3.44</v>
+      </c>
+      <c r="AC216">
+        <v>1.1</v>
+      </c>
+      <c r="AD216">
+        <v>6.5</v>
+      </c>
+      <c r="AE216">
+        <v>1.48</v>
+      </c>
+      <c r="AF216">
+        <v>2.6</v>
+      </c>
+      <c r="AG216">
+        <v>2.41</v>
+      </c>
+      <c r="AH216">
+        <v>1.5</v>
+      </c>
+      <c r="AI216">
+        <v>2.1</v>
+      </c>
+      <c r="AJ216">
+        <v>1.63</v>
+      </c>
+      <c r="AK216">
+        <v>1.27</v>
+      </c>
+      <c r="AL216">
+        <v>1.33</v>
+      </c>
+      <c r="AM216">
+        <v>1.71</v>
+      </c>
+      <c r="AN216">
+        <v>1.6</v>
+      </c>
+      <c r="AO216">
+        <v>0.9</v>
+      </c>
+      <c r="AP216">
+        <v>1.55</v>
+      </c>
+      <c r="AQ216">
+        <v>0.91</v>
+      </c>
+      <c r="AR216">
+        <v>1.37</v>
+      </c>
+      <c r="AS216">
+        <v>1.16</v>
+      </c>
+      <c r="AT216">
+        <v>2.53</v>
+      </c>
+      <c r="AU216">
+        <v>5</v>
+      </c>
+      <c r="AV216">
+        <v>4</v>
+      </c>
+      <c r="AW216">
+        <v>17</v>
+      </c>
+      <c r="AX216">
+        <v>3</v>
+      </c>
+      <c r="AY216">
+        <v>25</v>
+      </c>
+      <c r="AZ216">
+        <v>9</v>
+      </c>
+      <c r="BA216">
+        <v>11</v>
+      </c>
+      <c r="BB216">
+        <v>2</v>
+      </c>
+      <c r="BC216">
+        <v>13</v>
+      </c>
+      <c r="BD216">
+        <v>1.67</v>
+      </c>
+      <c r="BE216">
+        <v>6.25</v>
+      </c>
+      <c r="BF216">
+        <v>2.48</v>
+      </c>
+      <c r="BG216">
+        <v>1.53</v>
+      </c>
+      <c r="BH216">
+        <v>2.32</v>
+      </c>
+      <c r="BI216">
+        <v>1.89</v>
+      </c>
+      <c r="BJ216">
+        <v>1.8</v>
+      </c>
+      <c r="BK216">
+        <v>2.4</v>
+      </c>
+      <c r="BL216">
+        <v>1.49</v>
+      </c>
+      <c r="BM216">
+        <v>3.15</v>
+      </c>
+      <c r="BN216">
+        <v>1.29</v>
+      </c>
+      <c r="BO216">
+        <v>4.3</v>
+      </c>
+      <c r="BP216">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="217" spans="1:68">
+      <c r="A217" s="1">
+        <v>216</v>
+      </c>
+      <c r="B217">
+        <v>7509787</v>
+      </c>
+      <c r="C217" t="s">
+        <v>68</v>
+      </c>
+      <c r="D217" t="s">
+        <v>69</v>
+      </c>
+      <c r="E217" s="2">
+        <v>45675.55208333334</v>
+      </c>
+      <c r="F217">
+        <v>22</v>
+      </c>
+      <c r="G217" t="s">
+        <v>71</v>
+      </c>
+      <c r="H217" t="s">
+        <v>70</v>
+      </c>
+      <c r="I217">
+        <v>2</v>
+      </c>
+      <c r="J217">
+        <v>1</v>
+      </c>
+      <c r="K217">
+        <v>3</v>
+      </c>
+      <c r="L217">
+        <v>2</v>
+      </c>
+      <c r="M217">
+        <v>2</v>
+      </c>
+      <c r="N217">
+        <v>4</v>
+      </c>
+      <c r="O217" t="s">
+        <v>223</v>
+      </c>
+      <c r="P217" t="s">
+        <v>313</v>
+      </c>
+      <c r="Q217">
+        <v>2.65</v>
+      </c>
+      <c r="R217">
+        <v>1.98</v>
+      </c>
+      <c r="S217">
+        <v>4.1</v>
+      </c>
+      <c r="T217">
+        <v>1.46</v>
+      </c>
+      <c r="U217">
+        <v>2.5</v>
+      </c>
+      <c r="V217">
+        <v>3.1</v>
+      </c>
+      <c r="W217">
+        <v>1.32</v>
+      </c>
+      <c r="X217">
+        <v>8.5</v>
+      </c>
+      <c r="Y217">
+        <v>1.06</v>
+      </c>
+      <c r="Z217">
+        <v>2.1</v>
+      </c>
+      <c r="AA217">
+        <v>3.15</v>
+      </c>
+      <c r="AB217">
+        <v>3.6</v>
+      </c>
+      <c r="AC217">
+        <v>1.07</v>
+      </c>
+      <c r="AD217">
+        <v>8</v>
+      </c>
+      <c r="AE217">
+        <v>1.38</v>
+      </c>
+      <c r="AF217">
+        <v>2.95</v>
+      </c>
+      <c r="AG217">
+        <v>2.02</v>
+      </c>
+      <c r="AH217">
+        <v>1.68</v>
+      </c>
+      <c r="AI217">
+        <v>1.93</v>
+      </c>
+      <c r="AJ217">
+        <v>1.77</v>
+      </c>
+      <c r="AK217">
+        <v>1.27</v>
+      </c>
+      <c r="AL217">
+        <v>1.32</v>
+      </c>
+      <c r="AM217">
+        <v>1.73</v>
+      </c>
+      <c r="AN217">
+        <v>1.55</v>
+      </c>
+      <c r="AO217">
+        <v>1</v>
+      </c>
+      <c r="AP217">
+        <v>1.5</v>
+      </c>
+      <c r="AQ217">
+        <v>1</v>
+      </c>
+      <c r="AR217">
+        <v>1.34</v>
+      </c>
+      <c r="AS217">
+        <v>1.18</v>
+      </c>
+      <c r="AT217">
+        <v>2.52</v>
+      </c>
+      <c r="AU217">
+        <v>9</v>
+      </c>
+      <c r="AV217">
+        <v>7</v>
+      </c>
+      <c r="AW217">
+        <v>9</v>
+      </c>
+      <c r="AX217">
+        <v>2</v>
+      </c>
+      <c r="AY217">
+        <v>20</v>
+      </c>
+      <c r="AZ217">
+        <v>9</v>
+      </c>
+      <c r="BA217">
+        <v>6</v>
+      </c>
+      <c r="BB217">
+        <v>1</v>
+      </c>
+      <c r="BC217">
+        <v>7</v>
+      </c>
+      <c r="BD217">
+        <v>1.48</v>
+      </c>
+      <c r="BE217">
+        <v>6.5</v>
+      </c>
+      <c r="BF217">
+        <v>2.95</v>
+      </c>
+      <c r="BG217">
+        <v>1.35</v>
+      </c>
+      <c r="BH217">
+        <v>2.9</v>
+      </c>
+      <c r="BI217">
+        <v>1.6</v>
+      </c>
+      <c r="BJ217">
+        <v>2.17</v>
+      </c>
+      <c r="BK217">
+        <v>1.98</v>
+      </c>
+      <c r="BL217">
+        <v>1.73</v>
+      </c>
+      <c r="BM217">
+        <v>2.55</v>
+      </c>
+      <c r="BN217">
+        <v>1.45</v>
+      </c>
+      <c r="BO217">
+        <v>3.3</v>
+      </c>
+      <c r="BP217">
+        <v>1.28</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Italy Serie B_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Italy Serie B_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1364" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1388" uniqueCount="317">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -688,6 +688,9 @@
     <t>['1', '41']</t>
   </si>
   <si>
+    <t>['9', '55', '58', '69', '90+2']</t>
+  </si>
+  <si>
     <t>['24', '45+2', '80']</t>
   </si>
   <si>
@@ -956,6 +959,12 @@
   </si>
   <si>
     <t>['30', '65']</t>
+  </si>
+  <si>
+    <t>['3', '11', '64']</t>
+  </si>
+  <si>
+    <t>['20', '45+4', '50', '58']</t>
   </si>
 </sst>
 </file>
@@ -1317,7 +1326,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP217"/>
+  <dimension ref="A1:BP221"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1779,7 +1788,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q3">
         <v>2.63</v>
@@ -1860,7 +1869,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ3">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1985,7 +1994,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q4">
         <v>3.5</v>
@@ -2191,7 +2200,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q5">
         <v>3.2</v>
@@ -2272,7 +2281,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ5">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2603,7 +2612,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q7">
         <v>3.25</v>
@@ -3015,7 +3024,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q9">
         <v>3.4</v>
@@ -3221,7 +3230,7 @@
         <v>98</v>
       </c>
       <c r="P10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q10">
         <v>3.75</v>
@@ -3299,7 +3308,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ10">
         <v>2.18</v>
@@ -3633,7 +3642,7 @@
         <v>100</v>
       </c>
       <c r="P12" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q12">
         <v>3.25</v>
@@ -3839,7 +3848,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q13">
         <v>3.4</v>
@@ -4045,7 +4054,7 @@
         <v>102</v>
       </c>
       <c r="P14" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q14">
         <v>2.3</v>
@@ -4663,7 +4672,7 @@
         <v>104</v>
       </c>
       <c r="P17" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q17">
         <v>2.88</v>
@@ -5153,7 +5162,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AQ19">
         <v>0.73</v>
@@ -5281,7 +5290,7 @@
         <v>107</v>
       </c>
       <c r="P20" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q20">
         <v>2.88</v>
@@ -5565,10 +5574,10 @@
         <v>3</v>
       </c>
       <c r="AP21">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ21">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR21">
         <v>1.33</v>
@@ -5693,7 +5702,7 @@
         <v>91</v>
       </c>
       <c r="P22" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q22">
         <v>3.4</v>
@@ -5977,10 +5986,10 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AQ23">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR23">
         <v>0</v>
@@ -6105,7 +6114,7 @@
         <v>109</v>
       </c>
       <c r="P24" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q24">
         <v>2.98</v>
@@ -6392,7 +6401,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ25">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AR25">
         <v>0</v>
@@ -6723,7 +6732,7 @@
         <v>102</v>
       </c>
       <c r="P27" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q27">
         <v>2.74</v>
@@ -7422,7 +7431,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ30">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR30">
         <v>1.65</v>
@@ -7959,7 +7968,7 @@
         <v>102</v>
       </c>
       <c r="P33" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q33">
         <v>2.8</v>
@@ -8371,7 +8380,7 @@
         <v>116</v>
       </c>
       <c r="P35" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q35">
         <v>3</v>
@@ -8449,7 +8458,7 @@
         <v>0</v>
       </c>
       <c r="AP35">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AQ35">
         <v>1.82</v>
@@ -8577,7 +8586,7 @@
         <v>117</v>
       </c>
       <c r="P36" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q36">
         <v>2.9</v>
@@ -8864,7 +8873,7 @@
         <v>1</v>
       </c>
       <c r="AQ37">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR37">
         <v>1.58</v>
@@ -9195,7 +9204,7 @@
         <v>119</v>
       </c>
       <c r="P39" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q39">
         <v>2.63</v>
@@ -9273,7 +9282,7 @@
         <v>0</v>
       </c>
       <c r="AP39">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ39">
         <v>0.91</v>
@@ -9401,7 +9410,7 @@
         <v>120</v>
       </c>
       <c r="P40" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q40">
         <v>3.2</v>
@@ -9607,7 +9616,7 @@
         <v>121</v>
       </c>
       <c r="P41" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q41">
         <v>2.63</v>
@@ -9685,7 +9694,7 @@
         <v>0</v>
       </c>
       <c r="AP41">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ41">
         <v>0.55</v>
@@ -9813,7 +9822,7 @@
         <v>122</v>
       </c>
       <c r="P42" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q42">
         <v>2.88</v>
@@ -10637,7 +10646,7 @@
         <v>125</v>
       </c>
       <c r="P46" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q46">
         <v>3.75</v>
@@ -10924,7 +10933,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ47">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR47">
         <v>1.62</v>
@@ -11049,7 +11058,7 @@
         <v>116</v>
       </c>
       <c r="P48" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q48">
         <v>3.4</v>
@@ -11130,7 +11139,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ48">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR48">
         <v>1.25</v>
@@ -11255,7 +11264,7 @@
         <v>102</v>
       </c>
       <c r="P49" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q49">
         <v>3.75</v>
@@ -11333,7 +11342,7 @@
         <v>1</v>
       </c>
       <c r="AP49">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AQ49">
         <v>2.18</v>
@@ -11461,7 +11470,7 @@
         <v>127</v>
       </c>
       <c r="P50" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q50">
         <v>3.4</v>
@@ -11667,7 +11676,7 @@
         <v>128</v>
       </c>
       <c r="P51" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q51">
         <v>3.1</v>
@@ -11748,7 +11757,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ51">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AR51">
         <v>1.83</v>
@@ -11873,7 +11882,7 @@
         <v>129</v>
       </c>
       <c r="P52" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q52">
         <v>3.79</v>
@@ -11951,7 +11960,7 @@
         <v>1.5</v>
       </c>
       <c r="AP52">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ52">
         <v>1.82</v>
@@ -12363,7 +12372,7 @@
         <v>0</v>
       </c>
       <c r="AP54">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ54">
         <v>0.73</v>
@@ -12491,7 +12500,7 @@
         <v>130</v>
       </c>
       <c r="P55" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q55">
         <v>2.5</v>
@@ -12984,7 +12993,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ57">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR57">
         <v>0.86</v>
@@ -13190,7 +13199,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ58">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR58">
         <v>1.74</v>
@@ -13315,7 +13324,7 @@
         <v>102</v>
       </c>
       <c r="P59" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q59">
         <v>3.1</v>
@@ -13727,7 +13736,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q61">
         <v>2.38</v>
@@ -13933,7 +13942,7 @@
         <v>134</v>
       </c>
       <c r="P62" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q62">
         <v>3.25</v>
@@ -14217,10 +14226,10 @@
         <v>1</v>
       </c>
       <c r="AP63">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AQ63">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR63">
         <v>1.29</v>
@@ -14345,7 +14354,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q64">
         <v>2.9</v>
@@ -14629,7 +14638,7 @@
         <v>1.5</v>
       </c>
       <c r="AP65">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AQ65">
         <v>1.09</v>
@@ -14757,7 +14766,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q66">
         <v>2.4</v>
@@ -15044,7 +15053,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ67">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AR67">
         <v>1.2</v>
@@ -15169,7 +15178,7 @@
         <v>138</v>
       </c>
       <c r="P68" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q68">
         <v>3.1</v>
@@ -15581,7 +15590,7 @@
         <v>139</v>
       </c>
       <c r="P70" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q70">
         <v>3.5</v>
@@ -15787,7 +15796,7 @@
         <v>140</v>
       </c>
       <c r="P71" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q71">
         <v>3.5</v>
@@ -15993,7 +16002,7 @@
         <v>141</v>
       </c>
       <c r="P72" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q72">
         <v>2.4</v>
@@ -16074,7 +16083,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ72">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR72">
         <v>0.97</v>
@@ -16199,7 +16208,7 @@
         <v>102</v>
       </c>
       <c r="P73" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q73">
         <v>2.5</v>
@@ -16405,7 +16414,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q74">
         <v>2.5</v>
@@ -16483,7 +16492,7 @@
         <v>1.5</v>
       </c>
       <c r="AP74">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AQ74">
         <v>1.18</v>
@@ -16817,7 +16826,7 @@
         <v>143</v>
       </c>
       <c r="P76" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q76">
         <v>2.95</v>
@@ -17023,7 +17032,7 @@
         <v>102</v>
       </c>
       <c r="P77" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q77">
         <v>3.2</v>
@@ -17104,7 +17113,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ77">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR77">
         <v>1.41</v>
@@ -17229,7 +17238,7 @@
         <v>144</v>
       </c>
       <c r="P78" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q78">
         <v>3.1</v>
@@ -17435,7 +17444,7 @@
         <v>134</v>
       </c>
       <c r="P79" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q79">
         <v>2.5</v>
@@ -17641,7 +17650,7 @@
         <v>145</v>
       </c>
       <c r="P80" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q80">
         <v>3.4</v>
@@ -17719,7 +17728,7 @@
         <v>0.67</v>
       </c>
       <c r="AP80">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ80">
         <v>0.82</v>
@@ -17925,7 +17934,7 @@
         <v>0.33</v>
       </c>
       <c r="AP81">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ81">
         <v>0.6</v>
@@ -18259,7 +18268,7 @@
         <v>146</v>
       </c>
       <c r="P83" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q83">
         <v>3.6</v>
@@ -18340,7 +18349,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ83">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AR83">
         <v>1.66</v>
@@ -18465,7 +18474,7 @@
         <v>102</v>
       </c>
       <c r="P84" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q84">
         <v>3.4</v>
@@ -18546,7 +18555,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ84">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR84">
         <v>1.72</v>
@@ -18877,7 +18886,7 @@
         <v>147</v>
       </c>
       <c r="P86" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q86">
         <v>3.2</v>
@@ -19083,7 +19092,7 @@
         <v>148</v>
       </c>
       <c r="P87" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q87">
         <v>3.2</v>
@@ -19289,7 +19298,7 @@
         <v>149</v>
       </c>
       <c r="P88" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q88">
         <v>3.75</v>
@@ -19495,7 +19504,7 @@
         <v>150</v>
       </c>
       <c r="P89" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q89">
         <v>2.88</v>
@@ -19573,7 +19582,7 @@
         <v>0.25</v>
       </c>
       <c r="AP89">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AQ89">
         <v>0.75</v>
@@ -19907,7 +19916,7 @@
         <v>152</v>
       </c>
       <c r="P91" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q91">
         <v>3.1</v>
@@ -20606,7 +20615,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ94">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR94">
         <v>1.63</v>
@@ -21015,7 +21024,7 @@
         <v>1</v>
       </c>
       <c r="AP96">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ96">
         <v>1.09</v>
@@ -21221,7 +21230,7 @@
         <v>0.75</v>
       </c>
       <c r="AP97">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AQ97">
         <v>0.82</v>
@@ -21427,7 +21436,7 @@
         <v>1.2</v>
       </c>
       <c r="AP98">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AQ98">
         <v>1.18</v>
@@ -21633,10 +21642,10 @@
         <v>1.5</v>
       </c>
       <c r="AP99">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ99">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR99">
         <v>1.26</v>
@@ -21842,7 +21851,7 @@
         <v>1</v>
       </c>
       <c r="AQ100">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AR100">
         <v>1.52</v>
@@ -22460,7 +22469,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ103">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR103">
         <v>1.86</v>
@@ -22585,7 +22594,7 @@
         <v>160</v>
       </c>
       <c r="P104" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q104">
         <v>3.9</v>
@@ -22791,7 +22800,7 @@
         <v>161</v>
       </c>
       <c r="P105" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q105">
         <v>3.25</v>
@@ -23409,7 +23418,7 @@
         <v>162</v>
       </c>
       <c r="P108" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q108">
         <v>3.1</v>
@@ -24439,7 +24448,7 @@
         <v>163</v>
       </c>
       <c r="P113" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q113">
         <v>2.75</v>
@@ -24723,10 +24732,10 @@
         <v>1.5</v>
       </c>
       <c r="AP114">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AQ114">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR114">
         <v>1.23</v>
@@ -24929,7 +24938,7 @@
         <v>0.8</v>
       </c>
       <c r="AP115">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ115">
         <v>0.91</v>
@@ -25138,7 +25147,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ116">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR116">
         <v>1.53</v>
@@ -25263,7 +25272,7 @@
         <v>164</v>
       </c>
       <c r="P117" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q117">
         <v>3</v>
@@ -25469,7 +25478,7 @@
         <v>164</v>
       </c>
       <c r="P118" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q118">
         <v>2.88</v>
@@ -25550,7 +25559,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ118">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AR118">
         <v>1.42</v>
@@ -25753,7 +25762,7 @@
         <v>1</v>
       </c>
       <c r="AP119">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ119">
         <v>1.18</v>
@@ -25881,7 +25890,7 @@
         <v>102</v>
       </c>
       <c r="P120" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q120">
         <v>2.4</v>
@@ -26165,7 +26174,7 @@
         <v>0.33</v>
       </c>
       <c r="AP121">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AQ121">
         <v>0.75</v>
@@ -26293,7 +26302,7 @@
         <v>166</v>
       </c>
       <c r="P122" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q122">
         <v>3.45</v>
@@ -27117,7 +27126,7 @@
         <v>169</v>
       </c>
       <c r="P126" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q126">
         <v>3.1</v>
@@ -27529,7 +27538,7 @@
         <v>102</v>
       </c>
       <c r="P128" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q128">
         <v>3.65</v>
@@ -27610,7 +27619,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ128">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR128">
         <v>1.36</v>
@@ -27735,7 +27744,7 @@
         <v>102</v>
       </c>
       <c r="P129" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q129">
         <v>3.35</v>
@@ -27941,7 +27950,7 @@
         <v>170</v>
       </c>
       <c r="P130" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q130">
         <v>3</v>
@@ -28147,7 +28156,7 @@
         <v>102</v>
       </c>
       <c r="P131" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q131">
         <v>3.1</v>
@@ -28353,7 +28362,7 @@
         <v>119</v>
       </c>
       <c r="P132" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q132">
         <v>3.4</v>
@@ -28637,7 +28646,7 @@
         <v>0.83</v>
       </c>
       <c r="AP133">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AQ133">
         <v>0.6</v>
@@ -29049,10 +29058,10 @@
         <v>1.83</v>
       </c>
       <c r="AP135">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AQ135">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AR135">
         <v>1.13</v>
@@ -29177,7 +29186,7 @@
         <v>173</v>
       </c>
       <c r="P136" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q136">
         <v>2.5</v>
@@ -29255,7 +29264,7 @@
         <v>0.29</v>
       </c>
       <c r="AP136">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ136">
         <v>0.75</v>
@@ -29383,7 +29392,7 @@
         <v>174</v>
       </c>
       <c r="P137" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q137">
         <v>2.6</v>
@@ -29589,7 +29598,7 @@
         <v>175</v>
       </c>
       <c r="P138" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q138">
         <v>2.6</v>
@@ -29876,7 +29885,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ139">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR139">
         <v>1.53</v>
@@ -30207,7 +30216,7 @@
         <v>178</v>
       </c>
       <c r="P141" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -30285,7 +30294,7 @@
         <v>1.14</v>
       </c>
       <c r="AP141">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ141">
         <v>1</v>
@@ -30413,7 +30422,7 @@
         <v>102</v>
       </c>
       <c r="P142" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q142">
         <v>4.2</v>
@@ -30619,7 +30628,7 @@
         <v>179</v>
       </c>
       <c r="P143" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q143">
         <v>2.55</v>
@@ -30825,7 +30834,7 @@
         <v>102</v>
       </c>
       <c r="P144" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q144">
         <v>3.95</v>
@@ -31237,7 +31246,7 @@
         <v>181</v>
       </c>
       <c r="P146" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q146">
         <v>3.1</v>
@@ -31318,7 +31327,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ146">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR146">
         <v>1.34</v>
@@ -31727,10 +31736,10 @@
         <v>1.57</v>
       </c>
       <c r="AP148">
+        <v>1.64</v>
+      </c>
+      <c r="AQ148">
         <v>1.5</v>
-      </c>
-      <c r="AQ148">
-        <v>1.36</v>
       </c>
       <c r="AR148">
         <v>1.81</v>
@@ -31855,7 +31864,7 @@
         <v>183</v>
       </c>
       <c r="P149" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q149">
         <v>2.63</v>
@@ -32061,7 +32070,7 @@
         <v>184</v>
       </c>
       <c r="P150" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q150">
         <v>3.6</v>
@@ -32473,7 +32482,7 @@
         <v>186</v>
       </c>
       <c r="P152" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q152">
         <v>2.95</v>
@@ -32554,7 +32563,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ152">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR152">
         <v>1.26</v>
@@ -32963,7 +32972,7 @@
         <v>1.5</v>
       </c>
       <c r="AP154">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AQ154">
         <v>1.09</v>
@@ -33091,7 +33100,7 @@
         <v>188</v>
       </c>
       <c r="P155" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q155">
         <v>3.7</v>
@@ -33172,7 +33181,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ155">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AR155">
         <v>1.27</v>
@@ -33503,7 +33512,7 @@
         <v>102</v>
       </c>
       <c r="P157" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q157">
         <v>2.9</v>
@@ -33787,7 +33796,7 @@
         <v>1.14</v>
       </c>
       <c r="AP158">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ158">
         <v>1</v>
@@ -33915,7 +33924,7 @@
         <v>102</v>
       </c>
       <c r="P159" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q159">
         <v>2.2</v>
@@ -34327,7 +34336,7 @@
         <v>191</v>
       </c>
       <c r="P161" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q161">
         <v>2.2</v>
@@ -34405,7 +34414,7 @@
         <v>1.13</v>
       </c>
       <c r="AP161">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AQ161">
         <v>1</v>
@@ -34739,7 +34748,7 @@
         <v>193</v>
       </c>
       <c r="P163" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q163">
         <v>3</v>
@@ -35151,7 +35160,7 @@
         <v>194</v>
       </c>
       <c r="P165" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q165">
         <v>4.33</v>
@@ -35644,7 +35653,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ167">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR167">
         <v>1.43</v>
@@ -35769,7 +35778,7 @@
         <v>196</v>
       </c>
       <c r="P168" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q168">
         <v>2.4</v>
@@ -35847,7 +35856,7 @@
         <v>0.86</v>
       </c>
       <c r="AP168">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ168">
         <v>1.1</v>
@@ -36387,7 +36396,7 @@
         <v>197</v>
       </c>
       <c r="P171" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q171">
         <v>3</v>
@@ -36468,7 +36477,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ171">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR171">
         <v>1.73</v>
@@ -36877,7 +36886,7 @@
         <v>1.33</v>
       </c>
       <c r="AP173">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AQ173">
         <v>1.09</v>
@@ -37086,7 +37095,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ174">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR174">
         <v>1.36</v>
@@ -37289,7 +37298,7 @@
         <v>1.25</v>
       </c>
       <c r="AP175">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AQ175">
         <v>0.91</v>
@@ -37704,7 +37713,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ177">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AR177">
         <v>1.48</v>
@@ -37829,7 +37838,7 @@
         <v>201</v>
       </c>
       <c r="P178" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q178">
         <v>3.1</v>
@@ -38035,7 +38044,7 @@
         <v>102</v>
       </c>
       <c r="P179" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q179">
         <v>3.55</v>
@@ -38113,10 +38122,10 @@
         <v>1.33</v>
       </c>
       <c r="AP179">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ179">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR179">
         <v>1.23</v>
@@ -38940,7 +38949,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ183">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR183">
         <v>1.3</v>
@@ -39065,7 +39074,7 @@
         <v>91</v>
       </c>
       <c r="P184" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q184">
         <v>2.3</v>
@@ -39271,7 +39280,7 @@
         <v>204</v>
       </c>
       <c r="P185" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q185">
         <v>3.1</v>
@@ -39889,7 +39898,7 @@
         <v>206</v>
       </c>
       <c r="P188" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q188">
         <v>3.25</v>
@@ -40379,7 +40388,7 @@
         <v>1.25</v>
       </c>
       <c r="AP190">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ190">
         <v>1.1</v>
@@ -40507,7 +40516,7 @@
         <v>209</v>
       </c>
       <c r="P191" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q191">
         <v>2.75</v>
@@ -40713,7 +40722,7 @@
         <v>210</v>
       </c>
       <c r="P192" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q192">
         <v>2.4</v>
@@ -41000,7 +41009,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ193">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR193">
         <v>1.34</v>
@@ -41203,7 +41212,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP194">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AQ194">
         <v>0.73</v>
@@ -41409,7 +41418,7 @@
         <v>1.11</v>
       </c>
       <c r="AP195">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AQ195">
         <v>0.91</v>
@@ -41618,7 +41627,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ196">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR196">
         <v>1.41</v>
@@ -41743,7 +41752,7 @@
         <v>102</v>
       </c>
       <c r="P197" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q197">
         <v>2.5</v>
@@ -42233,7 +42242,7 @@
         <v>0.67</v>
       </c>
       <c r="AP199">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ199">
         <v>0.6</v>
@@ -42361,7 +42370,7 @@
         <v>149</v>
       </c>
       <c r="P200" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q200">
         <v>2.63</v>
@@ -42648,7 +42657,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ201">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AR201">
         <v>1.5</v>
@@ -42773,7 +42782,7 @@
         <v>215</v>
       </c>
       <c r="P202" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q202">
         <v>4.33</v>
@@ -43185,7 +43194,7 @@
         <v>197</v>
       </c>
       <c r="P204" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q204">
         <v>2.5</v>
@@ -43266,7 +43275,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ204">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR204">
         <v>1.74</v>
@@ -43469,7 +43478,7 @@
         <v>0.9</v>
       </c>
       <c r="AP205">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ205">
         <v>0.82</v>
@@ -43597,7 +43606,7 @@
         <v>217</v>
       </c>
       <c r="P206" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q206">
         <v>3.4</v>
@@ -43803,7 +43812,7 @@
         <v>218</v>
       </c>
       <c r="P207" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q207">
         <v>2.75</v>
@@ -44009,7 +44018,7 @@
         <v>102</v>
       </c>
       <c r="P208" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q208">
         <v>4</v>
@@ -44833,7 +44842,7 @@
         <v>217</v>
       </c>
       <c r="P212" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q212">
         <v>3</v>
@@ -45039,7 +45048,7 @@
         <v>220</v>
       </c>
       <c r="P213" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q213">
         <v>2.87</v>
@@ -45245,7 +45254,7 @@
         <v>112</v>
       </c>
       <c r="P214" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q214">
         <v>2.7</v>
@@ -45562,13 +45571,13 @@
         <v>11</v>
       </c>
       <c r="BA215">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BB215">
         <v>1</v>
       </c>
       <c r="BC215">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BD215">
         <v>1.53</v>
@@ -45863,7 +45872,7 @@
         <v>223</v>
       </c>
       <c r="P217" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q217">
         <v>2.65</v>
@@ -46019,6 +46028,830 @@
         <v>3.3</v>
       </c>
       <c r="BP217">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="218" spans="1:68">
+      <c r="A218" s="1">
+        <v>217</v>
+      </c>
+      <c r="B218">
+        <v>7509796</v>
+      </c>
+      <c r="C218" t="s">
+        <v>68</v>
+      </c>
+      <c r="D218" t="s">
+        <v>69</v>
+      </c>
+      <c r="E218" s="2">
+        <v>45676.45833333334</v>
+      </c>
+      <c r="F218">
+        <v>22</v>
+      </c>
+      <c r="G218" t="s">
+        <v>84</v>
+      </c>
+      <c r="H218" t="s">
+        <v>72</v>
+      </c>
+      <c r="I218">
+        <v>1</v>
+      </c>
+      <c r="J218">
+        <v>2</v>
+      </c>
+      <c r="K218">
+        <v>3</v>
+      </c>
+      <c r="L218">
+        <v>5</v>
+      </c>
+      <c r="M218">
+        <v>3</v>
+      </c>
+      <c r="N218">
+        <v>8</v>
+      </c>
+      <c r="O218" t="s">
+        <v>224</v>
+      </c>
+      <c r="P218" t="s">
+        <v>315</v>
+      </c>
+      <c r="Q218">
+        <v>2.05</v>
+      </c>
+      <c r="R218">
+        <v>2.2</v>
+      </c>
+      <c r="S218">
+        <v>5.5</v>
+      </c>
+      <c r="T218">
+        <v>1.37</v>
+      </c>
+      <c r="U218">
+        <v>2.85</v>
+      </c>
+      <c r="V218">
+        <v>2.7</v>
+      </c>
+      <c r="W218">
+        <v>1.41</v>
+      </c>
+      <c r="X218">
+        <v>6.75</v>
+      </c>
+      <c r="Y218">
+        <v>1.09</v>
+      </c>
+      <c r="Z218">
+        <v>1.5</v>
+      </c>
+      <c r="AA218">
+        <v>4.1</v>
+      </c>
+      <c r="AB218">
+        <v>6.08</v>
+      </c>
+      <c r="AC218">
+        <v>1.05</v>
+      </c>
+      <c r="AD218">
+        <v>9.5</v>
+      </c>
+      <c r="AE218">
+        <v>1.28</v>
+      </c>
+      <c r="AF218">
+        <v>3.55</v>
+      </c>
+      <c r="AG218">
+        <v>1.8</v>
+      </c>
+      <c r="AH218">
+        <v>1.9</v>
+      </c>
+      <c r="AI218">
+        <v>1.98</v>
+      </c>
+      <c r="AJ218">
+        <v>1.73</v>
+      </c>
+      <c r="AK218">
+        <v>1.12</v>
+      </c>
+      <c r="AL218">
+        <v>1.22</v>
+      </c>
+      <c r="AM218">
+        <v>2.45</v>
+      </c>
+      <c r="AN218">
+        <v>2.5</v>
+      </c>
+      <c r="AO218">
+        <v>1</v>
+      </c>
+      <c r="AP218">
+        <v>2.55</v>
+      </c>
+      <c r="AQ218">
+        <v>0.91</v>
+      </c>
+      <c r="AR218">
+        <v>1.73</v>
+      </c>
+      <c r="AS218">
+        <v>1.2</v>
+      </c>
+      <c r="AT218">
+        <v>2.93</v>
+      </c>
+      <c r="AU218">
+        <v>8</v>
+      </c>
+      <c r="AV218">
+        <v>6</v>
+      </c>
+      <c r="AW218">
+        <v>13</v>
+      </c>
+      <c r="AX218">
+        <v>5</v>
+      </c>
+      <c r="AY218">
+        <v>27</v>
+      </c>
+      <c r="AZ218">
+        <v>11</v>
+      </c>
+      <c r="BA218">
+        <v>4</v>
+      </c>
+      <c r="BB218">
+        <v>5</v>
+      </c>
+      <c r="BC218">
+        <v>9</v>
+      </c>
+      <c r="BD218">
+        <v>1.44</v>
+      </c>
+      <c r="BE218">
+        <v>6.75</v>
+      </c>
+      <c r="BF218">
+        <v>3.15</v>
+      </c>
+      <c r="BG218">
+        <v>1.44</v>
+      </c>
+      <c r="BH218">
+        <v>2.55</v>
+      </c>
+      <c r="BI218">
+        <v>1.73</v>
+      </c>
+      <c r="BJ218">
+        <v>1.98</v>
+      </c>
+      <c r="BK218">
+        <v>2.17</v>
+      </c>
+      <c r="BL218">
+        <v>1.6</v>
+      </c>
+      <c r="BM218">
+        <v>2.8</v>
+      </c>
+      <c r="BN218">
+        <v>1.38</v>
+      </c>
+      <c r="BO218">
+        <v>3.7</v>
+      </c>
+      <c r="BP218">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="219" spans="1:68">
+      <c r="A219" s="1">
+        <v>218</v>
+      </c>
+      <c r="B219">
+        <v>7509789</v>
+      </c>
+      <c r="C219" t="s">
+        <v>68</v>
+      </c>
+      <c r="D219" t="s">
+        <v>69</v>
+      </c>
+      <c r="E219" s="2">
+        <v>45676.45833333334</v>
+      </c>
+      <c r="F219">
+        <v>22</v>
+      </c>
+      <c r="G219" t="s">
+        <v>78</v>
+      </c>
+      <c r="H219" t="s">
+        <v>73</v>
+      </c>
+      <c r="I219">
+        <v>0</v>
+      </c>
+      <c r="J219">
+        <v>0</v>
+      </c>
+      <c r="K219">
+        <v>0</v>
+      </c>
+      <c r="L219">
+        <v>0</v>
+      </c>
+      <c r="M219">
+        <v>0</v>
+      </c>
+      <c r="N219">
+        <v>0</v>
+      </c>
+      <c r="O219" t="s">
+        <v>102</v>
+      </c>
+      <c r="P219" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q219">
+        <v>3.75</v>
+      </c>
+      <c r="R219">
+        <v>2</v>
+      </c>
+      <c r="S219">
+        <v>3.2</v>
+      </c>
+      <c r="T219">
+        <v>1.5</v>
+      </c>
+      <c r="U219">
+        <v>2.5</v>
+      </c>
+      <c r="V219">
+        <v>3.4</v>
+      </c>
+      <c r="W219">
+        <v>1.3</v>
+      </c>
+      <c r="X219">
+        <v>10</v>
+      </c>
+      <c r="Y219">
+        <v>1.06</v>
+      </c>
+      <c r="Z219">
+        <v>3.21</v>
+      </c>
+      <c r="AA219">
+        <v>2.8</v>
+      </c>
+      <c r="AB219">
+        <v>2.46</v>
+      </c>
+      <c r="AC219">
+        <v>1.09</v>
+      </c>
+      <c r="AD219">
+        <v>7</v>
+      </c>
+      <c r="AE219">
+        <v>1.42</v>
+      </c>
+      <c r="AF219">
+        <v>2.8</v>
+      </c>
+      <c r="AG219">
+        <v>2.19</v>
+      </c>
+      <c r="AH219">
+        <v>1.6</v>
+      </c>
+      <c r="AI219">
+        <v>1.91</v>
+      </c>
+      <c r="AJ219">
+        <v>1.91</v>
+      </c>
+      <c r="AK219">
+        <v>1.51</v>
+      </c>
+      <c r="AL219">
+        <v>1.36</v>
+      </c>
+      <c r="AM219">
+        <v>1.38</v>
+      </c>
+      <c r="AN219">
+        <v>1.55</v>
+      </c>
+      <c r="AO219">
+        <v>1.7</v>
+      </c>
+      <c r="AP219">
+        <v>1.5</v>
+      </c>
+      <c r="AQ219">
+        <v>1.64</v>
+      </c>
+      <c r="AR219">
+        <v>1.25</v>
+      </c>
+      <c r="AS219">
+        <v>1.11</v>
+      </c>
+      <c r="AT219">
+        <v>2.36</v>
+      </c>
+      <c r="AU219">
+        <v>7</v>
+      </c>
+      <c r="AV219">
+        <v>2</v>
+      </c>
+      <c r="AW219">
+        <v>9</v>
+      </c>
+      <c r="AX219">
+        <v>10</v>
+      </c>
+      <c r="AY219">
+        <v>18</v>
+      </c>
+      <c r="AZ219">
+        <v>14</v>
+      </c>
+      <c r="BA219">
+        <v>5</v>
+      </c>
+      <c r="BB219">
+        <v>5</v>
+      </c>
+      <c r="BC219">
+        <v>10</v>
+      </c>
+      <c r="BD219">
+        <v>2.02</v>
+      </c>
+      <c r="BE219">
+        <v>6.4</v>
+      </c>
+      <c r="BF219">
+        <v>1.97</v>
+      </c>
+      <c r="BG219">
+        <v>1.49</v>
+      </c>
+      <c r="BH219">
+        <v>2.43</v>
+      </c>
+      <c r="BI219">
+        <v>1.81</v>
+      </c>
+      <c r="BJ219">
+        <v>1.88</v>
+      </c>
+      <c r="BK219">
+        <v>2.32</v>
+      </c>
+      <c r="BL219">
+        <v>1.53</v>
+      </c>
+      <c r="BM219">
+        <v>3.05</v>
+      </c>
+      <c r="BN219">
+        <v>1.32</v>
+      </c>
+      <c r="BO219">
+        <v>4</v>
+      </c>
+      <c r="BP219">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="220" spans="1:68">
+      <c r="A220" s="1">
+        <v>219</v>
+      </c>
+      <c r="B220">
+        <v>7509793</v>
+      </c>
+      <c r="C220" t="s">
+        <v>68</v>
+      </c>
+      <c r="D220" t="s">
+        <v>69</v>
+      </c>
+      <c r="E220" s="2">
+        <v>45676.45833333334</v>
+      </c>
+      <c r="F220">
+        <v>22</v>
+      </c>
+      <c r="G220" t="s">
+        <v>89</v>
+      </c>
+      <c r="H220" t="s">
+        <v>88</v>
+      </c>
+      <c r="I220">
+        <v>0</v>
+      </c>
+      <c r="J220">
+        <v>0</v>
+      </c>
+      <c r="K220">
+        <v>0</v>
+      </c>
+      <c r="L220">
+        <v>1</v>
+      </c>
+      <c r="M220">
+        <v>0</v>
+      </c>
+      <c r="N220">
+        <v>1</v>
+      </c>
+      <c r="O220" t="s">
+        <v>209</v>
+      </c>
+      <c r="P220" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q220">
+        <v>2.55</v>
+      </c>
+      <c r="R220">
+        <v>2</v>
+      </c>
+      <c r="S220">
+        <v>4.2</v>
+      </c>
+      <c r="T220">
+        <v>1.44</v>
+      </c>
+      <c r="U220">
+        <v>2.55</v>
+      </c>
+      <c r="V220">
+        <v>3</v>
+      </c>
+      <c r="W220">
+        <v>1.33</v>
+      </c>
+      <c r="X220">
+        <v>8.25</v>
+      </c>
+      <c r="Y220">
+        <v>1.06</v>
+      </c>
+      <c r="Z220">
+        <v>1.93</v>
+      </c>
+      <c r="AA220">
+        <v>3.15</v>
+      </c>
+      <c r="AB220">
+        <v>4.18</v>
+      </c>
+      <c r="AC220">
+        <v>1.07</v>
+      </c>
+      <c r="AD220">
+        <v>8</v>
+      </c>
+      <c r="AE220">
+        <v>1.38</v>
+      </c>
+      <c r="AF220">
+        <v>3</v>
+      </c>
+      <c r="AG220">
+        <v>2.07</v>
+      </c>
+      <c r="AH220">
+        <v>1.67</v>
+      </c>
+      <c r="AI220">
+        <v>1.93</v>
+      </c>
+      <c r="AJ220">
+        <v>1.75</v>
+      </c>
+      <c r="AK220">
+        <v>1.24</v>
+      </c>
+      <c r="AL220">
+        <v>1.3</v>
+      </c>
+      <c r="AM220">
+        <v>1.82</v>
+      </c>
+      <c r="AN220">
+        <v>1.5</v>
+      </c>
+      <c r="AO220">
+        <v>1.36</v>
+      </c>
+      <c r="AP220">
+        <v>1.64</v>
+      </c>
+      <c r="AQ220">
+        <v>1.25</v>
+      </c>
+      <c r="AR220">
+        <v>1.84</v>
+      </c>
+      <c r="AS220">
+        <v>1.05</v>
+      </c>
+      <c r="AT220">
+        <v>2.89</v>
+      </c>
+      <c r="AU220">
+        <v>5</v>
+      </c>
+      <c r="AV220">
+        <v>4</v>
+      </c>
+      <c r="AW220">
+        <v>6</v>
+      </c>
+      <c r="AX220">
+        <v>7</v>
+      </c>
+      <c r="AY220">
+        <v>13</v>
+      </c>
+      <c r="AZ220">
+        <v>14</v>
+      </c>
+      <c r="BA220">
+        <v>5</v>
+      </c>
+      <c r="BB220">
+        <v>7</v>
+      </c>
+      <c r="BC220">
+        <v>12</v>
+      </c>
+      <c r="BD220">
+        <v>1.65</v>
+      </c>
+      <c r="BE220">
+        <v>6.4</v>
+      </c>
+      <c r="BF220">
+        <v>2.55</v>
+      </c>
+      <c r="BG220">
+        <v>1.46</v>
+      </c>
+      <c r="BH220">
+        <v>2.5</v>
+      </c>
+      <c r="BI220">
+        <v>1.76</v>
+      </c>
+      <c r="BJ220">
+        <v>1.94</v>
+      </c>
+      <c r="BK220">
+        <v>2.23</v>
+      </c>
+      <c r="BL220">
+        <v>1.57</v>
+      </c>
+      <c r="BM220">
+        <v>2.9</v>
+      </c>
+      <c r="BN220">
+        <v>1.35</v>
+      </c>
+      <c r="BO220">
+        <v>3.8</v>
+      </c>
+      <c r="BP220">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="221" spans="1:68">
+      <c r="A221" s="1">
+        <v>220</v>
+      </c>
+      <c r="B221">
+        <v>7509788</v>
+      </c>
+      <c r="C221" t="s">
+        <v>68</v>
+      </c>
+      <c r="D221" t="s">
+        <v>69</v>
+      </c>
+      <c r="E221" s="2">
+        <v>45676.55208333334</v>
+      </c>
+      <c r="F221">
+        <v>22</v>
+      </c>
+      <c r="G221" t="s">
+        <v>86</v>
+      </c>
+      <c r="H221" t="s">
+        <v>83</v>
+      </c>
+      <c r="I221">
+        <v>0</v>
+      </c>
+      <c r="J221">
+        <v>2</v>
+      </c>
+      <c r="K221">
+        <v>2</v>
+      </c>
+      <c r="L221">
+        <v>0</v>
+      </c>
+      <c r="M221">
+        <v>4</v>
+      </c>
+      <c r="N221">
+        <v>4</v>
+      </c>
+      <c r="O221" t="s">
+        <v>102</v>
+      </c>
+      <c r="P221" t="s">
+        <v>316</v>
+      </c>
+      <c r="Q221">
+        <v>3.75</v>
+      </c>
+      <c r="R221">
+        <v>1.91</v>
+      </c>
+      <c r="S221">
+        <v>3.4</v>
+      </c>
+      <c r="T221">
+        <v>1.57</v>
+      </c>
+      <c r="U221">
+        <v>2.25</v>
+      </c>
+      <c r="V221">
+        <v>3.75</v>
+      </c>
+      <c r="W221">
+        <v>1.25</v>
+      </c>
+      <c r="X221">
+        <v>11</v>
+      </c>
+      <c r="Y221">
+        <v>1.05</v>
+      </c>
+      <c r="Z221">
+        <v>2.75</v>
+      </c>
+      <c r="AA221">
+        <v>2.88</v>
+      </c>
+      <c r="AB221">
+        <v>2.75</v>
+      </c>
+      <c r="AC221">
+        <v>1.1</v>
+      </c>
+      <c r="AD221">
+        <v>6.5</v>
+      </c>
+      <c r="AE221">
+        <v>1.51</v>
+      </c>
+      <c r="AF221">
+        <v>2.55</v>
+      </c>
+      <c r="AG221">
+        <v>2.37</v>
+      </c>
+      <c r="AH221">
+        <v>1.48</v>
+      </c>
+      <c r="AI221">
+        <v>2.05</v>
+      </c>
+      <c r="AJ221">
+        <v>1.7</v>
+      </c>
+      <c r="AK221">
+        <v>1.5</v>
+      </c>
+      <c r="AL221">
+        <v>1.36</v>
+      </c>
+      <c r="AM221">
+        <v>1.38</v>
+      </c>
+      <c r="AN221">
+        <v>2.1</v>
+      </c>
+      <c r="AO221">
+        <v>1.36</v>
+      </c>
+      <c r="AP221">
+        <v>1.91</v>
+      </c>
+      <c r="AQ221">
+        <v>1.5</v>
+      </c>
+      <c r="AR221">
+        <v>1.33</v>
+      </c>
+      <c r="AS221">
+        <v>1.32</v>
+      </c>
+      <c r="AT221">
+        <v>2.65</v>
+      </c>
+      <c r="AU221">
+        <v>3</v>
+      </c>
+      <c r="AV221">
+        <v>8</v>
+      </c>
+      <c r="AW221">
+        <v>11</v>
+      </c>
+      <c r="AX221">
+        <v>13</v>
+      </c>
+      <c r="AY221">
+        <v>14</v>
+      </c>
+      <c r="AZ221">
+        <v>24</v>
+      </c>
+      <c r="BA221">
+        <v>4</v>
+      </c>
+      <c r="BB221">
+        <v>3</v>
+      </c>
+      <c r="BC221">
+        <v>7</v>
+      </c>
+      <c r="BD221">
+        <v>2.07</v>
+      </c>
+      <c r="BE221">
+        <v>6.4</v>
+      </c>
+      <c r="BF221">
+        <v>1.93</v>
+      </c>
+      <c r="BG221">
+        <v>1.34</v>
+      </c>
+      <c r="BH221">
+        <v>2.9</v>
+      </c>
+      <c r="BI221">
+        <v>1.57</v>
+      </c>
+      <c r="BJ221">
+        <v>2.2</v>
+      </c>
+      <c r="BK221">
+        <v>1.95</v>
+      </c>
+      <c r="BL221">
+        <v>1.75</v>
+      </c>
+      <c r="BM221">
+        <v>2.48</v>
+      </c>
+      <c r="BN221">
+        <v>1.47</v>
+      </c>
+      <c r="BO221">
+        <v>3.2</v>
+      </c>
+      <c r="BP221">
         <v>1.28</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Italy Serie B_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Italy Serie B_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1388" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1394" uniqueCount="319">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -691,6 +691,9 @@
     <t>['9', '55', '58', '69', '90+2']</t>
   </si>
   <si>
+    <t>['8', '75']</t>
+  </si>
+  <si>
     <t>['24', '45+2', '80']</t>
   </si>
   <si>
@@ -965,6 +968,9 @@
   </si>
   <si>
     <t>['20', '45+4', '50', '58']</t>
+  </si>
+  <si>
+    <t>['35']</t>
   </si>
 </sst>
 </file>
@@ -1326,7 +1332,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP221"/>
+  <dimension ref="A1:BP222"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1788,7 +1794,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q3">
         <v>2.63</v>
@@ -1994,7 +2000,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q4">
         <v>3.5</v>
@@ -2200,7 +2206,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q5">
         <v>3.2</v>
@@ -2612,7 +2618,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q7">
         <v>3.25</v>
@@ -3024,7 +3030,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q9">
         <v>3.4</v>
@@ -3230,7 +3236,7 @@
         <v>98</v>
       </c>
       <c r="P10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q10">
         <v>3.75</v>
@@ -3311,7 +3317,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ10">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3642,7 +3648,7 @@
         <v>100</v>
       </c>
       <c r="P12" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q12">
         <v>3.25</v>
@@ -3848,7 +3854,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q13">
         <v>3.4</v>
@@ -4054,7 +4060,7 @@
         <v>102</v>
       </c>
       <c r="P14" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q14">
         <v>2.3</v>
@@ -4672,7 +4678,7 @@
         <v>104</v>
       </c>
       <c r="P17" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q17">
         <v>2.88</v>
@@ -4750,7 +4756,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ17">
         <v>0.91</v>
@@ -5290,7 +5296,7 @@
         <v>107</v>
       </c>
       <c r="P20" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q20">
         <v>2.88</v>
@@ -5702,7 +5708,7 @@
         <v>91</v>
       </c>
       <c r="P22" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q22">
         <v>3.4</v>
@@ -5783,7 +5789,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ22">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AR22">
         <v>1.6</v>
@@ -6114,7 +6120,7 @@
         <v>109</v>
       </c>
       <c r="P24" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q24">
         <v>2.98</v>
@@ -6732,7 +6738,7 @@
         <v>102</v>
       </c>
       <c r="P27" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q27">
         <v>2.74</v>
@@ -7968,7 +7974,7 @@
         <v>102</v>
       </c>
       <c r="P33" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q33">
         <v>2.8</v>
@@ -8380,7 +8386,7 @@
         <v>116</v>
       </c>
       <c r="P35" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q35">
         <v>3</v>
@@ -8586,7 +8592,7 @@
         <v>117</v>
       </c>
       <c r="P36" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q36">
         <v>2.9</v>
@@ -9204,7 +9210,7 @@
         <v>119</v>
       </c>
       <c r="P39" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q39">
         <v>2.63</v>
@@ -9410,7 +9416,7 @@
         <v>120</v>
       </c>
       <c r="P40" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q40">
         <v>3.2</v>
@@ -9488,7 +9494,7 @@
         <v>0</v>
       </c>
       <c r="AP40">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ40">
         <v>0.73</v>
@@ -9616,7 +9622,7 @@
         <v>121</v>
       </c>
       <c r="P41" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q41">
         <v>2.63</v>
@@ -9822,7 +9828,7 @@
         <v>122</v>
       </c>
       <c r="P42" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q42">
         <v>2.88</v>
@@ -10646,7 +10652,7 @@
         <v>125</v>
       </c>
       <c r="P46" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q46">
         <v>3.75</v>
@@ -11058,7 +11064,7 @@
         <v>116</v>
       </c>
       <c r="P48" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q48">
         <v>3.4</v>
@@ -11264,7 +11270,7 @@
         <v>102</v>
       </c>
       <c r="P49" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q49">
         <v>3.75</v>
@@ -11345,7 +11351,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ49">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AR49">
         <v>0.9399999999999999</v>
@@ -11470,7 +11476,7 @@
         <v>127</v>
       </c>
       <c r="P50" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q50">
         <v>3.4</v>
@@ -11676,7 +11682,7 @@
         <v>128</v>
       </c>
       <c r="P51" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q51">
         <v>3.1</v>
@@ -11882,7 +11888,7 @@
         <v>129</v>
       </c>
       <c r="P52" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q52">
         <v>3.79</v>
@@ -12169,7 +12175,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ53">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AR53">
         <v>1.32</v>
@@ -12500,7 +12506,7 @@
         <v>130</v>
       </c>
       <c r="P55" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q55">
         <v>2.5</v>
@@ -13324,7 +13330,7 @@
         <v>102</v>
       </c>
       <c r="P59" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q59">
         <v>3.1</v>
@@ -13736,7 +13742,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q61">
         <v>2.38</v>
@@ -13814,7 +13820,7 @@
         <v>0</v>
       </c>
       <c r="AP61">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ61">
         <v>0.55</v>
@@ -13942,7 +13948,7 @@
         <v>134</v>
       </c>
       <c r="P62" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q62">
         <v>3.25</v>
@@ -14354,7 +14360,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q64">
         <v>2.9</v>
@@ -14766,7 +14772,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q66">
         <v>2.4</v>
@@ -15178,7 +15184,7 @@
         <v>138</v>
       </c>
       <c r="P68" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q68">
         <v>3.1</v>
@@ -15590,7 +15596,7 @@
         <v>139</v>
       </c>
       <c r="P70" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q70">
         <v>3.5</v>
@@ -15796,7 +15802,7 @@
         <v>140</v>
       </c>
       <c r="P71" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q71">
         <v>3.5</v>
@@ -16002,7 +16008,7 @@
         <v>141</v>
       </c>
       <c r="P72" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q72">
         <v>2.4</v>
@@ -16208,7 +16214,7 @@
         <v>102</v>
       </c>
       <c r="P73" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q73">
         <v>2.5</v>
@@ -16414,7 +16420,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q74">
         <v>2.5</v>
@@ -16698,7 +16704,7 @@
         <v>1.33</v>
       </c>
       <c r="AP75">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ75">
         <v>1.09</v>
@@ -16826,7 +16832,7 @@
         <v>143</v>
       </c>
       <c r="P76" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q76">
         <v>2.95</v>
@@ -17032,7 +17038,7 @@
         <v>102</v>
       </c>
       <c r="P77" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q77">
         <v>3.2</v>
@@ -17238,7 +17244,7 @@
         <v>144</v>
       </c>
       <c r="P78" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q78">
         <v>3.1</v>
@@ -17444,7 +17450,7 @@
         <v>134</v>
       </c>
       <c r="P79" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q79">
         <v>2.5</v>
@@ -17650,7 +17656,7 @@
         <v>145</v>
       </c>
       <c r="P80" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q80">
         <v>3.4</v>
@@ -18268,7 +18274,7 @@
         <v>146</v>
       </c>
       <c r="P83" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q83">
         <v>3.6</v>
@@ -18474,7 +18480,7 @@
         <v>102</v>
       </c>
       <c r="P84" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q84">
         <v>3.4</v>
@@ -18886,7 +18892,7 @@
         <v>147</v>
       </c>
       <c r="P86" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q86">
         <v>3.2</v>
@@ -19092,7 +19098,7 @@
         <v>148</v>
       </c>
       <c r="P87" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q87">
         <v>3.2</v>
@@ -19173,7 +19179,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ87">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AR87">
         <v>1.8</v>
@@ -19298,7 +19304,7 @@
         <v>149</v>
       </c>
       <c r="P88" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q88">
         <v>3.75</v>
@@ -19504,7 +19510,7 @@
         <v>150</v>
       </c>
       <c r="P89" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q89">
         <v>2.88</v>
@@ -19916,7 +19922,7 @@
         <v>152</v>
       </c>
       <c r="P91" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q91">
         <v>3.1</v>
@@ -20200,7 +20206,7 @@
         <v>1.25</v>
       </c>
       <c r="AP92">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ92">
         <v>1.1</v>
@@ -22594,7 +22600,7 @@
         <v>160</v>
       </c>
       <c r="P104" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q104">
         <v>3.9</v>
@@ -22675,7 +22681,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ104">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AR104">
         <v>1.28</v>
@@ -22800,7 +22806,7 @@
         <v>161</v>
       </c>
       <c r="P105" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q105">
         <v>3.25</v>
@@ -23418,7 +23424,7 @@
         <v>162</v>
       </c>
       <c r="P108" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q108">
         <v>3.1</v>
@@ -24320,7 +24326,7 @@
         <v>0.6</v>
       </c>
       <c r="AP112">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ112">
         <v>0.82</v>
@@ -24448,7 +24454,7 @@
         <v>163</v>
       </c>
       <c r="P113" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q113">
         <v>2.75</v>
@@ -25272,7 +25278,7 @@
         <v>164</v>
       </c>
       <c r="P117" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q117">
         <v>3</v>
@@ -25478,7 +25484,7 @@
         <v>164</v>
       </c>
       <c r="P118" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q118">
         <v>2.88</v>
@@ -25890,7 +25896,7 @@
         <v>102</v>
       </c>
       <c r="P120" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q120">
         <v>2.4</v>
@@ -26302,7 +26308,7 @@
         <v>166</v>
       </c>
       <c r="P122" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q122">
         <v>3.45</v>
@@ -26589,7 +26595,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ123">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AR123">
         <v>1.52</v>
@@ -27126,7 +27132,7 @@
         <v>169</v>
       </c>
       <c r="P126" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q126">
         <v>3.1</v>
@@ -27538,7 +27544,7 @@
         <v>102</v>
       </c>
       <c r="P128" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q128">
         <v>3.65</v>
@@ -27744,7 +27750,7 @@
         <v>102</v>
       </c>
       <c r="P129" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q129">
         <v>3.35</v>
@@ -27950,7 +27956,7 @@
         <v>170</v>
       </c>
       <c r="P130" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q130">
         <v>3</v>
@@ -28156,7 +28162,7 @@
         <v>102</v>
       </c>
       <c r="P131" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q131">
         <v>3.1</v>
@@ -28362,7 +28368,7 @@
         <v>119</v>
       </c>
       <c r="P132" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q132">
         <v>3.4</v>
@@ -29186,7 +29192,7 @@
         <v>173</v>
       </c>
       <c r="P136" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q136">
         <v>2.5</v>
@@ -29392,7 +29398,7 @@
         <v>174</v>
       </c>
       <c r="P137" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q137">
         <v>2.6</v>
@@ -29598,7 +29604,7 @@
         <v>175</v>
       </c>
       <c r="P138" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q138">
         <v>2.6</v>
@@ -29882,7 +29888,7 @@
         <v>1</v>
       </c>
       <c r="AP139">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ139">
         <v>0.91</v>
@@ -30216,7 +30222,7 @@
         <v>178</v>
       </c>
       <c r="P141" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -30422,7 +30428,7 @@
         <v>102</v>
       </c>
       <c r="P142" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q142">
         <v>4.2</v>
@@ -30503,7 +30509,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ142">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AR142">
         <v>1.2</v>
@@ -30628,7 +30634,7 @@
         <v>179</v>
       </c>
       <c r="P143" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q143">
         <v>2.55</v>
@@ -30834,7 +30840,7 @@
         <v>102</v>
       </c>
       <c r="P144" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q144">
         <v>3.95</v>
@@ -31246,7 +31252,7 @@
         <v>181</v>
       </c>
       <c r="P146" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q146">
         <v>3.1</v>
@@ -31864,7 +31870,7 @@
         <v>183</v>
       </c>
       <c r="P149" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q149">
         <v>2.63</v>
@@ -32070,7 +32076,7 @@
         <v>184</v>
       </c>
       <c r="P150" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q150">
         <v>3.6</v>
@@ -32482,7 +32488,7 @@
         <v>186</v>
       </c>
       <c r="P152" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q152">
         <v>2.95</v>
@@ -33100,7 +33106,7 @@
         <v>188</v>
       </c>
       <c r="P155" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q155">
         <v>3.7</v>
@@ -33512,7 +33518,7 @@
         <v>102</v>
       </c>
       <c r="P157" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q157">
         <v>2.9</v>
@@ -33924,7 +33930,7 @@
         <v>102</v>
       </c>
       <c r="P159" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q159">
         <v>2.2</v>
@@ -34208,7 +34214,7 @@
         <v>1.13</v>
       </c>
       <c r="AP160">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ160">
         <v>1.18</v>
@@ -34336,7 +34342,7 @@
         <v>191</v>
       </c>
       <c r="P161" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q161">
         <v>2.2</v>
@@ -34748,7 +34754,7 @@
         <v>193</v>
       </c>
       <c r="P163" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q163">
         <v>3</v>
@@ -35160,7 +35166,7 @@
         <v>194</v>
       </c>
       <c r="P165" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q165">
         <v>4.33</v>
@@ -35241,7 +35247,7 @@
         <v>1</v>
       </c>
       <c r="AQ165">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AR165">
         <v>1.36</v>
@@ -35778,7 +35784,7 @@
         <v>196</v>
       </c>
       <c r="P168" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q168">
         <v>2.4</v>
@@ -36396,7 +36402,7 @@
         <v>197</v>
       </c>
       <c r="P171" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q171">
         <v>3</v>
@@ -37838,7 +37844,7 @@
         <v>201</v>
       </c>
       <c r="P178" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q178">
         <v>3.1</v>
@@ -38044,7 +38050,7 @@
         <v>102</v>
       </c>
       <c r="P179" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q179">
         <v>3.55</v>
@@ -38743,7 +38749,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ182">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AR182">
         <v>1.39</v>
@@ -39074,7 +39080,7 @@
         <v>91</v>
       </c>
       <c r="P184" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q184">
         <v>2.3</v>
@@ -39152,7 +39158,7 @@
         <v>0.44</v>
       </c>
       <c r="AP184">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ184">
         <v>0.75</v>
@@ -39280,7 +39286,7 @@
         <v>204</v>
       </c>
       <c r="P185" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q185">
         <v>3.1</v>
@@ -39898,7 +39904,7 @@
         <v>206</v>
       </c>
       <c r="P188" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q188">
         <v>3.25</v>
@@ -40516,7 +40522,7 @@
         <v>209</v>
       </c>
       <c r="P191" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q191">
         <v>2.75</v>
@@ -40722,7 +40728,7 @@
         <v>210</v>
       </c>
       <c r="P192" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q192">
         <v>2.4</v>
@@ -41752,7 +41758,7 @@
         <v>102</v>
       </c>
       <c r="P197" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q197">
         <v>2.5</v>
@@ -42370,7 +42376,7 @@
         <v>149</v>
       </c>
       <c r="P200" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q200">
         <v>2.63</v>
@@ -42782,7 +42788,7 @@
         <v>215</v>
       </c>
       <c r="P202" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q202">
         <v>4.33</v>
@@ -42863,7 +42869,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ202">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AR202">
         <v>1.7</v>
@@ -43194,7 +43200,7 @@
         <v>197</v>
       </c>
       <c r="P204" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q204">
         <v>2.5</v>
@@ -43272,7 +43278,7 @@
         <v>1.4</v>
       </c>
       <c r="AP204">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ204">
         <v>1.25</v>
@@ -43606,7 +43612,7 @@
         <v>217</v>
       </c>
       <c r="P206" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q206">
         <v>3.4</v>
@@ -43812,7 +43818,7 @@
         <v>218</v>
       </c>
       <c r="P207" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q207">
         <v>2.75</v>
@@ -44018,7 +44024,7 @@
         <v>102</v>
       </c>
       <c r="P208" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q208">
         <v>4</v>
@@ -44842,7 +44848,7 @@
         <v>217</v>
       </c>
       <c r="P212" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q212">
         <v>3</v>
@@ -45048,7 +45054,7 @@
         <v>220</v>
       </c>
       <c r="P213" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q213">
         <v>2.87</v>
@@ -45254,7 +45260,7 @@
         <v>112</v>
       </c>
       <c r="P214" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q214">
         <v>2.7</v>
@@ -45872,7 +45878,7 @@
         <v>223</v>
       </c>
       <c r="P217" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q217">
         <v>2.65</v>
@@ -46078,7 +46084,7 @@
         <v>224</v>
       </c>
       <c r="P218" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q218">
         <v>2.05</v>
@@ -46696,7 +46702,7 @@
         <v>102</v>
       </c>
       <c r="P221" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q221">
         <v>3.75</v>
@@ -46853,6 +46859,212 @@
       </c>
       <c r="BP221">
         <v>1.28</v>
+      </c>
+    </row>
+    <row r="222" spans="1:68">
+      <c r="A222" s="1">
+        <v>221</v>
+      </c>
+      <c r="B222">
+        <v>7509816</v>
+      </c>
+      <c r="C222" t="s">
+        <v>68</v>
+      </c>
+      <c r="D222" t="s">
+        <v>69</v>
+      </c>
+      <c r="E222" s="2">
+        <v>45681.6875</v>
+      </c>
+      <c r="F222">
+        <v>23</v>
+      </c>
+      <c r="G222" t="s">
+        <v>83</v>
+      </c>
+      <c r="H222" t="s">
+        <v>84</v>
+      </c>
+      <c r="I222">
+        <v>1</v>
+      </c>
+      <c r="J222">
+        <v>1</v>
+      </c>
+      <c r="K222">
+        <v>2</v>
+      </c>
+      <c r="L222">
+        <v>2</v>
+      </c>
+      <c r="M222">
+        <v>1</v>
+      </c>
+      <c r="N222">
+        <v>3</v>
+      </c>
+      <c r="O222" t="s">
+        <v>225</v>
+      </c>
+      <c r="P222" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q222">
+        <v>3.1</v>
+      </c>
+      <c r="R222">
+        <v>2.1</v>
+      </c>
+      <c r="S222">
+        <v>3.1</v>
+      </c>
+      <c r="T222">
+        <v>1.38</v>
+      </c>
+      <c r="U222">
+        <v>2.8</v>
+      </c>
+      <c r="V222">
+        <v>2.7</v>
+      </c>
+      <c r="W222">
+        <v>1.4</v>
+      </c>
+      <c r="X222">
+        <v>6.75</v>
+      </c>
+      <c r="Y222">
+        <v>1.09</v>
+      </c>
+      <c r="Z222">
+        <v>2.68</v>
+      </c>
+      <c r="AA222">
+        <v>3.41</v>
+      </c>
+      <c r="AB222">
+        <v>2.71</v>
+      </c>
+      <c r="AC222">
+        <v>1.06</v>
+      </c>
+      <c r="AD222">
+        <v>8.5</v>
+      </c>
+      <c r="AE222">
+        <v>1.3</v>
+      </c>
+      <c r="AF222">
+        <v>3.45</v>
+      </c>
+      <c r="AG222">
+        <v>1.87</v>
+      </c>
+      <c r="AH222">
+        <v>1.83</v>
+      </c>
+      <c r="AI222">
+        <v>1.7</v>
+      </c>
+      <c r="AJ222">
+        <v>2</v>
+      </c>
+      <c r="AK222">
+        <v>1.47</v>
+      </c>
+      <c r="AL222">
+        <v>1.31</v>
+      </c>
+      <c r="AM222">
+        <v>1.47</v>
+      </c>
+      <c r="AN222">
+        <v>2.4</v>
+      </c>
+      <c r="AO222">
+        <v>2.18</v>
+      </c>
+      <c r="AP222">
+        <v>2.45</v>
+      </c>
+      <c r="AQ222">
+        <v>2</v>
+      </c>
+      <c r="AR222">
+        <v>1.73</v>
+      </c>
+      <c r="AS222">
+        <v>1.42</v>
+      </c>
+      <c r="AT222">
+        <v>3.15</v>
+      </c>
+      <c r="AU222">
+        <v>10</v>
+      </c>
+      <c r="AV222">
+        <v>4</v>
+      </c>
+      <c r="AW222">
+        <v>10</v>
+      </c>
+      <c r="AX222">
+        <v>5</v>
+      </c>
+      <c r="AY222">
+        <v>22</v>
+      </c>
+      <c r="AZ222">
+        <v>13</v>
+      </c>
+      <c r="BA222">
+        <v>3</v>
+      </c>
+      <c r="BB222">
+        <v>5</v>
+      </c>
+      <c r="BC222">
+        <v>8</v>
+      </c>
+      <c r="BD222">
+        <v>2</v>
+      </c>
+      <c r="BE222">
+        <v>6.25</v>
+      </c>
+      <c r="BF222">
+        <v>1.98</v>
+      </c>
+      <c r="BG222">
+        <v>1.4</v>
+      </c>
+      <c r="BH222">
+        <v>2.65</v>
+      </c>
+      <c r="BI222">
+        <v>1.68</v>
+      </c>
+      <c r="BJ222">
+        <v>2.05</v>
+      </c>
+      <c r="BK222">
+        <v>2.08</v>
+      </c>
+      <c r="BL222">
+        <v>1.65</v>
+      </c>
+      <c r="BM222">
+        <v>2.65</v>
+      </c>
+      <c r="BN222">
+        <v>1.4</v>
+      </c>
+      <c r="BO222">
+        <v>3.55</v>
+      </c>
+      <c r="BP222">
+        <v>1.24</v>
       </c>
     </row>
   </sheetData>
